--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -2721,25 +2721,25 @@
         <v>29.558</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5402095</v>
+        <v>113282</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2748,60 +2748,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Ray McCaughey TNP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>193.416</v>
+        <v>193.128</v>
       </c>
       <c r="I3" t="n">
-        <v>106.818</v>
+        <v>106.593</v>
       </c>
       <c r="J3" t="n">
-        <v>60.149</v>
+        <v>61.638</v>
       </c>
       <c r="K3" t="n">
-        <v>37.553</v>
+        <v>38.788</v>
       </c>
       <c r="L3" t="n">
-        <v>29.783</v>
+        <v>28.714</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88513</v>
+        <v>5402095</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jacob Ingram</t>
+          <t>Quentin Vee [EVO]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2824,46 +2824,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>193.584</v>
+        <v>193.416</v>
       </c>
       <c r="I4" t="n">
-        <v>107.829</v>
+        <v>106.818</v>
       </c>
       <c r="J4" t="n">
-        <v>60.253</v>
+        <v>60.149</v>
       </c>
       <c r="K4" t="n">
-        <v>38.034</v>
+        <v>37.553</v>
       </c>
       <c r="L4" t="n">
-        <v>28.598</v>
+        <v>29.783</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113282</v>
+        <v>88513</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2872,54 +2872,54 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ray McCaughey TNP</t>
+          <t>Jacob Ingram</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>193.128</v>
+        <v>193.584</v>
       </c>
       <c r="I5" t="n">
-        <v>106.593</v>
+        <v>107.829</v>
       </c>
       <c r="J5" t="n">
-        <v>61.638</v>
+        <v>60.253</v>
       </c>
       <c r="K5" t="n">
-        <v>38.788</v>
+        <v>38.034</v>
       </c>
       <c r="L5" t="n">
-        <v>28.714</v>
+        <v>28.598</v>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -2965,19 +2965,19 @@
         <v>33.094</v>
       </c>
       <c r="M6" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -3027,25 +3027,25 @@
         <v>29.695</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>679077</v>
+        <v>394612</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -3059,55 +3059,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>193.604</v>
+        <v>198.478</v>
       </c>
       <c r="I8" t="n">
-        <v>108.037</v>
+        <v>128.345</v>
       </c>
       <c r="J8" t="n">
-        <v>60.402</v>
+        <v>71.063</v>
       </c>
       <c r="K8" t="n">
-        <v>38.362</v>
+        <v>37.19</v>
       </c>
       <c r="L8" t="n">
-        <v>30.082</v>
+        <v>39.72</v>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>394612</v>
+        <v>679077</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -3121,49 +3121,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t>Den Morrison</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>198.478</v>
+        <v>193.604</v>
       </c>
       <c r="I9" t="n">
-        <v>128.345</v>
+        <v>108.037</v>
       </c>
       <c r="J9" t="n">
-        <v>71.063</v>
+        <v>60.402</v>
       </c>
       <c r="K9" t="n">
-        <v>37.19</v>
+        <v>38.362</v>
       </c>
       <c r="L9" t="n">
-        <v>39.72</v>
+        <v>30.082</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -3213,19 +3213,19 @@
         <v>37.799</v>
       </c>
       <c r="M10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -3275,25 +3275,25 @@
         <v>35.459</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2959735</v>
+        <v>2988740</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -3307,55 +3307,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>235.395</v>
+        <v>226.68</v>
       </c>
       <c r="I12" t="n">
-        <v>129.405</v>
+        <v>126.518</v>
       </c>
       <c r="J12" t="n">
-        <v>63.742</v>
+        <v>63.528</v>
       </c>
       <c r="K12" t="n">
-        <v>42.304</v>
+        <v>42.808</v>
       </c>
       <c r="L12" t="n">
-        <v>35.006</v>
+        <v>43.408</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2988740</v>
+        <v>260262</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3369,55 +3369,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>226.68</v>
+        <v>274.151</v>
       </c>
       <c r="I13" t="n">
-        <v>126.518</v>
+        <v>148.706</v>
       </c>
       <c r="J13" t="n">
-        <v>63.528</v>
+        <v>74.503</v>
       </c>
       <c r="K13" t="n">
-        <v>42.808</v>
+        <v>35.732</v>
       </c>
       <c r="L13" t="n">
-        <v>43.408</v>
+        <v>32.012</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>260262</v>
+        <v>2959735</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3431,49 +3431,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>HISP</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>274.151</v>
+        <v>235.395</v>
       </c>
       <c r="I14" t="n">
-        <v>148.706</v>
+        <v>129.405</v>
       </c>
       <c r="J14" t="n">
-        <v>74.503</v>
+        <v>63.742</v>
       </c>
       <c r="K14" t="n">
-        <v>35.732</v>
+        <v>42.304</v>
       </c>
       <c r="L14" t="n">
-        <v>32.012</v>
+        <v>35.006</v>
       </c>
       <c r="M14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -3519,19 +3519,19 @@
         <v>34.856</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R15" t="inlineStr"/>
     </row>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -3581,19 +3581,19 @@
         <v>38.45</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R16" t="inlineStr"/>
     </row>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -3643,25 +3643,25 @@
         <v>35.419</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2297188</v>
+        <v>25</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Javier (HERC) </t>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3684,46 +3684,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>247.428</v>
+        <v>246.415</v>
       </c>
       <c r="I18" t="n">
-        <v>140.483</v>
+        <v>143.226</v>
       </c>
       <c r="J18" t="n">
-        <v>68.947</v>
+        <v>63.67</v>
       </c>
       <c r="K18" t="n">
-        <v>40.29</v>
+        <v>42.136</v>
       </c>
       <c r="L18" t="n">
-        <v>39.053</v>
+        <v>44.269</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>25</v>
+        <v>7779078</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3746,46 +3746,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>246.415</v>
+        <v>269.648</v>
       </c>
       <c r="I19" t="n">
-        <v>143.226</v>
+        <v>147.455</v>
       </c>
       <c r="J19" t="n">
-        <v>63.67</v>
+        <v>75.449</v>
       </c>
       <c r="K19" t="n">
-        <v>42.136</v>
+        <v>36.355</v>
       </c>
       <c r="L19" t="n">
-        <v>44.269</v>
+        <v>35.063</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7779078</v>
+        <v>2297188</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t xml:space="preserve">1 Javier (HERC) </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3808,46 +3808,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>269.648</v>
+        <v>247.428</v>
       </c>
       <c r="I20" t="n">
-        <v>147.455</v>
+        <v>140.483</v>
       </c>
       <c r="J20" t="n">
-        <v>75.449</v>
+        <v>68.947</v>
       </c>
       <c r="K20" t="n">
-        <v>36.355</v>
+        <v>40.29</v>
       </c>
       <c r="L20" t="n">
-        <v>35.063</v>
+        <v>39.053</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1379058</v>
+        <v>368568</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3856,60 +3856,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>273.644</v>
+        <v>239.216</v>
       </c>
       <c r="I21" t="n">
-        <v>147.985</v>
+        <v>147.682</v>
       </c>
       <c r="J21" t="n">
-        <v>67.021</v>
+        <v>64.077</v>
       </c>
       <c r="K21" t="n">
-        <v>36.63</v>
+        <v>42.797</v>
       </c>
       <c r="L21" t="n">
-        <v>31.796</v>
+        <v>39.839</v>
       </c>
       <c r="M21" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>368568</v>
+        <v>1379058</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3918,54 +3918,54 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>239.216</v>
+        <v>273.644</v>
       </c>
       <c r="I22" t="n">
-        <v>147.682</v>
+        <v>147.985</v>
       </c>
       <c r="J22" t="n">
-        <v>64.077</v>
+        <v>67.021</v>
       </c>
       <c r="K22" t="n">
-        <v>42.797</v>
+        <v>36.63</v>
       </c>
       <c r="L22" t="n">
-        <v>39.839</v>
+        <v>31.796</v>
       </c>
       <c r="M22" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="R22" t="inlineStr"/>
     </row>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -4015,19 +4015,19 @@
         <v>39.652</v>
       </c>
       <c r="M23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R23" t="inlineStr"/>
     </row>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -4077,19 +4077,19 @@
         <v>39.405</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R24" t="inlineStr"/>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -4135,19 +4135,19 @@
         <v>58.468</v>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R25" t="inlineStr"/>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -4193,19 +4193,19 @@
         <v>46.632</v>
       </c>
       <c r="M26" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R26" t="inlineStr"/>
     </row>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -4255,19 +4255,19 @@
         <v>40.523</v>
       </c>
       <c r="M27" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -4317,19 +4317,19 @@
         <v>62.116</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33:46.947</t>
+          <t>31:57.682</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -516,27 +516,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jacob Ingram</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>Brandon Quinton</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33:56.989</t>
+          <t>32:31.802</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.042</t>
+          <t>34.120</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -556,22 +552,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Mads Buster</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33:57.106</t>
+          <t>33:00.660</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.159</t>
+          <t>01:02.978</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,27 +582,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tom R Everested </t>
+          <t>Andr&amp;eacute;  Jones (A-P-V)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33:57.310</t>
+          <t>33:01.374</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.363</t>
+          <t>01:03.692</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -621,27 +617,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Akira  CafeLatte</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33:57.721</t>
+          <t>33:01.392</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.774</t>
+          <t>01:03.710</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -656,27 +648,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ray McCaughey TNP</t>
+          <t>Martin Coffey</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33:58.293</t>
+          <t>33:01.766</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.346</t>
+          <t>01:04.084</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -691,23 +683,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
+          <t>Mike Leahy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34:04.668</t>
+          <t>33:02.469</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.721</t>
+          <t>01:04.787</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -727,22 +719,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36:39.066</t>
+          <t>33:09.857</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02:52.119</t>
+          <t>01:12.175</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -752,32 +744,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jorelle  Hernandez (TZP)</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TZP</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37:14.815</t>
+          <t>33:46.947</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:49.265</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -787,32 +779,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Jacob Ingram</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37:41.896</t>
+          <t>33:56.989</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27.081</t>
+          <t>01:59.307</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -822,28 +814,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Quentin Vee [EVO]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38:01.970</t>
+          <t>33:57.106</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.155</t>
+          <t>01:59.424</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -853,32 +849,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t xml:space="preserve">Tom R Everested </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38:07.386</t>
+          <t>33:57.310</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.571</t>
+          <t>01:59.628</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -888,7 +884,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,22 +894,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+          <t>Den Morrison</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38:09.320</t>
+          <t>33:57.721</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.505</t>
+          <t>02:00.039</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -923,32 +919,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
+          <t>Ray McCaughey TNP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39:15.657</t>
+          <t>33:58.293</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02:00.842</t>
+          <t>02:00.611</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -958,32 +954,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41:03.174</t>
+          <t>34:04.668</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>03:48.359</t>
+          <t>02:06.986</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -993,32 +985,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t xml:space="preserve">Garth Haigh </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:38.215</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>03:40.533</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1028,32 +1020,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38:36.864</t>
+          <t>36:39.066</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30.436</t>
+          <t>04:41.384</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1063,7 +1055,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,22 +1065,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Abdullah Ak&amp;ccedil;am</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Zwift TURKIYE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>37:50.496</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.988</t>
+          <t>05:52.814</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1098,32 +1090,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Javier (HERC) </t>
+          <t>Andrew Stamp(RollCo)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39:21.436</t>
+          <t>36:51.881</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01:15.008</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1133,32 +1125,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Jorelle  Hernandez (TZP)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41:02.969</t>
+          <t>37:14.815</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02:56.541</t>
+          <t>22.934</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1168,32 +1160,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41:03.656</t>
+          <t>37:41.896</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02:57.228</t>
+          <t>50.015</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1203,7 +1195,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,22 +1205,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vonita</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41:05.154</t>
+          <t>38:01.970</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>02:58.726</t>
+          <t>01:10.089</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1238,28 +1226,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>38:07.386</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:15.505</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1269,28 +1261,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>@ arrows</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>38:09.320</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>01:12.867</t>
+          <t>01:17.439</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1300,32 +1296,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Neil Rogers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>39:15.657</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01:18.436</t>
+          <t>02:23.776</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1335,32 +1331,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>41:03.174</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>01:37.906</t>
+          <t>04:11.293</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1370,35 +1366,579 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Phil Cox (TNP)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>42:47.362</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>05:55.481</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>38:03.039</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Scott Henderson (BON - GXY)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>38:06.428</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>03.389</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>38:36.864</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>33.825</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>38:58.416</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>55.377</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Javier (HERC) </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>39:21.436</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>01:18.397</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Simon Baker</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>39:22.574</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>01:19.535</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Roberto Delgado Hynes</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>39:46.669</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>01:43.630</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>41:02.969</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>02:59.930</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>david white (HERC)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>41:03.656</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>03:00.617</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>41:05.154</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>03:02.115</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Evan  Carouchio</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>41:55.814</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>03:52.775</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Matt Jones</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>44:04.011</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>45:16.878</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>01:12.867</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>45:22.447</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>01:18.436</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Kim Bryan &amp;#127800;</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>45:41.917</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>01:37.906</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>[GALAXY]</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>51:44.021</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>07:40.010</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1504,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,7 +2177,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>374410</v>
+        <v>1377319</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1646,19 +2186,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tom R Everested </t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BIKELY</t>
-        </is>
-      </c>
+          <t>Akira  CafeLatte</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>16</v>
       </c>
@@ -1666,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>12.281</v>
+        <v>11.946</v>
       </c>
       <c r="I4" t="n">
         <v>16</v>
@@ -1675,7 +2211,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>679077</v>
+        <v>5428334</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1689,12 +2225,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
+          <t>Andr&amp;eacute;  Jones (A-P-V)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1704,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>12.359</v>
+        <v>12.006</v>
       </c>
       <c r="I5" t="n">
         <v>14</v>
@@ -1713,7 +2249,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113282</v>
+        <v>374410</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1722,17 +2258,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ray McCaughey TNP</t>
+          <t xml:space="preserve">Tom R Everested </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1742,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>13.926</v>
+        <v>12.281</v>
       </c>
       <c r="I6" t="n">
         <v>12</v>
@@ -1751,7 +2287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4980720</v>
+        <v>679077</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1760,17 +2296,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>Den Morrison</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1780,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>15.149</v>
+        <v>12.359</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -1789,7 +2325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2213032</v>
+        <v>3428761</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1798,15 +2334,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>Martin Coffey</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A-P-V</t>
+        </is>
+      </c>
       <c r="F8" t="n">
         <v>9</v>
       </c>
@@ -1814,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>15.361</v>
+        <v>12.604</v>
       </c>
       <c r="I8" t="n">
         <v>9</v>
@@ -1823,7 +2363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>394612</v>
+        <v>6863000</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1832,17 +2372,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1852,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>15.767</v>
+        <v>12.617</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
@@ -1861,121 +2401,121 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4879864</v>
+        <v>5977246</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jorelle  Hernandez (TZP)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TZP</t>
-        </is>
-      </c>
+          <t>Mike Leahy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>13.058</v>
+        <v>12.754</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>260262</v>
+        <v>4860176</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>Mads Buster</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>13.83</v>
+        <v>13.3</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4166463</v>
+        <v>113282</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Ray McCaughey TNP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>14.418</v>
+        <v>13.926</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1005102</v>
+        <v>6730421</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1985,339 +2525,331 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Abdullah Ak&amp;ccedil;am</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Zwift TURKIYE</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>14.879</v>
+        <v>14.618</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1236596</v>
+        <v>7250325</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Brandon Quinton</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>15.021</v>
+        <v>15.046</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2988740</v>
+        <v>4980720</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>15.882</v>
+        <v>15.149</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2959735</v>
+        <v>2213032</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HISP</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>16.11</v>
+        <v>15.361</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7779078</v>
+        <v>5959135</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>13.51</v>
+        <v>16.525</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2297188</v>
+        <v>1070115</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Javier (HERC) </t>
+          <t xml:space="preserve">Garth Haigh </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>13.584</v>
+        <v>16.562</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>25</v>
+        <v>394612</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>14.251</v>
+        <v>15.767</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1379058</v>
+        <v>4879864</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Jorelle  Hernandez (TZP)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>14.296</v>
+        <v>13.058</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>288798</v>
+        <v>260262</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>14.342</v>
+        <v>13.83</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>832585</v>
+        <v>4166463</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2327,35 +2859,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Vonita</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>15.301</v>
+        <v>14.418</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>368568</v>
+        <v>1005102</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2365,209 +2893,809 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>15.824</v>
+        <v>14.879</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>687504</v>
+        <v>1236596</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Neil Rogers</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>15.666</v>
+        <v>15.021</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3294901</v>
+        <v>2988740</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>15.678</v>
+        <v>15.882</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5689173</v>
+        <v>2959735</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HISP</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>15.899</v>
+        <v>16.11</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>426099</v>
+        <v>7166418</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>@ arrows</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Andrew Stamp(RollCo)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>15.963</v>
+        <v>16.452</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>5277640</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Phil Cox (TNP)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16.481</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7779078</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2297188</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Javier (HERC) </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>18</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>13.584</v>
+      </c>
+      <c r="I30" t="n">
+        <v>18</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>14.251</v>
+      </c>
+      <c r="I31" t="n">
+        <v>16</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1379058</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>david white (HERC)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>14</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14.296</v>
+      </c>
+      <c r="I32" t="n">
+        <v>14</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>288798</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Scott Henderson (BON - GXY)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>12</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>14.342</v>
+      </c>
+      <c r="I33" t="n">
+        <v>12</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9152</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Simon Baker</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>15.217</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>832585</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>15.301</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>368568</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>15.824</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>7229860</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>15.866</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6786487</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Roberto Delgado Hynes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16.266</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1087000</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Evan  Carouchio</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>16.454</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>687504</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Matt Jones</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>20</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15.666</v>
+      </c>
+      <c r="I40" t="n">
+        <v>20</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>18</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>15.678</v>
+      </c>
+      <c r="I41" t="n">
+        <v>18</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5689173</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kim Bryan &amp;#127800;</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>15.899</v>
+      </c>
+      <c r="I42" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>426099</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>15.963</v>
+      </c>
+      <c r="I43" t="n">
+        <v>14</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>281429</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>[GALAXY]</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F44" t="n">
         <v>12</v>
       </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
         <v>16.175</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I44" t="n">
         <v>12</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2580,7 +3708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,7 +3805,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>374410</v>
+        <v>6863000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2686,60 +3814,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tom R Everested </t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>192.992</v>
+        <v>173.696</v>
       </c>
       <c r="I2" t="n">
-        <v>106.718</v>
+        <v>87.405</v>
       </c>
       <c r="J2" t="n">
-        <v>59.757</v>
+        <v>55.703</v>
       </c>
       <c r="K2" t="n">
-        <v>37.398</v>
+        <v>33.569</v>
       </c>
       <c r="L2" t="n">
-        <v>29.558</v>
+        <v>31.652</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113282</v>
+        <v>7250325</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2753,55 +3881,51 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ray McCaughey TNP</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Brandon Quinton</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>193.128</v>
+        <v>173.417</v>
       </c>
       <c r="I3" t="n">
-        <v>106.593</v>
+        <v>104.171</v>
       </c>
       <c r="J3" t="n">
-        <v>61.638</v>
+        <v>55.861</v>
       </c>
       <c r="K3" t="n">
-        <v>38.788</v>
+        <v>32.983</v>
       </c>
       <c r="L3" t="n">
-        <v>28.714</v>
+        <v>30.367</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5402095</v>
+        <v>4860176</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2815,55 +3939,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Mads Buster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>193.416</v>
+        <v>173.26</v>
       </c>
       <c r="I4" t="n">
-        <v>106.818</v>
+        <v>138.36</v>
       </c>
       <c r="J4" t="n">
-        <v>60.149</v>
+        <v>55.879</v>
       </c>
       <c r="K4" t="n">
-        <v>37.553</v>
+        <v>32.049</v>
       </c>
       <c r="L4" t="n">
-        <v>29.783</v>
+        <v>29.765</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88513</v>
+        <v>3428761</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2877,55 +4001,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jacob Ingram</t>
+          <t>Martin Coffey</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>193.584</v>
+        <v>173.368</v>
       </c>
       <c r="I5" t="n">
-        <v>107.829</v>
+        <v>108.108</v>
       </c>
       <c r="J5" t="n">
-        <v>60.253</v>
+        <v>55.964</v>
       </c>
       <c r="K5" t="n">
-        <v>38.034</v>
+        <v>32.659</v>
       </c>
       <c r="L5" t="n">
-        <v>28.598</v>
+        <v>28.949</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2213032</v>
+        <v>113282</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2939,51 +4063,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Ray McCaughey TNP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>193.549</v>
+        <v>193.128</v>
       </c>
       <c r="I6" t="n">
-        <v>110.302</v>
+        <v>106.593</v>
       </c>
       <c r="J6" t="n">
-        <v>59.998</v>
+        <v>61.638</v>
       </c>
       <c r="K6" t="n">
-        <v>38.335</v>
+        <v>38.788</v>
       </c>
       <c r="L6" t="n">
-        <v>33.094</v>
+        <v>28.714</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4980720</v>
+        <v>88513</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2992,39 +4120,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>Jacob Ingram</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>193.6</v>
+        <v>193.584</v>
       </c>
       <c r="I7" t="n">
-        <v>107.826</v>
+        <v>107.829</v>
       </c>
       <c r="J7" t="n">
-        <v>61.543</v>
+        <v>60.253</v>
       </c>
       <c r="K7" t="n">
-        <v>38.672</v>
+        <v>38.034</v>
       </c>
       <c r="L7" t="n">
-        <v>29.695</v>
+        <v>28.598</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -3033,19 +4161,19 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>394612</v>
+        <v>374410</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -3054,60 +4182,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t xml:space="preserve">Tom R Everested </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>198.478</v>
+        <v>192.992</v>
       </c>
       <c r="I8" t="n">
-        <v>128.345</v>
+        <v>106.718</v>
       </c>
       <c r="J8" t="n">
-        <v>71.063</v>
+        <v>59.757</v>
       </c>
       <c r="K8" t="n">
-        <v>37.19</v>
+        <v>37.398</v>
       </c>
       <c r="L8" t="n">
-        <v>39.72</v>
+        <v>29.558</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>5</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>679077</v>
+        <v>1377319</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -3116,39 +4244,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Akira  CafeLatte</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>193.604</v>
+        <v>173.823</v>
       </c>
       <c r="I9" t="n">
-        <v>108.037</v>
+        <v>109.012</v>
       </c>
       <c r="J9" t="n">
-        <v>60.402</v>
+        <v>57.701</v>
       </c>
       <c r="K9" t="n">
-        <v>38.362</v>
+        <v>33.646</v>
       </c>
       <c r="L9" t="n">
-        <v>30.082</v>
+        <v>30.723</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -3160,144 +4284,140 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4879864</v>
+        <v>5402095</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jorelle  Hernandez (TZP)</t>
+          <t>Quentin Vee [EVO]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TZP</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>227.558</v>
+        <v>193.416</v>
       </c>
       <c r="I10" t="n">
-        <v>124.058</v>
+        <v>106.818</v>
       </c>
       <c r="J10" t="n">
-        <v>63.463</v>
+        <v>60.149</v>
       </c>
       <c r="K10" t="n">
-        <v>42.216</v>
+        <v>37.553</v>
       </c>
       <c r="L10" t="n">
-        <v>37.799</v>
+        <v>29.783</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1005102</v>
+        <v>5977246</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Mike Leahy</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>225.194</v>
+        <v>173.883</v>
       </c>
       <c r="I11" t="n">
-        <v>126.855</v>
+        <v>109.76</v>
       </c>
       <c r="J11" t="n">
-        <v>63.616</v>
+        <v>56.164</v>
       </c>
       <c r="K11" t="n">
-        <v>41.705</v>
+        <v>33.27</v>
       </c>
       <c r="L11" t="n">
-        <v>35.459</v>
+        <v>30.996</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2988740</v>
+        <v>5959135</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3307,121 +4427,121 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>226.68</v>
+        <v>174.55</v>
       </c>
       <c r="I12" t="n">
-        <v>126.518</v>
+        <v>108.914</v>
       </c>
       <c r="J12" t="n">
-        <v>63.528</v>
+        <v>56.383</v>
       </c>
       <c r="K12" t="n">
-        <v>42.808</v>
+        <v>33.127</v>
       </c>
       <c r="L12" t="n">
-        <v>43.408</v>
+        <v>29.427</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>260262</v>
+        <v>4980720</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>274.151</v>
+        <v>193.6</v>
       </c>
       <c r="I13" t="n">
-        <v>148.706</v>
+        <v>107.826</v>
       </c>
       <c r="J13" t="n">
-        <v>74.503</v>
+        <v>61.543</v>
       </c>
       <c r="K13" t="n">
-        <v>35.732</v>
+        <v>38.672</v>
       </c>
       <c r="L13" t="n">
-        <v>32.012</v>
+        <v>29.695</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2959735</v>
+        <v>5428334</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3431,92 +4551,96 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+          <t>Andr&amp;eacute;  Jones (A-P-V)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>235.395</v>
+        <v>174.139</v>
       </c>
       <c r="I14" t="n">
-        <v>129.405</v>
+        <v>108.928</v>
       </c>
       <c r="J14" t="n">
-        <v>63.742</v>
+        <v>56.198</v>
       </c>
       <c r="K14" t="n">
-        <v>42.304</v>
+        <v>33.553</v>
       </c>
       <c r="L14" t="n">
-        <v>35.006</v>
+        <v>29.671</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4166463</v>
+        <v>679077</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Den Morrison</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>235.73</v>
+        <v>193.604</v>
       </c>
       <c r="I15" t="n">
-        <v>130.272</v>
+        <v>108.037</v>
       </c>
       <c r="J15" t="n">
-        <v>64.881</v>
+        <v>60.402</v>
       </c>
       <c r="K15" t="n">
-        <v>42.775</v>
+        <v>38.362</v>
       </c>
       <c r="L15" t="n">
-        <v>34.856</v>
+        <v>30.082</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -3525,60 +4649,56 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1236596</v>
+        <v>2213032</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>242.218</v>
+        <v>193.549</v>
       </c>
       <c r="I16" t="n">
-        <v>164.746</v>
+        <v>110.302</v>
       </c>
       <c r="J16" t="n">
-        <v>64.21599999999999</v>
+        <v>59.998</v>
       </c>
       <c r="K16" t="n">
-        <v>42.72</v>
+        <v>38.335</v>
       </c>
       <c r="L16" t="n">
-        <v>38.45</v>
+        <v>33.094</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3590,122 +4710,122 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>288798</v>
+        <v>1070115</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t xml:space="preserve">Garth Haigh </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>226.557</v>
+        <v>175.064</v>
       </c>
       <c r="I17" t="n">
-        <v>127.569</v>
+        <v>131.156</v>
       </c>
       <c r="J17" t="n">
-        <v>64.402</v>
+        <v>71.27800000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>42.09</v>
+        <v>33.756</v>
       </c>
       <c r="L17" t="n">
-        <v>35.419</v>
+        <v>39.52</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>25</v>
+        <v>394612</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>246.415</v>
+        <v>198.478</v>
       </c>
       <c r="I18" t="n">
-        <v>143.226</v>
+        <v>128.345</v>
       </c>
       <c r="J18" t="n">
-        <v>63.67</v>
+        <v>71.063</v>
       </c>
       <c r="K18" t="n">
-        <v>42.136</v>
+        <v>37.19</v>
       </c>
       <c r="L18" t="n">
-        <v>44.269</v>
+        <v>39.72</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3714,144 +4834,144 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7779078</v>
+        <v>6730421</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Abdullah Ak&amp;ccedil;am</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Zwift TURKIYE</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>269.648</v>
+        <v>228.585</v>
       </c>
       <c r="I19" t="n">
-        <v>147.455</v>
+        <v>135.232</v>
       </c>
       <c r="J19" t="n">
-        <v>75.449</v>
+        <v>67.268</v>
       </c>
       <c r="K19" t="n">
-        <v>36.355</v>
+        <v>46.465</v>
       </c>
       <c r="L19" t="n">
-        <v>35.063</v>
+        <v>36.553</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2297188</v>
+        <v>4879864</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Javier (HERC) </t>
+          <t>Jorelle  Hernandez (TZP)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>247.428</v>
+        <v>227.558</v>
       </c>
       <c r="I20" t="n">
-        <v>140.483</v>
+        <v>124.058</v>
       </c>
       <c r="J20" t="n">
-        <v>68.947</v>
+        <v>63.463</v>
       </c>
       <c r="K20" t="n">
-        <v>40.29</v>
+        <v>42.216</v>
       </c>
       <c r="L20" t="n">
-        <v>39.053</v>
+        <v>37.799</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>368568</v>
+        <v>1005102</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3861,477 +4981,1457 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>239.216</v>
+        <v>225.194</v>
       </c>
       <c r="I21" t="n">
-        <v>147.682</v>
+        <v>126.855</v>
       </c>
       <c r="J21" t="n">
-        <v>64.077</v>
+        <v>63.616</v>
       </c>
       <c r="K21" t="n">
-        <v>42.797</v>
+        <v>41.705</v>
       </c>
       <c r="L21" t="n">
-        <v>39.839</v>
+        <v>35.459</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1379058</v>
+        <v>2988740</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>273.644</v>
+        <v>226.68</v>
       </c>
       <c r="I22" t="n">
-        <v>147.985</v>
+        <v>126.518</v>
       </c>
       <c r="J22" t="n">
-        <v>67.021</v>
+        <v>63.528</v>
       </c>
       <c r="K22" t="n">
-        <v>36.63</v>
+        <v>42.808</v>
       </c>
       <c r="L22" t="n">
-        <v>31.796</v>
+        <v>43.408</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>832585</v>
+        <v>7166418</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Andrew Stamp(RollCo)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>273.7</v>
+        <v>233.433</v>
       </c>
       <c r="I23" t="n">
-        <v>149.223</v>
+        <v>133.828</v>
       </c>
       <c r="J23" t="n">
-        <v>74.93899999999999</v>
+        <v>69.43300000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>43.439</v>
+        <v>34.726</v>
       </c>
       <c r="L23" t="n">
-        <v>39.652</v>
+        <v>35.266</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5689173</v>
+        <v>2959735</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HISP</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>298.739</v>
+        <v>235.395</v>
       </c>
       <c r="I24" t="n">
-        <v>163.784</v>
+        <v>129.405</v>
       </c>
       <c r="J24" t="n">
-        <v>75.95999999999999</v>
+        <v>63.742</v>
       </c>
       <c r="K24" t="n">
-        <v>45.996</v>
+        <v>42.304</v>
       </c>
       <c r="L24" t="n">
-        <v>39.405</v>
+        <v>35.006</v>
       </c>
       <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" t="n">
         <v>5</v>
       </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>687504</v>
+        <v>4166463</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
+          <t>Corey Green (YT) GarageCycling</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>314.151</v>
+        <v>235.73</v>
       </c>
       <c r="I25" t="n">
-        <v>176.166</v>
+        <v>130.272</v>
       </c>
       <c r="J25" t="n">
-        <v>84.69799999999999</v>
+        <v>64.881</v>
       </c>
       <c r="K25" t="n">
-        <v>50.031</v>
+        <v>42.775</v>
       </c>
       <c r="L25" t="n">
-        <v>58.468</v>
+        <v>34.856</v>
       </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>3</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>426099</v>
+        <v>260262</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>@ arrows</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Greg SHED</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>300.562</v>
+        <v>274.151</v>
       </c>
       <c r="I26" t="n">
-        <v>189.988</v>
+        <v>148.706</v>
       </c>
       <c r="J26" t="n">
-        <v>86.953</v>
+        <v>74.503</v>
       </c>
       <c r="K26" t="n">
-        <v>48.368</v>
+        <v>35.732</v>
       </c>
       <c r="L26" t="n">
-        <v>46.632</v>
+        <v>32.012</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3294901</v>
+        <v>5277640</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Phil Cox (TNP)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>352.066</v>
+        <v>248.833</v>
       </c>
       <c r="I27" t="n">
-        <v>180.835</v>
+        <v>142.675</v>
       </c>
       <c r="J27" t="n">
-        <v>87.05</v>
+        <v>81.56</v>
       </c>
       <c r="K27" t="n">
-        <v>51.897</v>
+        <v>52.784</v>
       </c>
       <c r="L27" t="n">
-        <v>40.523</v>
+        <v>44.519</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>1236596</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Neil Rogers</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>242.218</v>
+      </c>
+      <c r="I28" t="n">
+        <v>164.746</v>
+      </c>
+      <c r="J28" t="n">
+        <v>64.21599999999999</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="L28" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>288798</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Scott Henderson (BON - GXY)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>24</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>226.557</v>
+      </c>
+      <c r="I29" t="n">
+        <v>127.569</v>
+      </c>
+      <c r="J29" t="n">
+        <v>64.402</v>
+      </c>
+      <c r="K29" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="L29" t="n">
+        <v>35.419</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9152</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Simon Baker</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>248.257</v>
+      </c>
+      <c r="I30" t="n">
+        <v>137.214</v>
+      </c>
+      <c r="J30" t="n">
+        <v>68.46599999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>45.483</v>
+      </c>
+      <c r="L30" t="n">
+        <v>30.864</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7229860</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>230.314</v>
+      </c>
+      <c r="I31" t="n">
+        <v>137.22</v>
+      </c>
+      <c r="J31" t="n">
+        <v>66.628</v>
+      </c>
+      <c r="K31" t="n">
+        <v>44.928</v>
+      </c>
+      <c r="L31" t="n">
+        <v>37.139</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>13</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>246.415</v>
+      </c>
+      <c r="I32" t="n">
+        <v>143.226</v>
+      </c>
+      <c r="J32" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="K32" t="n">
+        <v>42.136</v>
+      </c>
+      <c r="L32" t="n">
+        <v>44.269</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2297188</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Javier (HERC) </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>11</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>247.428</v>
+      </c>
+      <c r="I33" t="n">
+        <v>140.483</v>
+      </c>
+      <c r="J33" t="n">
+        <v>68.947</v>
+      </c>
+      <c r="K33" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="L33" t="n">
+        <v>39.053</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>368568</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>239.216</v>
+      </c>
+      <c r="I34" t="n">
+        <v>147.682</v>
+      </c>
+      <c r="J34" t="n">
+        <v>64.077</v>
+      </c>
+      <c r="K34" t="n">
+        <v>42.797</v>
+      </c>
+      <c r="L34" t="n">
+        <v>39.839</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7779078</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>269.648</v>
+      </c>
+      <c r="I35" t="n">
+        <v>147.455</v>
+      </c>
+      <c r="J35" t="n">
+        <v>75.449</v>
+      </c>
+      <c r="K35" t="n">
+        <v>36.355</v>
+      </c>
+      <c r="L35" t="n">
+        <v>35.063</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6786487</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Roberto Delgado Hynes</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>249.913</v>
+      </c>
+      <c r="I36" t="n">
+        <v>141.503</v>
+      </c>
+      <c r="J36" t="n">
+        <v>71.661</v>
+      </c>
+      <c r="K36" t="n">
+        <v>46.129</v>
+      </c>
+      <c r="L36" t="n">
+        <v>40.597</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1379058</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>david white (HERC)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>273.644</v>
+      </c>
+      <c r="I37" t="n">
+        <v>147.985</v>
+      </c>
+      <c r="J37" t="n">
+        <v>67.021</v>
+      </c>
+      <c r="K37" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31.796</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>832585</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>149.223</v>
+      </c>
+      <c r="J38" t="n">
+        <v>74.93899999999999</v>
+      </c>
+      <c r="K38" t="n">
+        <v>43.439</v>
+      </c>
+      <c r="L38" t="n">
+        <v>39.652</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1087000</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Evan  Carouchio</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>302.033</v>
+      </c>
+      <c r="I39" t="n">
+        <v>159.815</v>
+      </c>
+      <c r="J39" t="n">
+        <v>78.913</v>
+      </c>
+      <c r="K39" t="n">
+        <v>46.749</v>
+      </c>
+      <c r="L39" t="n">
+        <v>42.283</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5689173</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Kim Bryan &amp;#127800;</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>35</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>298.739</v>
+      </c>
+      <c r="I40" t="n">
+        <v>163.784</v>
+      </c>
+      <c r="J40" t="n">
+        <v>75.95999999999999</v>
+      </c>
+      <c r="K40" t="n">
+        <v>45.996</v>
+      </c>
+      <c r="L40" t="n">
+        <v>39.405</v>
+      </c>
+      <c r="M40" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>10</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>687504</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Matt Jones</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>19</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>314.151</v>
+      </c>
+      <c r="I41" t="n">
+        <v>176.166</v>
+      </c>
+      <c r="J41" t="n">
+        <v>84.69799999999999</v>
+      </c>
+      <c r="K41" t="n">
+        <v>50.031</v>
+      </c>
+      <c r="L41" t="n">
+        <v>58.468</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>426099</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>19</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>300.562</v>
+      </c>
+      <c r="I42" t="n">
+        <v>189.988</v>
+      </c>
+      <c r="J42" t="n">
+        <v>86.953</v>
+      </c>
+      <c r="K42" t="n">
+        <v>48.368</v>
+      </c>
+      <c r="L42" t="n">
+        <v>46.632</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>8</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>352.066</v>
+      </c>
+      <c r="I43" t="n">
+        <v>180.835</v>
+      </c>
+      <c r="J43" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="K43" t="n">
+        <v>51.897</v>
+      </c>
+      <c r="L43" t="n">
+        <v>40.523</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>281429</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>[GALAXY]</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F44" t="n">
         <v>11</v>
       </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
         <v>390.08</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I44" t="n">
         <v>227.753</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J44" t="n">
         <v>103.453</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K44" t="n">
         <v>47.626</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L44" t="n">
         <v>62.116</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>3</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q44" t="n">
         <v>4</v>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4344,7 +6444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4391,21 +6491,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4980720</v>
+        <v>6863000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33:46.947</t>
+          <t>31:57.682</t>
         </is>
       </c>
     </row>
@@ -4417,25 +6517,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88513</v>
+        <v>7250325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jacob Ingram</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>Brandon Quinton</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33:56.989</t>
+          <t>32:31.802</t>
         </is>
       </c>
     </row>
@@ -4451,21 +6547,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5402095</v>
+        <v>4860176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Mads Buster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33:57.106</t>
+          <t>33:00.660</t>
         </is>
       </c>
     </row>
@@ -4477,25 +6573,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>374410</v>
+        <v>5428334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tom R Everested </t>
+          <t>Andr&amp;eacute;  Jones (A-P-V)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33:57.310</t>
+          <t>33:01.374</t>
         </is>
       </c>
     </row>
@@ -4507,25 +6603,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>679077</v>
+        <v>1377319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Akira  CafeLatte</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33:57.721</t>
+          <t>33:01.392</t>
         </is>
       </c>
     </row>
@@ -4537,25 +6629,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>113282</v>
+        <v>3428761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ray McCaughey TNP</t>
+          <t>Martin Coffey</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33:58.293</t>
+          <t>33:01.766</t>
         </is>
       </c>
     </row>
@@ -4567,21 +6659,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2213032</v>
+        <v>5977246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
+          <t>Mike Leahy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34:04.668</t>
+          <t>33:02.469</t>
         </is>
       </c>
     </row>
@@ -4597,144 +6689,148 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>394612</v>
+        <v>5959135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36:39.066</t>
+          <t>33:09.857</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4879864</v>
+        <v>4980720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jorelle  Hernandez (TZP)</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TZP</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37:14.815</t>
+          <t>33:46.947</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2988740</v>
+        <v>88513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Jacob Ingram</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37:41.896</t>
+          <t>33:56.989</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4166463</v>
+        <v>5402095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Quentin Vee [EVO]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38:01.970</t>
+          <t>33:57.106</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1005102</v>
+        <v>374410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t xml:space="preserve">Tom R Everested </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38:07.386</t>
+          <t>33:57.310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4743,148 +6839,144 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2959735</v>
+        <v>679077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+          <t>Den Morrison</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38:09.320</t>
+          <t>33:57.721</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1236596</v>
+        <v>113282</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
+          <t>Ray McCaughey TNP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39:15.657</t>
+          <t>33:58.293</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>260262</v>
+        <v>2213032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41:03.174</t>
+          <t>34:04.668</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>288798</v>
+        <v>1070115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t xml:space="preserve">Garth Haigh </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:38.215</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>394612</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38:36.864</t>
+          <t>36:39.066</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4893,118 +6985,118 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>368568</v>
+        <v>6730421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Abdullah Ak&amp;ccedil;am</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Zwift TURKIYE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>37:50.496</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2297188</v>
+        <v>7166418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Javier (HERC) </t>
+          <t>Andrew Stamp(RollCo)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39:21.436</t>
+          <t>36:51.881</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7779078</v>
+        <v>4879864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Jorelle  Hernandez (TZP)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41:02.969</t>
+          <t>37:14.815</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1379058</v>
+        <v>2988740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41:03.656</t>
+          <t>37:41.896</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5013,161 +7105,629 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>832585</v>
+        <v>4166463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vonita</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41:05.154</t>
+          <t>38:01.970</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>687504</v>
+        <v>1005102</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>38:07.386</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>426099</v>
+        <v>2959735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>@ arrows</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>38:09.320</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3294901</v>
+        <v>1236596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Neil Rogers</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>39:15.657</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5689173</v>
+        <v>260262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>41:03.174</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5277640</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Phil Cox (TNP)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>42:47.362</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7229860</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>38:03.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>288798</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Scott Henderson (BON - GXY)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>38:06.428</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>38:36.864</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>368568</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>38:58.416</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2297188</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Javier (HERC) </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>39:21.436</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9152</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Simon Baker</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>39:22.574</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6786487</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Roberto Delgado Hynes</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>39:46.669</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7779078</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>41:02.969</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1379058</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>david white (HERC)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>41:03.656</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>832585</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>41:05.154</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1087000</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Evan  Carouchio</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>41:55.814</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>687504</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Matt Jones</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>44:04.011</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>426099</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>45:16.878</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>45:22.447</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5689173</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kim Bryan &amp;#127800;</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>45:41.917</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
         <v>281429</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>[GALAXY]</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>51:44.021</t>
         </is>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -3663,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3689,7 +3689,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>races</t>
+          <t>racers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>racers1</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3711,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01:39:19.783</t>
+          <t>31:57.682</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3715,6 +3725,14 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31:57.682</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3726,20 +3744,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01:40:23.926</t>
+          <t>33:00.660</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01:04.143</t>
+          <t>01:02.978</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33:00.660</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3751,146 +3777,1415 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>HEXAGONE.CC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01:44:33.161</t>
+          <t>33:17.955</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05:13.378</t>
+          <t>01:20.273</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>33:17.955</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01:50:55.878</t>
+          <t>33:21.271</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:23.589</t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>33:21.271</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01:51:04.193</t>
+          <t>33:22.401</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08.315</t>
+          <t>01:24.719</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>33:22.401</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Njinga Cycling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01:57:16.061</t>
+          <t>33:23.872</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:20.183</t>
+          <t>01:26.190</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>33:23.872</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01:57:37.668</t>
+          <t>33:24.482</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:26.800</t>
         </is>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>33:24.482</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>VenTech</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>33:45.002</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>01:47.320</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>33:45.002</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>33:46.947</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>01:49.265</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>33:46.947</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BIKELY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>33:57.310</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>01:59.628</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33:57.310</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>33:57.721</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>02:00.039</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>33:57.721</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>34:53.668</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>02:55.986</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>34:53.668</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ZSUNR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>35:38.215</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>03:40.533</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>35:38.215</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zwift TURKIYE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>37:50.496</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>05:52.814</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>37:50.496</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01:08:53.692</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>36:56.010</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>01:08:53.692</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ATGNI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01:15:34.745</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>43:37.063</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>01:15:34.745</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A-P-V</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01:39:19.783</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>01:07:22.101</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>01:39:19.783</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01:40:23.926</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>01:08:26.244</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>01:40:23.926</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01:44:33.161</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>01:12:35.479</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>01:44:33.161</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Team CLS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>35:55.766</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>35:55.766</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DZR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>36:22.857</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>27.091</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>36:22.857</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TZP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>37:14.815</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>01:19.049</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>37:14.815</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HERD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>37:22.000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>01:26.234</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>37:22.000</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S R T</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>37:39.450</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>01:43.684</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>37:39.450</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>37:41.896</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>01:46.130</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>37:41.896</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>38:05.091</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>02:09.325</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>38:05.091</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>38:09.320</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>02:13.554</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>38:09.320</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>39:15.657</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>03:19.891</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>39:15.657</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>01:15:36.260</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>39:40.494</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>01:15:36.260</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>01:50:55.878</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>01:15:00.112</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>01:50:55.878</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>01:51:04.193</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>01:15:08.427</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>01:51:04.193</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>HERC</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>01:57:16.061</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>01:21:20.295</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>01:57:16.061</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>35:10.925</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>35:10.925</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S R T</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>38:04.051</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>02:53.126</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>38:04.051</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>38:06.428</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>02:55.503</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>38:06.428</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>38:58.416</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>03:47.491</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>38:58.416</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>39:16.112</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>04:05.187</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>39:16.112</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TBG</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>41:26.901</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>06:15.976</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>41:26.901</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CTT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>44:34.144</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09:23.219</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>44:34.144</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>01:57:37.668</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>01:22:26.743</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>01:57:37.668</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>01:59:01.269</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>01:23.601</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>01:23:50.344</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>01:59:01.269</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>41:36.187</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>41:36.187</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>45:22.447</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>03:46.260</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>45:22.447</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DBM</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>48:08.706</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>06:32.519</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48:08.706</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>01:37:25.938</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>55:49.751</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>01:37:25.938</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -3711,12 +3711,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WEz pb Cycling District</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31:57.682</t>
+          <t>01:39:19.783</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3725,15 +3725,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31:57.682</t>
+          <t>01:39:19.783</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3744,29 +3744,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33:00.660</t>
+          <t>01:40:23.926</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01:02.978</t>
+          <t>01:04.143</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33:00.660</t>
+          <t>01:40:23.926</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3777,29 +3777,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HEXAGONE.CC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33:17.955</t>
+          <t>01:44:33.161</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>01:20.273</t>
+          <t>05:13.378</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33:17.955</t>
+          <t>01:44:33.161</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33:21.271</t>
+          <t>01:08:53.692</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:23.589</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33:21.271</t>
+          <t>01:08:53.692</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3843,29 +3843,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33:22.401</t>
+          <t>01:15:34.745</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01:24.719</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33:22.401</t>
+          <t>01:15:34.745</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Njinga Cycling</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33:23.872</t>
+          <t>31:57.682</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01:26.190</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33:23.872</t>
+          <t>31:57.682</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3909,17 +3909,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>33:24.482</t>
+          <t>33:00.660</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>01:26.800</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33:24.482</t>
+          <t>33:00.660</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3942,17 +3942,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VenTech</t>
+          <t>HEXAGONE.CC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33:45.002</t>
+          <t>33:17.955</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>01:47.320</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33:45.002</t>
+          <t>33:17.955</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3975,17 +3975,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33:46.947</t>
+          <t>33:21.271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01:49.265</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33:46.947</t>
+          <t>33:21.271</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33:57.310</t>
+          <t>33:22.401</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>01:59.628</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33:57.310</t>
+          <t>33:22.401</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Njinga Cycling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>33:57.721</t>
+          <t>33:23.872</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>02:00.039</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33:57.721</t>
+          <t>33:23.872</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>34:53.668</t>
+          <t>33:24.482</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>02:55.986</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>34:53.668</t>
+          <t>33:24.482</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>VenTech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>35:38.215</t>
+          <t>33:45.002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>03:40.533</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35:38.215</t>
+          <t>33:45.002</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zwift TURKIYE</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>37:50.496</t>
+          <t>33:46.947</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05:52.814</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37:50.496</t>
+          <t>33:46.947</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4173,17 +4173,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01:08:53.692</t>
+          <t>33:57.310</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>36:56.010</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4191,11 +4191,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01:08:53.692</t>
+          <t>33:57.310</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4206,17 +4206,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATGNI</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01:15:34.745</t>
+          <t>33:57.721</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43:37.063</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -4224,11 +4224,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01:15:34.745</t>
+          <t>33:57.721</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01:39:19.783</t>
+          <t>34:53.668</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01:07:22.101</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4257,11 +4257,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01:39:19.783</t>
+          <t>34:53.668</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4272,17 +4272,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01:40:23.926</t>
+          <t>35:38.215</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01:08:26.244</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>01:40:23.926</t>
+          <t>35:38.215</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4305,17 +4305,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Zwift TURKIYE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01:44:33.161</t>
+          <t>37:50.496</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01:12:35.479</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -4323,11 +4323,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01:44:33.161</t>
+          <t>37:50.496</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team CLS</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>35:55.766</t>
+          <t>01:50:55.878</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4352,15 +4352,15 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>35:55.766</t>
+          <t>01:50:55.878</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4371,29 +4371,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>36:22.857</t>
+          <t>01:51:04.193</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27.091</t>
+          <t>08.315</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36:22.857</t>
+          <t>01:51:04.193</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4404,29 +4404,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TZP</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>37:14.815</t>
+          <t>01:57:16.061</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>01:19.049</t>
+          <t>06:20.183</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>37:14.815</t>
+          <t>01:57:16.061</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4437,29 +4437,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HERD</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>37:22.000</t>
+          <t>01:15:36.260</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01:26.234</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>37:22.000</t>
+          <t>01:15:36.260</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4470,17 +4470,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>37:39.450</t>
+          <t>35:55.766</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01:43.684</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>37:39.450</t>
+          <t>35:55.766</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4503,17 +4503,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>37:41.896</t>
+          <t>36:22.857</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>01:46.130</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>37:41.896</t>
+          <t>36:22.857</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>38:05.091</t>
+          <t>37:14.815</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02:09.325</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>38:05.091</t>
+          <t>37:14.815</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>38:09.320</t>
+          <t>37:22.000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02:13.554</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>38:09.320</t>
+          <t>37:22.000</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4602,17 +4602,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>39:15.657</t>
+          <t>37:39.450</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>03:19.891</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>39:15.657</t>
+          <t>37:39.450</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01:15:36.260</t>
+          <t>37:41.896</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>39:40.494</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4653,11 +4653,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01:15:36.260</t>
+          <t>37:41.896</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4668,17 +4668,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01:50:55.878</t>
+          <t>38:05.091</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>01:15:00.112</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4686,11 +4686,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01:50:55.878</t>
+          <t>38:05.091</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>HISP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01:51:04.193</t>
+          <t>38:09.320</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>01:15:08.427</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4719,11 +4719,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01:51:04.193</t>
+          <t>38:09.320</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01:57:16.061</t>
+          <t>39:15.657</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01:21:20.295</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01:57:16.061</t>
+          <t>39:15.657</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>01:57:37.668</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4781,15 +4781,15 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>01:57:37.668</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -4800,29 +4800,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>38:04.051</t>
+          <t>01:59:01.269</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>02:53.126</t>
+          <t>01:23.601</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>38:04.051</t>
+          <t>01:59:01.269</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>02:55.503</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:04.051</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>03:47.491</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:04.051</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4899,17 +4899,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>38:06.428</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>04:05.187</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>38:06.428</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4932,17 +4932,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TBG</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06:15.976</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CTT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>09:23.219</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>TBG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01:57:37.668</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>01:22:26.743</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5016,11 +5016,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>01:57:37.668</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>CTT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01:59:01.269</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>01:23:50.344</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5049,11 +5049,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01:59:01.269</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>41:36.187</t>
+          <t>01:37:25.938</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5078,15 +5078,15 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>41:36.187</t>
+          <t>01:37:25.938</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>41:36.187</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>03:46.260</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>41:36.187</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5130,17 +5130,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:22.447</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>06:32.519</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:22.447</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01:37:25.938</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>55:49.751</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5181,11 +5181,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01:37:25.938</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4935,23 +4935,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
+          <t>Jason Spiker (DDIRC)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>43:32.716</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>02:27.824</t>
+          <t>01:56.529</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4971,22 +4971,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Matt Jones</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>44:09.197</t>
+          <t>44:04.011</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>02:33.010</t>
+          <t>02:27.824</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -5006,18 +5002,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>45:14.312</t>
+          <t>44:09.197</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>03:38.125</t>
+          <t>02:33.010</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -5037,18 +5037,18 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>@ arrows</t>
+          <t>Philip Gill</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>45:14.312</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>03:40.691</t>
+          <t>03:38.125</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -5068,22 +5068,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>45:16.878</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>03:46.260</t>
+          <t>03:40.691</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -5103,22 +5099,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>45:22.447</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>04:05.730</t>
+          <t>03:46.260</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -5133,27 +5129,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rikke Rasmussen #DBM#</t>
+          <t>Kim Bryan &amp;#127800;</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:41.917</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>06:32.519</t>
+          <t>04:05.730</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -5168,27 +5164,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
+          <t>Rikke Rasmussen #DBM#</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>08:24.763</t>
+          <t>06:32.519</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -5203,27 +5199,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+          <t>Mailan Kimsuan [ZIRT]</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>51:44.021</t>
+          <t>50:00.950</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>10:07.834</t>
+          <t>08:24.763</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -5233,31 +5229,132 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Adrian ZC</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Momentum CR</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>51:07.527</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>09:31.340</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>51:44.021</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>10:07.834</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Leslie Koh</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>51:08.233</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Stuart Haigh</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
         <is>
           <t>58:30.748</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>07:22.515</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5272,7 +5369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7652,6 +7749,39 @@
         </is>
       </c>
       <c r="G72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Momentum CR</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>51:07.527</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>51:07.527</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7666,7 +7796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12825,7 +12955,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2505328</v>
+        <v>6478454</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -12834,19 +12964,15 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
-        </is>
-      </c>
+          <t>Jason Spiker (DDIRC)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>6</v>
       </c>
@@ -12854,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>18.47</v>
+        <v>17.882</v>
       </c>
       <c r="I139" t="n">
         <v>6</v>
@@ -12863,7 +12989,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>7963870</v>
+        <v>2505328</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -12877,10 +13003,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>Mailan Kimsuan [ZIRT]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+        </is>
+      </c>
       <c r="F140" t="n">
         <v>5</v>
       </c>
@@ -12888,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>18.676</v>
+        <v>18.47</v>
       </c>
       <c r="I140" t="n">
         <v>5</v>
@@ -12897,11 +13027,11 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1500543</v>
+        <v>7963870</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -12911,23 +13041,129 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Stuart Haigh</t>
+          <t>Philip Gill</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
+        <v>4</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>18.676</v>
+      </c>
+      <c r="I141" t="n">
+        <v>4</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>5805064</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Adrian ZC</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Momentum CR</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>3</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="I142" t="n">
+        <v>3</v>
+      </c>
+      <c r="J142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4175869</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Leslie Koh</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
         <v>20</v>
       </c>
-      <c r="G141" t="n">
-        <v>1</v>
-      </c>
-      <c r="H141" t="n">
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>19.592</v>
+      </c>
+      <c r="I143" t="n">
+        <v>20</v>
+      </c>
+      <c r="J143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1500543</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Stuart Haigh</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>18</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
         <v>20.384</v>
       </c>
-      <c r="I141" t="n">
-        <v>20</v>
-      </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>18</v>
+      </c>
+      <c r="J144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12940,7 +13176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R141"/>
+  <dimension ref="A1:R144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20900,7 +21136,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -20930,7 +21166,7 @@
         <v>2</v>
       </c>
       <c r="P130" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q130" t="n">
         <v>10</v>
@@ -20962,7 +21198,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -20992,10 +21228,10 @@
         <v>5</v>
       </c>
       <c r="P131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R131" t="inlineStr"/>
     </row>
@@ -21024,7 +21260,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -21057,13 +21293,13 @@
         <v>10</v>
       </c>
       <c r="Q132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3228186</v>
+        <v>6478454</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -21072,60 +21308,56 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Jason Spiker (DDIRC)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>284.211</v>
+        <v>288.066</v>
       </c>
       <c r="I133" t="n">
-        <v>184.83</v>
+        <v>156.47</v>
       </c>
       <c r="J133" t="n">
-        <v>72.991</v>
+        <v>78.224</v>
       </c>
       <c r="K133" t="n">
-        <v>45.406</v>
+        <v>49.941</v>
       </c>
       <c r="L133" t="n">
-        <v>53.454</v>
+        <v>43.596</v>
       </c>
       <c r="M133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q133" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>7963870</v>
+        <v>3228186</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -21139,51 +21371,55 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F134" t="n">
+        <v>14</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>284.211</v>
+      </c>
+      <c r="I134" t="n">
+        <v>184.83</v>
+      </c>
+      <c r="J134" t="n">
+        <v>72.991</v>
+      </c>
+      <c r="K134" t="n">
+        <v>45.406</v>
+      </c>
+      <c r="L134" t="n">
+        <v>53.454</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>8</v>
-      </c>
-      <c r="G134" t="n">
-        <v>1</v>
-      </c>
-      <c r="H134" t="n">
-        <v>300.634</v>
-      </c>
-      <c r="I134" t="n">
-        <v>166.903</v>
-      </c>
-      <c r="J134" t="n">
-        <v>81.55500000000001</v>
-      </c>
-      <c r="K134" t="n">
-        <v>57.624</v>
-      </c>
-      <c r="L134" t="n">
-        <v>51.249</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>3</v>
       </c>
       <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>687504</v>
+        <v>7963870</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -21197,7 +21433,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
+          <t>Philip Gill</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -21208,19 +21444,19 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>314.151</v>
+        <v>300.634</v>
       </c>
       <c r="I135" t="n">
-        <v>176.166</v>
+        <v>166.903</v>
       </c>
       <c r="J135" t="n">
-        <v>84.69799999999999</v>
+        <v>81.55500000000001</v>
       </c>
       <c r="K135" t="n">
-        <v>50.031</v>
+        <v>57.624</v>
       </c>
       <c r="L135" t="n">
-        <v>58.468</v>
+        <v>51.249</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -21264,7 +21500,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -21294,7 +21530,7 @@
         <v>3</v>
       </c>
       <c r="P136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
@@ -21303,7 +21539,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>426099</v>
+        <v>687504</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -21317,7 +21553,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>@ arrows</t>
+          <t>Matt Jones</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -21328,19 +21564,19 @@
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>300.562</v>
+        <v>314.151</v>
       </c>
       <c r="I137" t="n">
-        <v>189.988</v>
+        <v>176.166</v>
       </c>
       <c r="J137" t="n">
-        <v>86.953</v>
+        <v>84.69799999999999</v>
       </c>
       <c r="K137" t="n">
-        <v>48.368</v>
+        <v>50.031</v>
       </c>
       <c r="L137" t="n">
-        <v>46.632</v>
+        <v>58.468</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -21352,16 +21588,16 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2505328</v>
+        <v>426099</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -21375,14 +21611,10 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
-        </is>
-      </c>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>3</v>
       </c>
@@ -21390,19 +21622,19 @@
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>336.616</v>
+        <v>300.562</v>
       </c>
       <c r="I138" t="n">
-        <v>183.217</v>
+        <v>189.988</v>
       </c>
       <c r="J138" t="n">
-        <v>103.825</v>
+        <v>86.953</v>
       </c>
       <c r="K138" t="n">
-        <v>64.23999999999999</v>
+        <v>48.368</v>
       </c>
       <c r="L138" t="n">
-        <v>53.63</v>
+        <v>46.632</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -21414,16 +21646,16 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>281429</v>
+        <v>2505328</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -21432,17 +21664,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+          <t>Mailan Kimsuan [ZIRT]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -21452,31 +21684,31 @@
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>390.08</v>
+        <v>336.616</v>
       </c>
       <c r="I139" t="n">
-        <v>227.753</v>
+        <v>183.217</v>
       </c>
       <c r="J139" t="n">
-        <v>103.453</v>
+        <v>103.825</v>
       </c>
       <c r="K139" t="n">
-        <v>47.626</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="L139" t="n">
-        <v>62.116</v>
+        <v>53.63</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -21485,7 +21717,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>5302599</v>
+        <v>281429</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -21499,40 +21731,40 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Rikke Rasmussen #DBM#</t>
+          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>344.12</v>
+        <v>390.08</v>
       </c>
       <c r="I140" t="n">
-        <v>198.137</v>
+        <v>227.753</v>
       </c>
       <c r="J140" t="n">
-        <v>77.28400000000001</v>
+        <v>103.453</v>
       </c>
       <c r="K140" t="n">
-        <v>57.419</v>
+        <v>47.626</v>
       </c>
       <c r="L140" t="n">
-        <v>45.081</v>
+        <v>62.116</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -21547,61 +21779,243 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
+        <v>5302599</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Rikke Rasmussen #DBM#</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DBM</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>344.12</v>
+      </c>
+      <c r="I141" t="n">
+        <v>198.137</v>
+      </c>
+      <c r="J141" t="n">
+        <v>77.28400000000001</v>
+      </c>
+      <c r="K141" t="n">
+        <v>57.419</v>
+      </c>
+      <c r="L141" t="n">
+        <v>45.081</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>5805064</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Adrian ZC</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Momentum CR</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>366.263</v>
+      </c>
+      <c r="I142" t="n">
+        <v>196.548</v>
+      </c>
+      <c r="J142" t="n">
+        <v>102.665</v>
+      </c>
+      <c r="K142" t="n">
+        <v>64.64700000000001</v>
+      </c>
+      <c r="L142" t="n">
+        <v>51.529</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4175869</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Leslie Koh</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>35</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>373.009</v>
+      </c>
+      <c r="I143" t="n">
+        <v>196.861</v>
+      </c>
+      <c r="J143" t="n">
+        <v>95.843</v>
+      </c>
+      <c r="K143" t="n">
+        <v>62.435</v>
+      </c>
+      <c r="L143" t="n">
+        <v>61.414</v>
+      </c>
+      <c r="M143" t="n">
+        <v>5</v>
+      </c>
+      <c r="N143" t="n">
+        <v>5</v>
+      </c>
+      <c r="O143" t="n">
+        <v>5</v>
+      </c>
+      <c r="P143" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>10</v>
+      </c>
+      <c r="R143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
         <v>1500543</v>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>Stuart Haigh</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="n">
-        <v>35</v>
-      </c>
-      <c r="G141" t="n">
-        <v>1</v>
-      </c>
-      <c r="H141" t="n">
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>25</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
         <v>482.758</v>
       </c>
-      <c r="I141" t="n">
+      <c r="I144" t="n">
         <v>248.476</v>
       </c>
-      <c r="J141" t="n">
+      <c r="J144" t="n">
         <v>127.599</v>
       </c>
-      <c r="K141" t="n">
+      <c r="K144" t="n">
         <v>73.389</v>
       </c>
-      <c r="L141" t="n">
+      <c r="L144" t="n">
         <v>76.169</v>
       </c>
-      <c r="M141" t="n">
-        <v>5</v>
-      </c>
-      <c r="N141" t="n">
-        <v>5</v>
-      </c>
-      <c r="O141" t="n">
-        <v>5</v>
-      </c>
-      <c r="P141" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>10</v>
-      </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" t="n">
+        <v>3</v>
+      </c>
+      <c r="P144" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>8</v>
+      </c>
+      <c r="R144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21614,7 +22028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25461,21 +25875,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>687504</v>
+        <v>6478454</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
+          <t>Jason Spiker (DDIRC)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>43:32.716</t>
         </is>
       </c>
     </row>
@@ -25491,21 +25905,17 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3228186</v>
+        <v>687504</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Matt Jones</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>44:09.197</t>
+          <t>44:04.011</t>
         </is>
       </c>
     </row>
@@ -25521,17 +25931,21 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7963870</v>
+        <v>3228186</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>45:14.312</t>
+          <t>44:09.197</t>
         </is>
       </c>
     </row>
@@ -25547,17 +25961,17 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>426099</v>
+        <v>7963870</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>@ arrows</t>
+          <t>Philip Gill</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>45:14.312</t>
         </is>
       </c>
     </row>
@@ -25573,21 +25987,17 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3294901</v>
+        <v>426099</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>45:16.878</t>
         </is>
       </c>
     </row>
@@ -25603,21 +26013,21 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5689173</v>
+        <v>3294901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>45:22.447</t>
         </is>
       </c>
     </row>
@@ -25629,25 +26039,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5302599</v>
+        <v>5689173</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Rikke Rasmussen #DBM#</t>
+          <t>Kim Bryan &amp;#127800;</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:41.917</t>
         </is>
       </c>
     </row>
@@ -25659,25 +26069,25 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2505328</v>
+        <v>5302599</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
+          <t>Rikke Rasmussen #DBM#</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>48:08.706</t>
         </is>
       </c>
     </row>
@@ -25689,49 +26099,135 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>281429</v>
+        <v>2505328</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+          <t>Mailan Kimsuan [ZIRT]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>51:44.021</t>
+          <t>50:00.950</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5805064</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Adrian ZC</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Momentum CR</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>51:07.527</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>281429</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>51:44.021</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C141" t="n">
+      <c r="C143" t="n">
+        <v>4175869</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Leslie Koh</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>51:08.233</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
         <v>1500543</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>Stuart Haigh</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
         <is>
           <t>58:30.748</t>
         </is>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,22 +1575,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T Ired (DIRTy Rascals Rogue)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>PORK CHOP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17:54.932</t>
+          <t>17:43.586</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1611,13 +1607,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>anas samman</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>T Ired (DIRTy Rascals Rogue)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18:13.739</t>
+          <t>17:54.932</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1638,17 +1638,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rolf Lautenbacher (Bollerwagen)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bollerwagen</t>
-        </is>
-      </c>
+          <t>anas samman</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18:54.224</t>
+          <t>18:13.739</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1669,17 +1665,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mattias Wahlbeck [eSRT]</t>
+          <t>Rolf Lautenbacher (Bollerwagen)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>Bollerwagen</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19:27.002</t>
+          <t>18:54.224</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1695,18 +1691,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Takuma Kanehira</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Mattias Wahlbeck [eSRT]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19:35.776</t>
+          <t>19:27.002</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1722,22 +1722,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gert Segers [WATT]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>The Watt Squad</t>
-        </is>
-      </c>
+          <t>Takuma Kanehira</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>32:25.335</t>
+          <t>19:35.776</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1758,17 +1754,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Michael Mansfield</t>
+          <t>Gert Segers [WATT]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>32:25.399</t>
+          <t>32:25.335</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1789,13 +1785,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brandon Quinton</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Michael Mansfield</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Team CRYO-GEN</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32:31.802</t>
+          <t>32:25.399</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1811,22 +1811,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kevin Hodges | NeXT pb Enshored</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NeXT pb ENSH</t>
-        </is>
-      </c>
+          <t>Brandon Quinton</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32:42.296</t>
+          <t>32:31.802</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1847,17 +1843,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wilson [GTR E-Racing]</t>
+          <t>Kevin Hodges | NeXT pb Enshored</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GTR E-Racing</t>
+          <t>NeXT pb ENSH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>32:43.627</t>
+          <t>32:42.296</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1878,17 +1874,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mads Buster</t>
+          <t>Wilson [GTR E-Racing]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>GTR E-Racing</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33:00.660</t>
+          <t>32:43.627</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1904,22 +1900,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Andr&amp;eacute;  Jones (A-P-V)</t>
+          <t>Mads Buster</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>33:01.374</t>
+          <t>33:00.660</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1935,18 +1931,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Akira  CafeLatte</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Andr&amp;eacute;  Jones (A-P-V)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A-P-V</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33:01.392</t>
+          <t>33:01.374</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1962,22 +1962,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Martin Coffey</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>A-P-V</t>
-        </is>
-      </c>
+          <t>Akira  CafeLatte</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>33:01.766</t>
+          <t>33:01.392</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1998,13 +1994,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mike Leahy</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Martin Coffey</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>A-P-V</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33:02.469</t>
+          <t>33:01.766</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -2025,17 +2025,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kaan Kayin [HEX]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>HEXAGONE.CC</t>
-        </is>
-      </c>
+          <t>Mike Leahy</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>33:17.955</t>
+          <t>33:02.469</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2051,22 +2047,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rasmus Fischer</t>
+          <t>Kaan Kayin [HEX]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>HEXAGONE.CC</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>33:20.972</t>
+          <t>33:17.955</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -2082,22 +2078,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lennart Pol</t>
+          <t>Rasmus Fischer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33:21.271</t>
+          <t>33:20.972</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -2118,17 +2114,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>John Harrison [A-P-V]</t>
+          <t>Lennart Pol</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>33:22.006</t>
+          <t>33:21.271</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2144,18 +2140,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alex Aronne</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>John Harrison [A-P-V]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A-P-V</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>33:22.255</t>
+          <t>33:22.006</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2171,22 +2171,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kim  Damgaard (DZR)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>DZR</t>
-        </is>
-      </c>
+          <t>Alex Aronne</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>33:22.401</t>
+          <t>33:22.255</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2207,17 +2203,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alan   Glendinning</t>
+          <t>Kim  Damgaard (DZR)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>33:24.482</t>
+          <t>33:22.401</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2233,22 +2229,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BEHE Peter Gilmore</t>
+          <t>Alan   Glendinning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>33:31.500</t>
+          <t>33:24.482</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2264,22 +2260,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kevin Plasmans</t>
+          <t>BEHE Peter Gilmore</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ZWB Cycling</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>33:32.562</t>
+          <t>33:31.500</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -2300,17 +2296,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Peter Van Win [WATT]</t>
+          <t>Kevin Plasmans</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>ZWB Cycling</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>33:32.697</t>
+          <t>33:32.562</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2326,22 +2322,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morten Kallevig [V]</t>
+          <t>Peter Van Win [WATT]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33:33.978</t>
+          <t>33:32.697</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -2357,18 +2353,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jack  Matthews</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Morten Kallevig [V]</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Vikings</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>33:34.316</t>
+          <t>33:33.978</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2384,18 +2384,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ezna Ragrts</t>
+          <t>Jack  Matthews</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>33:35.041</t>
+          <t>33:34.316</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -2416,17 +2416,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Marcel Hies</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LEVEL Esports</t>
-        </is>
-      </c>
+          <t>Ezna Ragrts</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>33:35.828</t>
+          <t>33:35.041</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2442,22 +2438,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Luke Walton</t>
+          <t>Marcel Hies</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VenTech</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>33:45.002</t>
+          <t>33:35.828</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2478,13 +2474,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Timothy Pettersson</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Luke Walton</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VenTech</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>33:48.259</t>
+          <t>33:45.002</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2500,22 +2500,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrian Montanez </t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>COALITION</t>
-        </is>
-      </c>
+          <t>Timothy Pettersson</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>35:32.720</t>
+          <t>33:48.259</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2531,22 +2527,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mark Hayes [PWCC]</t>
+          <t xml:space="preserve">Adrian Montanez </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>35:37.346</t>
+          <t>35:32.720</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2562,22 +2558,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garth Haigh </t>
+          <t>Mark Hayes [PWCC]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>35:38.215</t>
+          <t>35:37.346</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2598,17 +2594,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ron Peterson</t>
+          <t xml:space="preserve">Garth Haigh </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>37:17.875</t>
+          <t>35:38.215</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2629,17 +2625,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Abdullah Ak&amp;ccedil;am</t>
+          <t>Ron Peterson</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Zwift TURKIYE</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>37:50.496</t>
+          <t>37:17.875</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2655,22 +2651,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. auritz </t>
+          <t>Abdullah Ak&amp;ccedil;am</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>Zwift TURKIYE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>46:28.636</t>
+          <t>37:50.496</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2691,17 +2687,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nick Baberuxki</t>
+          <t xml:space="preserve">L. auritz </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Talent:frei p/b Baldiso</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>46:30.405</t>
+          <t>46:28.636</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -2717,18 +2713,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yannik Magnussen</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Nick Baberuxki</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Talent:frei p/b Baldiso</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>46:30.506</t>
+          <t>46:30.405</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -2749,17 +2749,13 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thomas Grill (TSE)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>TSE</t>
-        </is>
-      </c>
+          <t>Yannik Magnussen</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>46:30.531</t>
+          <t>46:30.506</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -2775,22 +2771,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Lichtwark </t>
+          <t>Thomas Grill (TSE)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>46:30.573</t>
+          <t>46:30.531</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -2811,17 +2807,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wib Wob</t>
+          <t xml:space="preserve">Jan Lichtwark </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>&amp;#129420; HCT &amp;#129420;</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>46:31.047</t>
+          <t>46:30.573</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -2842,17 +2838,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alexander Laustsen</t>
+          <t>Wib Wob</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>WSport</t>
+          <t>&amp;#129420; HCT &amp;#129420;</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>46:31.077</t>
+          <t>46:31.047</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -2873,17 +2869,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chris Bolwell</t>
+          <t>Alexander Laustsen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>WSport</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>46:35.246</t>
+          <t>46:31.077</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -2899,22 +2895,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hugo Bled [A-P-V]</t>
+          <t>Chris Bolwell</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>46:35.517</t>
+          <t>46:35.246</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -2930,22 +2926,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Steven Garr&amp;eacute; [WATT]</t>
+          <t>Hugo Bled [A-P-V]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>48:05.426</t>
+          <t>46:35.517</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -2966,17 +2962,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>&amp;Oslash;yvind Str&amp;oslash;msholm Pettersen [V]</t>
+          <t>Steven Garr&amp;eacute; [WATT]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>48:13.278</t>
+          <t>48:05.426</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -2992,22 +2988,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dominick Brookes [Freakshow]</t>
+          <t>&amp;Oslash;yvind Str&amp;oslash;msholm Pettersen [V]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[DRAFT]</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>50:35.538</t>
+          <t>48:13.278</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -3028,17 +3024,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tom Been</t>
+          <t>Dominick Brookes [Freakshow]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CONED</t>
+          <t>[DRAFT]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>50:39.719</t>
+          <t>50:35.538</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -3054,18 +3050,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wolfi Mayer</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Tom Been</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CONED</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>50:39.771</t>
+          <t>50:39.719</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3086,17 +3086,13 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Andrea Tritto (ITA)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Team Italy</t>
-        </is>
-      </c>
+          <t>Wolfi Mayer</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>50:45.899</t>
+          <t>50:39.771</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -3117,17 +3113,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNB </t>
+          <t>Andrea Tritto (ITA)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Road2&amp;#129412;</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>51:08.816</t>
+          <t>50:45.899</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -3143,22 +3139,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mads K&amp;uuml;hn</t>
+          <t xml:space="preserve">MNB </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>POW.&amp;#1071;</t>
+          <t>Road2&amp;#129412;</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>51:42.416</t>
+          <t>51:08.816</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -3174,22 +3170,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johan Olivier </t>
+          <t>Mads K&amp;uuml;hn</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>POW.&amp;#1071;</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>51:47.540</t>
+          <t>51:42.416</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -3205,22 +3201,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jason Robinson</t>
+          <t xml:space="preserve">Johan Olivier </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>51:57.759</t>
+          <t>51:47.540</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -3236,22 +3232,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Genaro Nu&amp;ntilde;ez</t>
+          <t>Jason Robinson</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t xml:space="preserve">4STAR </t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>52:56.218</t>
+          <t>51:57.759</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -3267,22 +3263,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gary Forbes (TFC)</t>
+          <t>Genaro Nu&amp;ntilde;ez</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>52:56.733</t>
+          <t>52:56.218</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -3303,17 +3299,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Naohide Hamamoto [ZWC]</t>
+          <t>Gary Forbes (TFC)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TEAM ZWC</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>55:48.972</t>
+          <t>52:56.733</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -3329,22 +3325,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kester Dobson [SDW]</t>
+          <t>Naohide Hamamoto [ZWC]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SDW</t>
+          <t>TEAM ZWC</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>56:47.464</t>
+          <t>55:48.972</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -3355,36 +3351,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sem VH</t>
+          <t>Kester Dobson [SDW]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>COERS</t>
+          <t>SDW</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>01:40:04.671</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>56:47.464</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3400,18 +3392,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Sem VH</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>COERS</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>01:41:56.190</t>
+          <t>01:40:04.671</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01:51.519</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -3431,22 +3427,18 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Thomas Mutz</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01:42:17.110</t>
+          <t>01:41:56.190</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>02:12.439</t>
+          <t>01:51.519</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -3466,18 +3458,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Luke van Harskamp</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t xml:space="preserve">Robert McEwan </t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>01:44:22.993</t>
+          <t>01:42:17.110</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>04:18.322</t>
+          <t>02:12.439</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -3497,22 +3493,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Luke van Harskamp</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01:46:07.754</t>
+          <t>01:44:22.993</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>06:03.083</t>
+          <t>04:18.322</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -3532,22 +3524,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>01:48:57.345</t>
+          <t>01:46:07.754</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>08:52.674</t>
+          <t>06:03.083</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -3562,27 +3554,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
+          <t>L ook mum no hands (RollCo)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>01:49:14.898</t>
+          <t>01:48:57.345</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>09:10.227</t>
+          <t>08:52.674</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -3602,7 +3594,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3612,12 +3604,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>01:49:41.475</t>
+          <t>01:49:14.898</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>09:36.804</t>
+          <t>09:10.227</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3637,22 +3629,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Heinz Ensen (Herd)</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>HERD</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>01:50:03.187</t>
+          <t>01:49:41.475</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>09:58.516</t>
+          <t>09:36.804</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -3667,27 +3659,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
+          <t>Heinz Ensen (Herd)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>01:50:24.252</t>
+          <t>01:50:03.187</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10:19.581</t>
+          <t>09:58.516</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -3707,22 +3699,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>01:51:37.203</t>
+          <t>01:50:24.252</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>11:32.532</t>
+          <t>10:19.581</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3737,23 +3729,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>01:51:57.038</t>
+          <t>01:51:37.203</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>11:52.367</t>
+          <t>11:32.532</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -3773,22 +3769,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mathieu Brisebois-Boies (Rhinos)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01:51:57.935</t>
+          <t>01:51:57.038</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>11:53.264</t>
+          <t>11:52.367</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -3808,22 +3800,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Mathieu Brisebois-Boies (Rhinos)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>01:53:14.134</t>
+          <t>01:51:57.935</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>13:09.463</t>
+          <t>11:53.264</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -3843,22 +3835,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>01:54:35.745</t>
+          <t>01:53:14.134</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>14:31.074</t>
+          <t>13:09.463</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -3873,27 +3865,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
+          <t>Neil Rogers</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>01:58:22.580</t>
+          <t>01:54:35.745</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>18:17.909</t>
+          <t>14:31.074</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3913,22 +3905,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
+          <t>Justin Draper [Fellowship]</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>02:11:19.402</t>
+          <t>01:58:22.580</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>31:14.731</t>
+          <t>18:17.909</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3943,27 +3935,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Phil Cox (TNP)</t>
+          <t>2. Burrito &amp;#127791;</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>02:51:32.259</t>
+          <t>02:11:19.402</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01:11:27.588</t>
+          <t>31:14.731</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3978,12 +3970,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oliver Slowboi (TNP)</t>
+          <t>Phil Cox (TNP)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3993,12 +3985,16 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>01:13:09.902</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>02:51:32.259</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>01:11:27.588</t>
+        </is>
+      </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -4009,22 +4005,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Oliver Slowboi (TNP)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>01:15:35.073</t>
+          <t>01:13:09.902</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Andrew Stamp(RollCo)</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>01:29:00.740</t>
+          <t>01:15:35.073</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -4076,17 +4072,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Andrew Stamp(RollCo)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>01:32:18.744</t>
+          <t>01:29:00.740</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -4107,17 +4103,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos Barreiros </t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>01:33:07.466</t>
+          <t>01:32:18.744</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -4133,27 +4129,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jeremy Gourd (FUTURE)</t>
+          <t xml:space="preserve">Carlos Barreiros </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FUTR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>16:19.801</t>
+          <t>01:33:07.466</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -4164,18 +4160,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>F. Lofsgaard (Oslofjord)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Jeremy Gourd (FUTURE)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>FUTR</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>17:05.523</t>
+          <t>16:19.801</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -4196,17 +4196,13 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ivar  Bringedal [V] </t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Vikings</t>
-        </is>
-      </c>
+          <t>F. Lofsgaard (Oslofjord)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>17:19.121</t>
+          <t>17:05.523</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -4227,17 +4223,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lance Loveday (Victory Velo Racing)</t>
+          <t xml:space="preserve">Jan Ivar  Bringedal [V] </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Victory Velo Racing</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>18:34.306</t>
+          <t>17:19.121</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -4258,17 +4254,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tonne (DIRT)</t>
+          <t>Lance Loveday (Victory Velo Racing)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Victory Velo Racing</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>18:58.125</t>
+          <t>18:34.306</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -4289,17 +4285,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Steffen Schulz (HCH.CC)</t>
+          <t>Tonne (DIRT)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>HCH.CC</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>19:05.995</t>
+          <t>18:58.125</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -4315,22 +4311,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chris Beardsell (TNP)</t>
+          <t>Steffen Schulz (HCH.CC)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HCH.CC</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>19:25.664</t>
+          <t>19:05.995</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -4351,17 +4347,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Alexey Tikhov (B)</t>
+          <t>Chris Beardsell (TNP)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20:18.104</t>
+          <t>19:25.664</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -4382,13 +4378,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Alex Leonard</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Alexey Tikhov (B)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>MTBtraining</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20:57.635</t>
+          <t>20:18.104</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kashiwa no Ha Campus Seikeigeka</t>
+          <t>Alex Leonard</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>22:08.029</t>
+          <t>20:57.635</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -4436,13 +4436,13 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Connor Wilm</t>
+          <t>Kashiwa no Ha Campus Seikeigeka</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>22:44.080</t>
+          <t>22:08.029</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -4458,22 +4458,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chris Cayford</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Team Velos</t>
-        </is>
-      </c>
+          <t>Connor Wilm</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>32:59.583</t>
+          <t>22:44.080</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -4489,22 +4485,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Rob Wainwright  (Corona Zwifters)</t>
+          <t>Chris Cayford</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Corona Zwifters</t>
+          <t>Team Velos</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>33:34.276</t>
+          <t>32:59.583</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -4525,17 +4521,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erlend Olsen </t>
+          <t>Rob Wainwright  (Corona Zwifters)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>BAB</t>
+          <t>Corona Zwifters</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>34:11.228</t>
+          <t>33:34.276</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4556,17 +4552,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>kristian Mikkelsen</t>
+          <t xml:space="preserve">Erlend Olsen </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CK 2020</t>
+          <t>BAB</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>34:15.757</t>
+          <t>34:11.228</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -4587,17 +4583,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Niclas M&amp;aelig;hle (TNP)</t>
+          <t>kristian Mikkelsen</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>CK 2020</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>34:43.721</t>
+          <t>34:15.757</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -4618,13 +4614,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ben dart</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Niclas M&amp;aelig;hle (TNP)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>35:17.401</t>
+          <t>34:43.721</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -4645,17 +4645,13 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>ben dart</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>35:34.069</t>
+          <t>35:17.401</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -4671,22 +4667,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Adam Britton</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>35:41.512</t>
+          <t>35:34.069</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -4707,17 +4703,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Christian Brown (Rhino)</t>
+          <t>Adam Britton</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>35:51.007</t>
+          <t>35:41.512</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -4733,22 +4729,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>David Fisher (Team CLS)</t>
+          <t>Christian Brown (Rhino)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Team CLS</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>35:55.766</t>
+          <t>35:51.007</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -4764,22 +4760,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hans Fischer</t>
+          <t>David Fisher (Team CLS)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>36:22.857</t>
+          <t>35:55.766</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -4800,17 +4796,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mark Williams (RollCo)</t>
+          <t>Hans Fischer</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>36:33.721</t>
+          <t>36:22.857</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -4831,17 +4827,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jorelle  Hernandez (TZP)</t>
+          <t>Mark Williams (RollCo)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TZP</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>37:14.815</t>
+          <t>36:33.721</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -4862,17 +4858,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Phillip Reynolds (LEQPxHunters)</t>
+          <t>Jorelle  Hernandez (TZP)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>37:39.268</t>
+          <t>37:14.815</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -4893,17 +4889,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+          <t>Phillip Reynolds (LEQPxHunters)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>38:09.320</t>
+          <t>37:39.268</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -4924,13 +4920,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>K.O.&amp;#128048;[TMR]</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>38:31.471</t>
+          <t>38:09.320</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -4946,22 +4946,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Nathan Gerdts (SISU)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>K.O.&amp;#128048;[TMR]</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>39:03.466</t>
+          <t>38:31.471</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -4977,22 +4973,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Daniel Kent</t>
+          <t>Nathan Gerdts (SISU)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>39:06.280</t>
+          <t>39:03.466</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -5013,13 +5009,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brian Pryor</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Daniel Kent</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>39:27.783</t>
+          <t>39:06.280</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -5040,13 +5040,13 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cristian Montero</t>
+          <t>Brian Pryor</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>39:28.748</t>
+          <t>39:27.783</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -5067,17 +5067,13 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Cristian Montero</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>41:03.174</t>
+          <t>39:28.748</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -5093,18 +5089,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pedro Leal</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Greg SHED</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>42:04.672</t>
+          <t>41:03.174</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -5120,22 +5120,18 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Jens Liljekrok [OUT]&amp;#128023;</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
+          <t>Pedro Leal</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>48:55.896</t>
+          <t>42:04.672</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -5151,18 +5147,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Blair Rouse KSBT</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t xml:space="preserve">	Jens Liljekrok [OUT]&amp;#128023;</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>48:58.105</t>
+          <t>48:55.896</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -5178,18 +5178,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ryan Quinn</t>
+          <t>Blair Rouse KSBT</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>50:35.813</t>
+          <t>48:58.105</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -5210,17 +5210,13 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Nikolay Hristozov</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Ryan Quinn</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>51:35.555</t>
+          <t>50:35.813</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -5236,22 +5232,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  Steelo [GXY] </t>
+          <t>Nikolay Hristozov</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>51:56.202</t>
+          <t>51:35.555</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5267,22 +5263,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Trevan Burn [Rhino]</t>
+          <t xml:space="preserve">...  Steelo [GXY] </t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>51:56.407</t>
+          <t>51:56.202</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -5303,17 +5299,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t>Trevan Burn [Rhino]</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>51:57.484</t>
+          <t>51:56.407</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5334,17 +5330,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Juan The One</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>51:57.589</t>
+          <t>51:57.484</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -5365,13 +5361,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Duncan Donnay</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Juan The One</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>52:00.120</t>
+          <t>51:57.589</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5392,17 +5392,13 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ronny Holen [ZU4R]</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>ZU4R eSport</t>
-        </is>
-      </c>
+          <t>Duncan Donnay</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>52:01.437</t>
+          <t>52:00.120</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -5423,17 +5419,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Stephen Collins</t>
+          <t>Ronny Holen [ZU4R]</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VRR</t>
+          <t>ZU4R eSport</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>52:01.710</t>
+          <t>52:01.437</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -5454,13 +5450,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Benjamin Howe</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Stephen Collins</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>VRR</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>52:28.109</t>
+          <t>52:01.710</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -5481,13 +5481,13 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tim Baldwin</t>
+          <t>Benjamin Howe</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>52:43.417</t>
+          <t>52:28.109</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5508,13 +5508,13 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>mark R</t>
+          <t>Tim Baldwin</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>53:06.439</t>
+          <t>52:43.417</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -5535,17 +5535,13 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Rex  Tan</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>ZPH Philippines</t>
-        </is>
-      </c>
+          <t>mark R</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>53:11.780</t>
+          <t>53:06.439</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -5566,13 +5562,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Casey Morgan</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Rex  Tan</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ZPH Philippines</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>53:14.384</t>
+          <t>53:11.780</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -5593,13 +5593,13 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Joshua Bramah</t>
+          <t>Casey Morgan</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>54:07.843</t>
+          <t>53:14.384</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -5620,17 +5620,13 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Antonie Vervenne</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>CMC</t>
-        </is>
-      </c>
+          <t>Joshua Bramah</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>54:25.661</t>
+          <t>54:07.843</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -5651,17 +5647,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Sam Mack (BPCC)</t>
+          <t>Antonie Vervenne</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>BPCC</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>54:38.070</t>
+          <t>54:25.661</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -5677,18 +5673,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kasper Steadywheel</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Sam Mack (BPCC)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BPCC</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>54:41.448</t>
+          <t>54:38.070</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -5704,22 +5704,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chris Cremer</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Kasper Steadywheel</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>54:58.285</t>
+          <t>54:41.448</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -5740,17 +5736,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Marco Roetert Steenbruggen</t>
+          <t>Chris Cremer</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TeamNL</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>55:01.809</t>
+          <t>54:58.285</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -5771,17 +5767,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>D Welch</t>
+          <t>Marco Roetert Steenbruggen</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ROCA</t>
+          <t>TeamNL</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>55:01.843</t>
+          <t>55:01.809</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -5797,18 +5793,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stuart  Campbell</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>D Welch</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ROCA</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>55:09.451</t>
+          <t>55:01.843</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -5824,22 +5824,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>JV Allstar</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Stuart  Campbell</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>55:10.094</t>
+          <t>55:09.451</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -5860,13 +5856,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tim van Reusel</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>JV Allstar</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>55:17.063</t>
+          <t>55:10.094</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -5887,17 +5887,13 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Barrie &amp;#128059;&amp;#10084;&amp;#65039;&amp;#128060; (Rhino)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Tim van Reusel</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>57:23.726</t>
+          <t>55:17.063</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -5913,18 +5909,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jerome Wigger</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Barrie &amp;#128059;&amp;#10084;&amp;#65039;&amp;#128060; (Rhino)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>01:00:47.732</t>
+          <t>57:23.726</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -5940,18 +5940,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Eugene Shuster</t>
+          <t>Jerome Wigger</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>01:03:18.565</t>
+          <t>01:00:47.732</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5972,26 +5972,18 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Simon Baker</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Eugene Shuster</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>01:52:19.710</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:03:18.565</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -6002,27 +5994,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>01:52:30.533</t>
+          <t>01:52:19.710</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>10.823</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -6037,23 +6029,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Olivier Simonin</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>01:52:50.242</t>
+          <t>01:52:30.533</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>30.532</t>
+          <t>10.823</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -6068,27 +6064,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>David Irwin</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>01:57:17.045</t>
+          <t>01:52:50.242</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>04:57.335</t>
+          <t>30.532</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -6108,22 +6100,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>01:58:21.471</t>
+          <t>01:57:17.045</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>06:01.761</t>
+          <t>04:57.335</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -6143,22 +6135,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>02:01:42.581</t>
+          <t>01:58:21.471</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>09:22.871</t>
+          <t>06:01.761</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -6178,7 +6170,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6188,12 +6180,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>02:03:07.712</t>
+          <t>02:01:42.581</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>10:48.002</t>
+          <t>09:22.871</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -6213,22 +6205,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>02:06:33.477</t>
+          <t>02:03:07.712</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>14:13.767</t>
+          <t>10:48.002</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -6243,27 +6235,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cara Lockwood (RollCo)</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>01:01:16.590</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
+          <t>02:06:33.477</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>14:13.767</t>
+        </is>
+      </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -6279,22 +6275,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Javier (HERC) </t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Jason Spiker (DDIRC)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>01:34:05.691</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
+          <t>02:07:16.610</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>14:56.900</t>
+        </is>
+      </c>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -6305,18 +6301,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Evan  Carouchio</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Cara Lockwood (RollCo)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>01:40:13.863</t>
+          <t>01:01:16.590</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -6337,13 +6337,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jason Spiker (DDIRC)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t xml:space="preserve">3 Javier (HERC) </t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>01:43:51.918</t>
+          <t>01:34:05.691</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -6364,18 +6368,18 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prz Luca</t>
+          <t>Evan  Carouchio</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>20:25.170</t>
+          <t>01:40:13.863</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
@@ -6391,13 +6395,13 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Matt Whisker</t>
+          <t>Prz Luca</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>20:44.463</t>
+          <t>20:25.170</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -6418,17 +6422,13 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ian Stokes</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Matt Whisker</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>22:09.403</t>
+          <t>20:44.463</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -6444,22 +6444,22 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Michael Leesing</t>
+          <t>Ian Stokes</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>TBR Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>33:36.908</t>
+          <t>22:09.403</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -6480,17 +6480,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Dag Eidesen</t>
+          <t>Michael Leesing</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>TBR Racing</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>33:36.908</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -6506,22 +6506,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t>Dag Eidesen</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -6537,22 +6537,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Scott Henderson (BON - GXY)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:06.428</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -6568,22 +6568,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>sheldon White (BAKPDL B3)</t>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>BAKPDL</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>39:05.483</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -6604,13 +6604,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Richard Finch</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>sheldon White (BAKPDL B3)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BAKPDL</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>39:07.515</t>
+          <t>39:05.483</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -6631,17 +6635,13 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Dirk Richter</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>ZRG</t>
-        </is>
-      </c>
+          <t>Richard Finch</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>39:07.844</t>
+          <t>39:07.515</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -6662,17 +6662,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Ben Hartopp [SNOW]</t>
+          <t>Dirk Richter</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ZRG</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>39:07.844</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -6688,22 +6688,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jorge Ar&amp;eacute;valo</t>
+          <t>Ben Hartopp [SNOW]</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>39:26.642</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -6724,17 +6724,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Roberto Delgado Hynes</t>
+          <t>Jorge Ar&amp;eacute;valo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Velo&amp;#039;Z</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>39:46.669</t>
+          <t>39:26.642</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -6750,12 +6750,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>John Swift</t>
+          <t>Roberto Delgado Hynes</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>39:51.976</t>
+          <t>39:46.669</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -6786,13 +6786,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sebastian Borquez</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>John Swift</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>40:39.786</t>
+          <t>39:51.976</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -6813,17 +6817,13 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andy Westall </t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>SWCC</t>
-        </is>
-      </c>
+          <t>Sebastian Borquez</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>40:55.101</t>
+          <t>40:39.786</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -6844,17 +6844,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Pearce </t>
+          <t xml:space="preserve">Andy Westall </t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>TBG</t>
+          <t>SWCC</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>40:55.101</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -6870,22 +6870,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Mads Gronbek [DBR]</t>
+          <t xml:space="preserve">John Pearce </t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>TBG</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>42:08.148</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -6901,18 +6901,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Andrew Lowrie</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Mads Gronbek [DBR]</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DBR</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>42:29.930</t>
+          <t>42:08.148</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -6928,22 +6932,18 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Mark SMITH6725</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>CTT</t>
-        </is>
-      </c>
+          <t>Andrew Lowrie</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>42:29.930</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -6959,18 +6959,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Magnus Morel</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Mark SMITH6725</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CTT</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>44:58.275</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -6986,18 +6990,18 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sam Godfrey</t>
+          <t>Magnus Morel</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>45:17.857</t>
+          <t>44:58.275</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -7018,13 +7022,13 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Christophe Chris [BIKES-FR]</t>
+          <t>Sam Godfrey</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>50:43.002</t>
+          <t>45:17.857</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -7045,13 +7049,13 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adam Sternfield </t>
+          <t>Christophe Chris [BIKES-FR]</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
-          <t>51:57.148</t>
+          <t>50:43.002</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -7067,22 +7071,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Morten  Bach  Jepsen</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>DBR</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Adam Sternfield </t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>52:58.678</t>
+          <t>51:57.148</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -7098,22 +7098,22 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
+          <t>Morten  Bach  Jepsen</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>53:25.685</t>
+          <t>52:58.678</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -7129,22 +7129,22 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Richard Emblen</t>
+          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>54:43.733</t>
+          <t>53:25.685</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -7165,17 +7165,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nick Kelly [4STAR] </t>
+          <t>Richard Emblen</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>54:45.613</t>
+          <t>54:43.733</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -7196,13 +7196,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tom Bradley</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
+          <t xml:space="preserve">Nick Kelly [4STAR] </t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>54:59.827</t>
+          <t>54:45.613</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -7218,18 +7222,18 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Zsolt Kun-Szabo</t>
+          <t>Tom Bradley</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
-          <t>55:01.241</t>
+          <t>54:59.827</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -7245,22 +7249,18 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steve Boon (GXY) </t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Zsolt Kun-Szabo</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>55:01.338</t>
+          <t>55:01.241</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -7281,17 +7281,17 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Marc Singer</t>
+          <t xml:space="preserve">Steve Boon (GXY) </t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>T3 Philly</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>55:10.735</t>
+          <t>55:01.338</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -7312,17 +7312,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane King </t>
+          <t>Marc Singer</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>R4CF.</t>
+          <t>T3 Philly</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>55:20.717</t>
+          <t>55:10.735</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -7343,17 +7343,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Lorenzo Meciani (CAY)</t>
+          <t xml:space="preserve">Shane King </t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Dogs-Pigs</t>
+          <t>R4CF.</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>56:48.630</t>
+          <t>55:20.717</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -7374,13 +7374,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>john hoffmann6976</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>Lorenzo Meciani (CAY)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Dogs-Pigs</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>57:28.007</t>
+          <t>56:48.630</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -7401,17 +7405,13 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Simon  Harvey</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>COALITION</t>
-        </is>
-      </c>
+          <t>john hoffmann6976</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>57:28.797</t>
+          <t>57:28.007</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -7432,13 +7432,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>oliver johnson</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Simon  Harvey</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>57:29.161</t>
+          <t>57:28.797</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -7459,17 +7463,13 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Ryan Dagooc</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4STAR </t>
-        </is>
-      </c>
+          <t>oliver johnson</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>57:29.768</t>
+          <t>57:29.161</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -7490,13 +7490,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis  Gouchie </t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Ryan Dagooc</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>57:31.232</t>
+          <t>57:29.768</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -7512,18 +7516,18 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Fabien V</t>
+          <t xml:space="preserve">Travis  Gouchie </t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>57:45.692</t>
+          <t>57:31.232</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -7539,18 +7543,18 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>L Andersen</t>
+          <t>Fabien V</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>57:52.627</t>
+          <t>57:45.692</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -7571,17 +7575,13 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Paul Potter (HERC)</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>L Andersen</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>57:58.030</t>
+          <t>57:52.627</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -7602,17 +7602,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Michael Lindsay</t>
+          <t>Paul Potter (HERC)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>58:05.278</t>
+          <t>57:58.030</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -7633,17 +7633,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Christopher Lindskjold</t>
+          <t>Michael Lindsay</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>58:17.985</t>
+          <t>58:05.278</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -7664,17 +7664,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Christopher Lindskjold</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>59:33.723</t>
+          <t>58:17.985</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -7695,13 +7695,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Shige Haru</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t xml:space="preserve">Kim YUU </t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>59:49.958</t>
+          <t>59:33.723</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -7717,22 +7721,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Carl</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Shige Haru</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>59:57.500</t>
+          <t>59:49.958</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -7748,22 +7748,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artur Burdasz </t>
+          <t>Carl</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ZTPL.CC</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>01:01:28.813</t>
+          <t>59:57.500</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -7784,17 +7784,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>psf</t>
+          <t xml:space="preserve">Artur Burdasz </t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>ZTPL.CC</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>01:01:36.829</t>
+          <t>01:01:28.813</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -7810,22 +7810,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luke O&amp;#039;Connor </t>
+          <t>psf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Tamworth CC</t>
+          <t>WCC</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>01:04:59.019</t>
+          <t>01:01:36.829</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -7846,17 +7846,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t xml:space="preserve">Luke O&amp;#039;Connor </t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Tamworth CC</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>01:05:04.959</t>
+          <t>01:04:59.019</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -7867,36 +7867,32 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>02:08:02.879</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:05:04.959</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -7907,27 +7903,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>02:08:11.820</t>
+          <t>02:08:02.879</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>08.941</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -7947,22 +7943,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>02:09:46.608</t>
+          <t>02:08:11.820</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>01:43.729</t>
+          <t>08.941</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -7977,27 +7973,31 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+          <t>Aidan Novis (RHINO)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>01:17:01.165</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr"/>
+          <t>02:09:46.608</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>01:43.729</t>
+        </is>
+      </c>
       <c r="G246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -8013,17 +8013,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>01:24:31.213</t>
+          <t>01:17:01.165</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>01:26:11.009</t>
+          <t>01:24:31.213</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -8070,27 +8070,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Matt Taylor (Charlies Angels Full Throttle)</t>
+          <t>Brian Benner (HERC)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>CAFT</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>21:38.777</t>
+          <t>01:26:11.009</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -8101,22 +8101,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Stefaan Lampaert</t>
+          <t>Matt Taylor (Charlies Angels Full Throttle)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>BZR eCycling Club</t>
+          <t>CAFT</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>22:33.716</t>
+          <t>21:38.777</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -8132,18 +8132,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>FELIX CALVO POO</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Stefaan Lampaert</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>BZR eCycling Club</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>22:39.179</t>
+          <t>22:33.716</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -8164,17 +8168,13 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Julia Umbrello [eSRT]</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+          <t>FELIX CALVO POO</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>22:54.914</t>
+          <t>22:39.179</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -8190,18 +8190,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Austin H</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>Julia Umbrello [eSRT]</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>24:27.518</t>
+          <t>22:54.914</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -8222,13 +8226,13 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Ryan Gower</t>
+          <t>Austin H</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>25:21.604</t>
+          <t>24:27.518</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -8249,13 +8253,13 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Ian Lovely</t>
+          <t>Ryan Gower</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>26:35.426</t>
+          <t>25:21.604</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -8271,18 +8275,18 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Joe Limke</t>
+          <t>Ian Lovely</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>29:31.924</t>
+          <t>26:35.426</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -8298,22 +8302,18 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>COALITION</t>
-        </is>
-      </c>
+          <t>Joe Limke</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>30:35.758</t>
+          <t>29:31.924</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -8334,13 +8334,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>30:35.758</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -8361,13 +8365,13 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
+          <t>Matt Jones</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>45:14.312</t>
+          <t>44:04.011</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -8388,13 +8392,13 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>@ arrows</t>
+          <t>Philip Gill</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>45:14.312</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -8415,17 +8419,13 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>45:16.878</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -8441,22 +8441,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Rikke Rasmussen #DBM#</t>
+          <t>Kim Bryan &amp;#127800;</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:41.917</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -8472,22 +8472,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
+          <t>Rikke Rasmussen #DBM#</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -8503,22 +8503,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Adrian ZC</t>
+          <t>Mailan Kimsuan [ZIRT]</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Momentum CR</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>51:07.527</t>
+          <t>50:00.950</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -8534,22 +8534,22 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Jamie Roy</t>
+          <t>Adrian ZC</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Stages Cycling</t>
+          <t>Momentum CR</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>57:26.520</t>
+          <t>51:07.527</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -8570,17 +8570,17 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Ant Vine</t>
+          <t>Jamie Roy</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Stages Cycling</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>57:31.627</t>
+          <t>57:26.520</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -8601,17 +8601,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>sean carter [WMZ]</t>
+          <t>Ant Vine</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>57:32.338</t>
+          <t>57:31.627</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -8632,13 +8632,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jason Gillespie (Orkney CC)</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>sean carter [WMZ]</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>WMZ</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>58:45.630</t>
+          <t>57:32.338</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -8659,17 +8663,13 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Arif Wijayanto</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>ZID</t>
-        </is>
-      </c>
+          <t>Jason Gillespie (Orkney CC)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>01:02:24.672</t>
+          <t>58:45.630</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -8690,17 +8690,17 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Armitage  Herc </t>
+          <t>Arif Wijayanto</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>ZID</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>01:03:30.326</t>
+          <t>01:02:24.672</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -8716,22 +8716,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Ron Clarino TeamODZ</t>
+          <t xml:space="preserve">Robert Armitage  Herc </t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TeamODZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>01:05:07.663</t>
+          <t>01:03:30.326</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -8747,18 +8747,22 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Danny Postell GCC</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Ron Clarino TeamODZ</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>TeamODZ</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>01:05:25.276</t>
+          <t>01:05:07.663</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -8779,13 +8783,13 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>&amp;#321;ukasz Karasi&amp;#324;ski</t>
+          <t>Danny Postell GCC</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>01:09:46.960</t>
+          <t>01:05:25.276</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -8796,7 +8800,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8806,13 +8810,13 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>John Rae</t>
+          <t>&amp;#321;ukasz Karasi&amp;#324;ski</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>27:07.445</t>
+          <t>01:09:46.960</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -8833,13 +8837,13 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Philip Gkikas CAAT &amp;#128076;</t>
+          <t>John Rae</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>28:25.665</t>
+          <t>27:07.445</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -8860,13 +8864,13 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Leslie Koh</t>
+          <t xml:space="preserve"> Philip Gkikas CAAT &amp;#128076;</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>51:08.233</t>
+          <t>28:25.665</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -8887,13 +8891,13 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Stuart Haigh</t>
+          <t>Leslie Koh</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>58:30.748</t>
+          <t>51:08.233</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -8914,17 +8918,44 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Benjamin Sommervoll</t>
+          <t>Stuart Haigh</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>01:01:28.928</t>
+          <t>58:30.748</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Benjamin Sommervoll</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>01:01:28.928</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15135,7 +15166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17030,11 +17061,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6842342</v>
+        <v>6478454</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17044,37 +17075,33 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Jason Spiker (DDIRC)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
         <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>14.968</v>
+        <v>17.882</v>
       </c>
       <c r="I44" t="n">
-        <v>40.369</v>
+        <v>49.568</v>
       </c>
       <c r="J44" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3294901</v>
+        <v>6842342</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -17083,42 +17110,42 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
         <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>15.678</v>
+        <v>14.968</v>
       </c>
       <c r="I45" t="n">
-        <v>41.622</v>
+        <v>40.369</v>
       </c>
       <c r="J45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3228186</v>
+        <v>3294901</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -17132,12 +17159,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -17147,18 +17174,62 @@
         <v>3</v>
       </c>
       <c r="H46" t="n">
+        <v>15.678</v>
+      </c>
+      <c r="I46" t="n">
+        <v>41.622</v>
+      </c>
+      <c r="J46" t="n">
+        <v>16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>18</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3228186</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>34</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
         <v>15.417</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I47" t="n">
         <v>45.259</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J47" t="n">
         <v>18</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K47" t="n">
         <v>16</v>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17171,7 +17242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19666,7 +19737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8149174</v>
+        <v>832585</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -19680,12 +19751,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -19695,40 +19766,40 @@
         <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>249.148</v>
+        <v>273.7</v>
       </c>
       <c r="I41" t="n">
-        <v>162.06</v>
+        <v>149.223</v>
       </c>
       <c r="J41" t="n">
-        <v>68.562</v>
+        <v>74.93899999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>44.718</v>
+        <v>43.439</v>
       </c>
       <c r="L41" t="n">
-        <v>49.544</v>
+        <v>39.652</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>832585</v>
+        <v>8149174</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -19742,49 +19813,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>273.7</v>
+        <v>249.148</v>
       </c>
       <c r="I42" t="n">
-        <v>149.223</v>
+        <v>162.06</v>
       </c>
       <c r="J42" t="n">
-        <v>74.93899999999999</v>
+        <v>68.562</v>
       </c>
       <c r="K42" t="n">
-        <v>43.439</v>
+        <v>44.718</v>
       </c>
       <c r="L42" t="n">
-        <v>39.652</v>
+        <v>49.544</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R42" t="inlineStr"/>
     </row>
@@ -19813,7 +19884,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
         <v>3</v>
@@ -19846,17 +19917,17 @@
         <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6842342</v>
+        <v>6478454</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -19866,55 +19937,51 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Jason Spiker (DDIRC)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
         <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>277.114</v>
+        <v>288.066</v>
       </c>
       <c r="I44" t="n">
-        <v>163.575</v>
+        <v>156.47</v>
       </c>
       <c r="J44" t="n">
-        <v>72.70399999999999</v>
+        <v>78.224</v>
       </c>
       <c r="K44" t="n">
-        <v>44.468</v>
+        <v>49.941</v>
       </c>
       <c r="L44" t="n">
-        <v>41.404</v>
+        <v>43.596</v>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3294901</v>
+        <v>6842342</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -19923,60 +19990,60 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G45" t="n">
         <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>352.066</v>
+        <v>277.114</v>
       </c>
       <c r="I45" t="n">
-        <v>180.835</v>
+        <v>163.575</v>
       </c>
       <c r="J45" t="n">
-        <v>87.05</v>
+        <v>72.70399999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>51.897</v>
+        <v>44.468</v>
       </c>
       <c r="L45" t="n">
-        <v>40.523</v>
+        <v>41.404</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3228186</v>
+        <v>3294901</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -19990,51 +20057,113 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G46" t="n">
         <v>3</v>
       </c>
       <c r="H46" t="n">
+        <v>352.066</v>
+      </c>
+      <c r="I46" t="n">
+        <v>180.835</v>
+      </c>
+      <c r="J46" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="K46" t="n">
+        <v>51.897</v>
+      </c>
+      <c r="L46" t="n">
+        <v>40.523</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>5</v>
+      </c>
+      <c r="P46" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3228186</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>22</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
         <v>284.211</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I47" t="n">
         <v>184.83</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J47" t="n">
         <v>72.991</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K47" t="n">
         <v>45.406</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L47" t="n">
         <v>53.454</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M47" t="n">
         <v>3</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N47" t="n">
         <v>3</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O47" t="n">
         <v>2</v>
       </c>
-      <c r="P46" t="n">
+      <c r="P47" t="n">
         <v>6</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q47" t="n">
         <v>8</v>
       </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28841,7 +28970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29849,30 +29978,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2648548</v>
+        <v>2541068</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>PORK CHOP</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24:57.241</t>
+          <t>17:43.586</t>
         </is>
       </c>
     </row>
@@ -29884,51 +30009,51 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2702018</v>
+        <v>2648548</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Austin H</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Claire Greensides [HERC]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24:27.518</t>
+          <t>24:57.241</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2881429</v>
+        <v>2702018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Austin H</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20:55.077</t>
+          <t>24:27.518</t>
         </is>
       </c>
     </row>
@@ -29940,21 +30065,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2897364</v>
+        <v>2881429</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>F. Lofsgaard (Oslofjord)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17:05.523</t>
+          <t>20:55.077</t>
         </is>
       </c>
     </row>
@@ -29970,51 +30099,47 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3029902</v>
+        <v>2897364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tonne (DIRT)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>F. Lofsgaard (Oslofjord)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18:58.125</t>
+          <t>17:05.523</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3228186</v>
+        <v>3029902</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>Tonne (DIRT)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>23:16.078</t>
+          <t>18:58.125</t>
         </is>
       </c>
     </row>
@@ -30030,51 +30155,51 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3294901</v>
+        <v>3228186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Aidan Novis (RHINO)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25:00.961</t>
+          <t>23:16.078</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3614977</v>
+        <v>3294901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Heinz Ensen (Herd)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HERD</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20:44.865</t>
+          <t>25:00.961</t>
         </is>
       </c>
     </row>
@@ -30090,28 +30215,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3785513</v>
+        <v>3614977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chris Beardsell (TNP)</t>
+          <t>Heinz Ensen (Herd)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>19:25.664</t>
+          <t>20:44.865</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -30120,24 +30245,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4115593</v>
+        <v>3785513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Matt Whisker</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>Chris Beardsell (TNP)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20:44.463</t>
+          <t>19:25.664</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -30146,110 +30275,106 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4166463</v>
+        <v>4115593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
+          <t>Matt Whisker</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20:41.230</t>
+          <t>20:44.463</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4730842</v>
+        <v>4166463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>ATGNI</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>16:52.190</t>
+          <t>20:41.230</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4744093</v>
+        <v>4730842</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ian Lovely</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Harris Waters(ATGNI)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ATGNI</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>26:35.426</t>
+          <t>16:52.190</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4752321</v>
+        <v>4744093</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Alexey Tikhov (B)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>MTBtraining</t>
-        </is>
-      </c>
+          <t>Ian Lovely</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20:18.104</t>
+          <t>26:35.426</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -30258,54 +30383,54 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4812330</v>
+        <v>4752321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FELIX CALVO POO</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>Alexey Tikhov (B)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MTBtraining</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>22:39.179</t>
+          <t>20:18.104</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5023963</v>
+        <v>4812330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Coach lak (TNP)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>FELIX CALVO POO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17:09.476</t>
+          <t>22:39.179</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -30314,11 +30439,11 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5070491</v>
+        <v>5023963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Oliver Slowboi (TNP)</t>
+          <t>Coach lak (TNP)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -30328,7 +30453,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>18:58.696</t>
+          <t>17:09.476</t>
         </is>
       </c>
     </row>
@@ -30344,69 +30469,73 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5139632</v>
+        <v>5070491</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Oliver Slowboi (TNP)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17:46.581</t>
+          <t>18:58.696</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5244070</v>
+        <v>5139632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ryan Gower</t>
+          <t>Thomas Mutz</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25:21.604</t>
+          <t>17:46.581</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5244607</v>
+        <v>5244070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>K.O.&amp;#128048;[TMR]</t>
+          <t>Ryan Gower</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>38:31.471</t>
+          <t>25:21.604</t>
         </is>
       </c>
     </row>
@@ -30418,32 +30547,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5277640</v>
+        <v>5244607</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Phil Cox (TNP)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>K.O.&amp;#128048;[TMR]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>21:40.789</t>
+          <t>38:31.471</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -30452,81 +30577,81 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5338314</v>
+        <v>5277640</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Julia Umbrello [eSRT]</t>
+          <t>Phil Cox (TNP)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>22:54.914</t>
+          <t>21:40.789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5402095</v>
+        <v>5338314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Julia Umbrello [eSRT]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>16:20.781</t>
+          <t>22:54.914</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5410692</v>
+        <v>5402095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
+          <t>Quentin Vee [EVO]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>30:35.758</t>
+          <t>16:20.781</t>
         </is>
       </c>
     </row>
@@ -30542,51 +30667,51 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5491339</v>
+        <v>5410692</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24:41.858</t>
+          <t>30:35.758</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5877680</v>
+        <v>5491339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sem VH</t>
+          <t>Brian Benner (HERC)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>COERS</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17:33.561</t>
+          <t>24:41.858</t>
         </is>
       </c>
     </row>
@@ -30598,55 +30723,55 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5880054</v>
+        <v>5877680</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
+          <t>Sem VH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>19:15.645</t>
+          <t>17:33.561</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5893609</v>
+        <v>5880054</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>15:56.912</t>
+          <t>19:15.645</t>
         </is>
       </c>
     </row>
@@ -30658,15 +30783,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5959135</v>
+        <v>5893609</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ben  Spedding [TNP]</t>
+          <t>Aled Jones</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -30676,67 +30801,67 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17:19.299</t>
+          <t>15:56.912</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5981378</v>
+        <v>5959135</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20:01.465</t>
+          <t>17:19.299</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6006740</v>
+        <v>5981378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Keegan McCormick [A-P-V]</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>15:20.732</t>
+          <t>20:01.465</t>
         </is>
       </c>
     </row>
@@ -30748,32 +30873,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6172013</v>
+        <v>6006740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Markel Sierra</t>
+          <t>Keegan McCormick [A-P-V]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>16:54.243</t>
+          <t>15:20.732</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -30782,28 +30907,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6311848</v>
+        <v>6172013</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cara Lockwood (RollCo)</t>
+          <t>Markel Sierra</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>19:54.102</t>
+          <t>16:54.243</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -30812,11 +30937,11 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6311857</v>
+        <v>6311848</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
+          <t>Cara Lockwood (RollCo)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -30826,14 +30951,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>19:18.935</t>
+          <t>19:54.102</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30842,28 +30967,28 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6715306</v>
+        <v>6311857</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Jay Rowe</t>
+          <t>L ook mum no hands (RollCo)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>17:06.997</t>
+          <t>19:18.935</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30872,47 +30997,47 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6740030</v>
+        <v>6478454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Takuma Kanehira</t>
+          <t>Jason Spiker (DDIRC)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>19:35.776</t>
+          <t>23:24.692</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6842342</v>
+        <v>6715306</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
+          <t>Jay Rowe</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>22:56.074</t>
+          <t>17:06.997</t>
         </is>
       </c>
     </row>
@@ -30924,32 +31049,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6853346</v>
+        <v>6740030</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthieu De Smet </t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Takuma Kanehira</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14:08.328</t>
+          <t>19:35.776</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -30958,17 +31079,21 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6856298</v>
+        <v>6842342</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Connor Wilm</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>Ed Ferebee (Rhino)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>22:44.080</t>
+          <t>22:56.074</t>
         </is>
       </c>
     </row>
@@ -30980,161 +31105,157 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6863000</v>
+        <v>6853346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Markus Schweizer</t>
+          <t xml:space="preserve">Matthieu De Smet </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WEz pb Cycling District</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>13:31.808</t>
+          <t>14:08.328</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6952720</v>
+        <v>6856298</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Remco Vanhoutte [A-P-V]</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>A-P-V</t>
-        </is>
-      </c>
+          <t>Connor Wilm</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>16:04.572</t>
+          <t>22:44.080</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6977747</v>
+        <v>6863000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Joe Limke</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>Markus Schweizer</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>WEz pb Cycling District</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>29:31.924</t>
+          <t>13:31.808</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6991072</v>
+        <v>6952720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Remco Vanhoutte [A-P-V]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>19:44.722</t>
+          <t>16:04.572</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6997588</v>
+        <v>6977747</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
-        </is>
-      </c>
+          <t>Joe Limke</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20:22.224</t>
+          <t>29:31.924</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7053041</v>
+        <v>6991072</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>William Smith (RollCo/TNP)</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -31144,7 +31265,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>17:39.478</t>
+          <t>19:44.722</t>
         </is>
       </c>
     </row>
@@ -31160,37 +31281,41 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7229860</v>
+        <v>6997588</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Olivier Simonin</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>19:41.655</t>
+          <t>20:22.224</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7291113</v>
+        <v>7053041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ian Stokes</t>
+          <t>William Smith (RollCo/TNP)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -31200,171 +31325,171 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>22:09.403</t>
+          <t>17:39.478</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7315891</v>
+        <v>7229860</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Joe Kierce</t>
+          <t>Olivier Simonin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>15:46.930</t>
+          <t>19:41.655</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7410098</v>
+        <v>7291113</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Luke van Harskamp</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>Ian Stokes</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>17:30.708</t>
+          <t>22:09.403</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7455653</v>
+        <v>7315891</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Joe Kierce</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>21:45.940</t>
+          <t>15:46.930</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7721955</v>
+        <v>7410098</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ethan Smith</t>
+          <t>Luke van Harskamp</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>17:36.649</t>
+          <t>17:30.708</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7775038</v>
+        <v>7455653</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Alex Leonard</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>Justin Draper [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20:57.635</t>
+          <t>21:45.940</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7779078</v>
+        <v>7721955</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>David Irwin</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Ethan Smith</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>21:28.793</t>
+          <t>17:36.649</t>
         </is>
       </c>
     </row>
@@ -31376,71 +31501,71 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7799511</v>
+        <v>7775038</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Alex Leonard</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>18:29.532</t>
+          <t>20:57.635</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7932168</v>
+        <v>7779078</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>John Rae</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>27:07.445</t>
+          <t>21:28.793</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8149174</v>
+        <v>7799511</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -31450,57 +31575,113 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>21:04.413</t>
+          <t>18:29.532</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8389020</v>
+        <v>7932168</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tibo Peeters</t>
+          <t>John Rae</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>13:49.473</t>
+          <t>27:07.445</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>8149174</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>21:04.413</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>8389020</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tibo Peeters</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>13:49.473</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
         <v>8436825</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>anas samman</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
         <is>
           <t>18:13.739</t>
         </is>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4063,18 +4063,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>Heinz Ensen (Herd)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>HERD</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>03:25:47.064</t>
+          <t>03:21:20.600</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4099,27 +4103,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>03:26:15.833</t>
+          <t>03:24:43.593</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>28.769</t>
+          <t>03:22.993</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -4134,7 +4138,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4144,22 +4148,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>03:59:43.471</t>
+          <t>03:25:47.064</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>33:56.407</t>
+          <t>04:26.464</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -4179,27 +4179,31 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sem VH</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>COERS</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>01:40:04.671</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+          <t>03:26:15.833</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>04:55.233</t>
+        </is>
+      </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -4220,18 +4224,26 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>2. Burrito &amp;#127791;</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01:41:56.190</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
+          <t>03:59:43.471</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>38:22.871</t>
+        </is>
+      </c>
       <c r="H107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
@@ -4247,22 +4259,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>Sem VH</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>01:42:17.110</t>
+          <t>01:40:04.671</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -4283,18 +4295,18 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Luke van Harskamp</t>
+          <t>Thomas Mutz</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01:44:22.993</t>
+          <t>01:41:56.190</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -4320,7 +4332,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4330,7 +4342,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>01:46:07.754</t>
+          <t>01:42:17.110</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -4351,22 +4363,18 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RollCo</t>
-        </is>
-      </c>
+          <t>Luke van Harskamp</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>01:48:57.345</t>
+          <t>01:44:22.993</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -4382,27 +4390,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01:49:14.898</t>
+          <t>01:46:07.754</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -4418,27 +4426,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>L ook mum no hands (RollCo)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>01:49:41.475</t>
+          <t>01:48:57.345</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -4459,22 +4467,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Heinz Ensen (Herd)</t>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>HERD</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>01:50:03.187</t>
+          <t>01:49:14.898</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -4490,27 +4498,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>01:50:24.252</t>
+          <t>01:49:41.475</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -4526,27 +4534,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mathieu Brisebois-Boies (Rhinos)</t>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>01:51:57.935</t>
+          <t>01:50:24.252</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -4572,17 +4580,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Mathieu Brisebois-Boies (Rhinos)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>01:53:14.134</t>
+          <t>01:51:57.935</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -4608,17 +4616,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>01:54:35.745</t>
+          <t>01:53:14.134</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -4634,27 +4642,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
+          <t>Neil Rogers</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>01:58:22.580</t>
+          <t>01:54:35.745</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -4670,17 +4678,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Phil Cox (TNP)</t>
+          <t>Justin Draper [Fellowship]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4690,7 +4698,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>02:51:32.259</t>
+          <t>01:58:22.580</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -4711,22 +4719,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Phil Cox (TNP)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>03:06:34.515</t>
+          <t>02:51:32.259</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -4742,32 +4750,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Oliver Slowboi (TNP)</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>01:13:09.902</t>
+          <t>03:06:34.515</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -4783,22 +4791,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Andrew Stamp(RollCo)</t>
+          <t>Oliver Slowboi (TNP)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>01:29:00.740</t>
+          <t>01:13:09.902</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -4824,17 +4832,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t>Andrew Stamp(RollCo)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>01:32:18.744</t>
+          <t>01:29:00.740</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -4860,17 +4868,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos Barreiros </t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>01:33:07.466</t>
+          <t>01:32:18.744</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -4896,7 +4904,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t xml:space="preserve">Carlos Barreiros </t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4906,7 +4914,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>02:21:35.976</t>
+          <t>01:33:07.466</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -4922,32 +4930,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Jeremy Gourd (FUTURE)</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FUTR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>16:19.801</t>
+          <t>02:21:35.976</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -4958,23 +4966,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>F. Lofsgaard (Oslofjord)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Jeremy Gourd (FUTURE)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>FUTR</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>17:05.523</t>
+          <t>16:19.801</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -4995,22 +5007,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ivar  Bringedal [V] </t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Vikings</t>
-        </is>
-      </c>
+          <t>F. Lofsgaard (Oslofjord)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>17:19.121</t>
+          <t>17:05.523</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -5031,22 +5039,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Lance Loveday (Victory Velo Racing)</t>
+          <t xml:space="preserve">Jan Ivar  Bringedal [V] </t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Victory Velo Racing</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18:34.306</t>
+          <t>17:19.121</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -5067,22 +5075,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tonne (DIRT)</t>
+          <t>Lance Loveday (Victory Velo Racing)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Victory Velo Racing</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>18:58.125</t>
+          <t>18:34.306</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -5103,22 +5111,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Steffen Schulz (HCH.CC)</t>
+          <t>Tonne (DIRT)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HCH.CC</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>19:05.995</t>
+          <t>18:58.125</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -5134,27 +5142,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chris Beardsell (TNP)</t>
+          <t>Steffen Schulz (HCH.CC)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HCH.CC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>19:25.664</t>
+          <t>19:05.995</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -5175,22 +5183,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Alexey Tikhov (B)</t>
+          <t>Chris Beardsell (TNP)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>20:18.104</t>
+          <t>19:25.664</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -5211,18 +5219,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Alex Leonard</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>Alexey Tikhov (B)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>MTBtraining</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>20:57.635</t>
+          <t>20:18.104</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -5243,18 +5255,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Kashiwa no Ha Campus Seikeigeka</t>
+          <t>Alex Leonard</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>22:08.029</t>
+          <t>20:57.635</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -5275,18 +5287,18 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Connor Wilm</t>
+          <t>Kashiwa no Ha Campus Seikeigeka</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>22:44.080</t>
+          <t>22:08.029</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5302,27 +5314,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Chris Cayford</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Team Velos</t>
-        </is>
-      </c>
+          <t>Connor Wilm</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>32:59.583</t>
+          <t>22:44.080</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -5338,27 +5346,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Rob Wainwright  (Corona Zwifters)</t>
+          <t>Chris Cayford</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Corona Zwifters</t>
+          <t>Team Velos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>33:34.276</t>
+          <t>32:59.583</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -5379,22 +5387,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erlend Olsen </t>
+          <t>Rob Wainwright  (Corona Zwifters)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>BAB</t>
+          <t>Corona Zwifters</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>34:11.228</t>
+          <t>33:34.276</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -5420,17 +5428,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>kristian Mikkelsen</t>
+          <t xml:space="preserve">Erlend Olsen </t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>CK 2020</t>
+          <t>BAB</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>34:15.757</t>
+          <t>34:11.228</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5456,17 +5464,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Niclas M&amp;aelig;hle (TNP)</t>
+          <t>kristian Mikkelsen</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>CK 2020</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>34:43.721</t>
+          <t>34:15.757</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -5492,13 +5500,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ben dart</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>Niclas M&amp;aelig;hle (TNP)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>35:17.401</t>
+          <t>34:43.721</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -5524,17 +5536,13 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>ben dart</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>35:34.069</t>
+          <t>35:17.401</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -5550,7 +5558,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5560,17 +5568,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Adam Britton</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>35:41.512</t>
+          <t>35:34.069</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5596,17 +5604,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Christian Brown (Rhino)</t>
+          <t>Adam Britton</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>35:51.007</t>
+          <t>35:41.512</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5622,27 +5630,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>David Fisher (Team CLS)</t>
+          <t>Christian Brown (Rhino)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Team CLS</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>35:55.766</t>
+          <t>35:51.007</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -5658,27 +5666,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Hans Fischer</t>
+          <t>David Fisher (Team CLS)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>36:22.857</t>
+          <t>35:55.766</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -5699,22 +5707,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mark Williams (RollCo)</t>
+          <t>Hans Fischer</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>36:33.721</t>
+          <t>36:22.857</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -5735,22 +5743,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Jorelle  Hernandez (TZP)</t>
+          <t>Mark Williams (RollCo)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>TZP</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>37:14.815</t>
+          <t>36:33.721</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -5771,22 +5779,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Phillip Reynolds (LEQPxHunters)</t>
+          <t>Jorelle  Hernandez (TZP)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
+          <t>TZP</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>37:39.268</t>
+          <t>37:14.815</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -5807,22 +5815,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+          <t>Phillip Reynolds (LEQPxHunters)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>38:09.320</t>
+          <t>37:39.268</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -5843,18 +5851,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>K.O.&amp;#128048;[TMR]</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>David Iba&amp;ntilde;ez  (HISP)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>38:31.471</t>
+          <t>38:09.320</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -5870,7 +5882,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5880,17 +5892,13 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Nathan Gerdts (SISU)</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>K.O.&amp;#128048;[TMR]</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>39:03.466</t>
+          <t>38:31.471</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -5906,7 +5914,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5916,17 +5924,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Daniel Kent</t>
+          <t>Nathan Gerdts (SISU)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>39:06.280</t>
+          <t>39:03.466</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -5947,18 +5955,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Brian Pryor</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
+          <t>Daniel Kent</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>39:27.783</t>
+          <t>39:06.280</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -5979,18 +5991,18 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cristian Montero</t>
+          <t>Brian Pryor</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>39:28.748</t>
+          <t>39:27.783</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -6006,23 +6018,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Pedro Leal</t>
+          <t>Cristian Montero</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>42:04.672</t>
+          <t>39:28.748</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -6038,27 +6050,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Jens Liljekrok [OUT]&amp;#128023;</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
+          <t>Pedro Leal</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>48:55.896</t>
+          <t>42:04.672</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -6074,23 +6082,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Blair Rouse KSBT</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t xml:space="preserve">	Jens Liljekrok [OUT]&amp;#128023;</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>48:58.105</t>
+          <t>48:55.896</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -6106,23 +6118,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ryan Quinn</t>
+          <t>Blair Rouse KSBT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>50:35.813</t>
+          <t>48:58.105</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -6143,22 +6155,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Nikolay Hristozov</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Ryan Quinn</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>51:35.555</t>
+          <t>50:35.813</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -6174,7 +6182,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6184,17 +6192,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  Steelo [GXY] </t>
+          <t>Nikolay Hristozov</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>51:56.202</t>
+          <t>51:35.555</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -6210,27 +6218,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Trevan Burn [Rhino]</t>
+          <t xml:space="preserve">...  Steelo [GXY] </t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>51:56.407</t>
+          <t>51:56.202</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -6251,22 +6259,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t>Trevan Burn [Rhino]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>51:57.484</t>
+          <t>51:56.407</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -6287,22 +6295,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Juan The One</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>51:57.589</t>
+          <t>51:57.484</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
@@ -6323,18 +6331,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Duncan Donnay</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
+          <t>Juan The One</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>52:00.120</t>
+          <t>51:57.589</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
@@ -6355,22 +6367,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Ronny Holen [ZU4R]</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>ZU4R eSport</t>
-        </is>
-      </c>
+          <t>Duncan Donnay</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>52:01.437</t>
+          <t>52:00.120</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
@@ -6391,22 +6399,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Stephen Collins</t>
+          <t>Ronny Holen [ZU4R]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>VRR</t>
+          <t>ZU4R eSport</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>52:01.710</t>
+          <t>52:01.437</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
@@ -6427,18 +6435,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Benjamin Howe</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
+          <t>Stephen Collins</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>VRR</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>52:28.109</t>
+          <t>52:01.710</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
@@ -6459,18 +6471,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tim Baldwin</t>
+          <t>Benjamin Howe</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>52:43.417</t>
+          <t>52:28.109</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
@@ -6491,18 +6503,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>mark R</t>
+          <t>Tim Baldwin</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>53:06.439</t>
+          <t>52:43.417</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -6523,22 +6535,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Rex  Tan</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>ZPH Philippines</t>
-        </is>
-      </c>
+          <t>mark R</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>53:11.780</t>
+          <t>53:06.439</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -6559,18 +6567,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Casey Morgan</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
+          <t>Rex  Tan</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ZPH Philippines</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>53:14.384</t>
+          <t>53:11.780</t>
         </is>
       </c>
       <c r="G174" t="inlineStr"/>
@@ -6591,18 +6603,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Joshua Bramah</t>
+          <t>Casey Morgan</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>54:07.843</t>
+          <t>53:14.384</t>
         </is>
       </c>
       <c r="G175" t="inlineStr"/>
@@ -6628,17 +6640,13 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Antonie Vervenne</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>CMC</t>
-        </is>
-      </c>
+          <t>Joshua Bramah</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>54:25.661</t>
+          <t>54:07.843</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -6659,22 +6667,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Sam Mack (BPCC)</t>
+          <t>Antonie Vervenne</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>BPCC</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>54:38.070</t>
+          <t>54:25.661</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -6690,7 +6698,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6700,13 +6708,17 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Kasper Steadywheel</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
+          <t>Sam Mack (BPCC)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>BPCC</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>54:41.448</t>
+          <t>54:38.070</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -6722,7 +6734,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6732,17 +6744,13 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Chris Cremer</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Kasper Steadywheel</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>54:58.285</t>
+          <t>54:41.448</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
@@ -6763,22 +6771,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Marco Roetert Steenbruggen</t>
+          <t>Chris Cremer</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TeamNL</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>55:01.809</t>
+          <t>54:58.285</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -6804,17 +6812,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>D Welch</t>
+          <t>Marco Roetert Steenbruggen</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ROCA</t>
+          <t>TeamNL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>55:01.843</t>
+          <t>55:01.809</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -6830,23 +6838,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Stuart  Campbell</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
+          <t>D Welch</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>ROCA</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>55:09.451</t>
+          <t>55:01.843</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -6862,27 +6874,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>JV Allstar</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Stuart  Campbell</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>55:10.094</t>
+          <t>55:09.451</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -6903,18 +6911,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Tim van Reusel</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
+          <t>JV Allstar</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>55:17.063</t>
+          <t>55:10.094</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
@@ -6935,22 +6947,18 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Barrie &amp;#128059;&amp;#10084;&amp;#65039;&amp;#128060; (Rhino)</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Tim van Reusel</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>57:23.726</t>
+          <t>55:17.063</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -6966,23 +6974,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Jerome Wigger</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
+          <t>Barrie &amp;#128059;&amp;#10084;&amp;#65039;&amp;#128060; (Rhino)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>01:00:47.732</t>
+          <t>57:23.726</t>
         </is>
       </c>
       <c r="G186" t="inlineStr"/>
@@ -6998,7 +7010,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7008,13 +7020,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Eugene Shuster</t>
+          <t>Jerome Wigger</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>01:03:18.565</t>
+          <t>01:00:47.732</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -7035,18 +7047,18 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>olivier fonquerne</t>
+          <t>Eugene Shuster</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>01:29:26.948</t>
+          <t>01:03:18.565</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -7057,12 +7069,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7072,26 +7084,18 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>olivier fonquerne</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>03:30:26.028</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:29:26.948</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -7112,7 +7116,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7122,12 +7126,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>03:35:39.627</t>
+          <t>03:30:26.028</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>05:13.599</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -7147,12 +7151,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7162,12 +7166,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>03:52:37.832</t>
+          <t>03:35:39.627</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>22:11.804</t>
+          <t>05:13.599</t>
         </is>
       </c>
       <c r="H191" t="n">
@@ -7187,12 +7191,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7202,12 +7206,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>03:54:07.411</t>
+          <t>03:52:37.832</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>23:41.383</t>
+          <t>22:11.804</t>
         </is>
       </c>
       <c r="H192" t="n">
@@ -7222,32 +7226,36 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Simon Baker</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>01:52:19.710</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+          <t>03:54:07.411</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>23:41.383</t>
+        </is>
+      </c>
       <c r="H193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -7258,7 +7266,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7268,18 +7276,26 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Olivier Simonin</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
+          <t>Andy Morton (TNP)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>01:52:50.242</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr"/>
+          <t>04:01:16.001</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>30:49.973</t>
+        </is>
+      </c>
       <c r="H194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
@@ -7290,27 +7306,23 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>01:58:21.471</t>
+          <t>01:52:50.242</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
@@ -7331,12 +7343,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7346,7 +7358,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>02:06:33.477</t>
+          <t>01:58:21.471</t>
         </is>
       </c>
       <c r="G196" t="inlineStr"/>
@@ -7498,28 +7510,32 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Prz Luca</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
+          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>SZ</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>20:25.170</t>
+          <t>02:28:57.045</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -7535,18 +7551,18 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Matt Whisker</t>
+          <t>Prz Luca</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>20:44.463</t>
+          <t>20:25.170</t>
         </is>
       </c>
       <c r="G202" t="inlineStr"/>
@@ -7567,22 +7583,18 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Ian Stokes</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Matt Whisker</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>22:09.403</t>
+          <t>20:44.463</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
@@ -7598,27 +7610,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Michael Leesing</t>
+          <t>Ian Stokes</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>TBR Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>33:36.908</t>
+          <t>22:09.403</t>
         </is>
       </c>
       <c r="G204" t="inlineStr"/>
@@ -7639,22 +7651,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Dag Eidesen</t>
+          <t>Michael Leesing</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>TBR Racing</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>33:36.908</t>
         </is>
       </c>
       <c r="G205" t="inlineStr"/>
@@ -7670,27 +7682,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t>Dag Eidesen</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="G206" t="inlineStr"/>
@@ -7706,27 +7718,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Scott Henderson (BON - GXY)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:06.428</t>
         </is>
       </c>
       <c r="G207" t="inlineStr"/>
@@ -7742,27 +7754,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>sheldon White (BAKPDL B3)</t>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>BAKPDL</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>39:05.483</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="G208" t="inlineStr"/>
@@ -7783,18 +7795,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Richard Finch</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
+          <t>sheldon White (BAKPDL B3)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>BAKPDL</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>39:07.515</t>
+          <t>39:05.483</t>
         </is>
       </c>
       <c r="G209" t="inlineStr"/>
@@ -7815,22 +7831,18 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Dirk Richter</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>ZRG</t>
-        </is>
-      </c>
+          <t>Richard Finch</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>39:07.844</t>
+          <t>39:07.515</t>
         </is>
       </c>
       <c r="G210" t="inlineStr"/>
@@ -7856,17 +7868,17 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Ben Hartopp [SNOW]</t>
+          <t>Dirk Richter</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ZRG</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>39:07.844</t>
         </is>
       </c>
       <c r="G211" t="inlineStr"/>
@@ -7882,7 +7894,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7892,17 +7904,17 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Jorge Ar&amp;eacute;valo</t>
+          <t>Ben Hartopp [SNOW]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>39:26.642</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="G212" t="inlineStr"/>
@@ -7923,22 +7935,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Roberto Delgado Hynes</t>
+          <t>Jorge Ar&amp;eacute;valo</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Velo&amp;#039;Z</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>39:46.669</t>
+          <t>39:26.642</t>
         </is>
       </c>
       <c r="G213" t="inlineStr"/>
@@ -7954,7 +7966,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7964,7 +7976,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>John Swift</t>
+          <t>Roberto Delgado Hynes</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7974,7 +7986,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>39:51.976</t>
+          <t>39:46.669</t>
         </is>
       </c>
       <c r="G214" t="inlineStr"/>
@@ -7995,18 +8007,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Sebastian Borquez</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
+          <t>John Swift</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>40:39.786</t>
+          <t>39:51.976</t>
         </is>
       </c>
       <c r="G215" t="inlineStr"/>
@@ -8027,22 +8043,18 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andy Westall </t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>SWCC</t>
-        </is>
-      </c>
+          <t>Sebastian Borquez</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>40:55.101</t>
+          <t>40:39.786</t>
         </is>
       </c>
       <c r="G216" t="inlineStr"/>
@@ -8063,22 +8075,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Pearce </t>
+          <t xml:space="preserve">Andy Westall </t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>TBG</t>
+          <t>SWCC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>40:55.101</t>
         </is>
       </c>
       <c r="G217" t="inlineStr"/>
@@ -8094,7 +8106,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8104,17 +8116,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Mads Gronbek [DBR]</t>
+          <t xml:space="preserve">John Pearce </t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>TBG</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>42:08.148</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="G218" t="inlineStr"/>
@@ -8130,23 +8142,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Andrew Lowrie</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
+          <t>Mads Gronbek [DBR]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>DBR</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>42:29.930</t>
+          <t>42:08.148</t>
         </is>
       </c>
       <c r="G219" t="inlineStr"/>
@@ -8162,27 +8178,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Mark SMITH6725</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>CTT</t>
-        </is>
-      </c>
+          <t>Andrew Lowrie</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>42:29.930</t>
         </is>
       </c>
       <c r="G220" t="inlineStr"/>
@@ -8198,23 +8210,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Magnus Morel</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr"/>
+          <t>Mark SMITH6725</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>CTT</t>
+        </is>
+      </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>44:58.275</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="G221" t="inlineStr"/>
@@ -8230,7 +8246,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8240,13 +8256,13 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Sam Godfrey</t>
+          <t>Magnus Morel</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>45:17.857</t>
+          <t>44:58.275</t>
         </is>
       </c>
       <c r="G222" t="inlineStr"/>
@@ -8267,18 +8283,18 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Christophe Chris [BIKES-FR]</t>
+          <t>Sam Godfrey</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>50:43.002</t>
+          <t>45:17.857</t>
         </is>
       </c>
       <c r="G223" t="inlineStr"/>
@@ -8299,18 +8315,18 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adam Sternfield </t>
+          <t>Christophe Chris [BIKES-FR]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>51:57.148</t>
+          <t>50:43.002</t>
         </is>
       </c>
       <c r="G224" t="inlineStr"/>
@@ -8326,27 +8342,23 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Morten  Bach  Jepsen</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>DBR</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Adam Sternfield </t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>52:58.678</t>
+          <t>51:57.148</t>
         </is>
       </c>
       <c r="G225" t="inlineStr"/>
@@ -8362,27 +8374,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
+          <t>Morten  Bach  Jepsen</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>53:25.685</t>
+          <t>52:58.678</t>
         </is>
       </c>
       <c r="G226" t="inlineStr"/>
@@ -9302,27 +9314,23 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>eiji yama</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>01:43:08.050</t>
+          <t>01:36:55.390</t>
         </is>
       </c>
       <c r="G253" t="inlineStr"/>
@@ -9333,22 +9341,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9358,22 +9366,18 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>04:01:35.392</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:43:08.050</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9383,27 +9387,23 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Park Jinhea3000[TEC]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>02:08:02.879</t>
+          <t>01:44:16.860</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -9419,27 +9419,31 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>02:09:46.608</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr"/>
+          <t>04:01:35.392</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
       <c r="H256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257">
@@ -9455,27 +9459,27 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>01:17:01.165</t>
+          <t>02:08:02.879</t>
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -9486,32 +9490,32 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Aidan Novis (RHINO)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>01:24:31.213</t>
+          <t>02:09:46.608</t>
         </is>
       </c>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -9522,27 +9526,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>01:26:11.009</t>
+          <t>01:17:01.165</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
@@ -9568,22 +9572,22 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Matt Taylor (Charlies Angels Full Throttle)</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CAFT</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>21:38.777</t>
+          <t>01:24:31.213</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -9604,22 +9608,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Stefaan Lampaert</t>
+          <t>Brian Benner (HERC)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>BZR eCycling Club</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>22:33.716</t>
+          <t>01:26:11.009</t>
         </is>
       </c>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -9635,18 +9639,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>FELIX CALVO POO</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
+          <t>Matt Taylor (Charlies Angels Full Throttle)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>CAFT</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>22:39.179</t>
+          <t>21:38.777</t>
         </is>
       </c>
       <c r="G262" t="inlineStr"/>
@@ -9662,27 +9670,27 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Julia Umbrello [eSRT]</t>
+          <t>Stefaan Lampaert</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>BZR eCycling Club</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>22:54.914</t>
+          <t>22:33.716</t>
         </is>
       </c>
       <c r="G263" t="inlineStr"/>
@@ -9698,23 +9706,23 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Austin H</t>
+          <t>FELIX CALVO POO</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>24:27.518</t>
+          <t>22:39.179</t>
         </is>
       </c>
       <c r="G264" t="inlineStr"/>
@@ -9730,23 +9738,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Ryan Gower</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr"/>
+          <t>Julia Umbrello [eSRT]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>25:21.604</t>
+          <t>22:54.914</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -9767,18 +9779,18 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Ian Lovely</t>
+          <t>Austin H</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>26:35.426</t>
+          <t>24:27.518</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
@@ -9794,23 +9806,23 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Joe Limke</t>
+          <t>Ryan Gower</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>29:31.924</t>
+          <t>25:21.604</t>
         </is>
       </c>
       <c r="G267" t="inlineStr"/>
@@ -9831,22 +9843,18 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>COALITION</t>
-        </is>
-      </c>
+          <t>Ian Lovely</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>30:35.758</t>
+          <t>26:35.426</t>
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
@@ -9862,23 +9870,23 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
+          <t>Joe Limke</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>29:31.924</t>
         </is>
       </c>
       <c r="G269" t="inlineStr"/>
@@ -9899,18 +9907,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr"/>
+          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>45:14.312</t>
+          <t>30:35.758</t>
         </is>
       </c>
       <c r="G270" t="inlineStr"/>
@@ -9936,13 +9948,13 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>@ arrows</t>
+          <t>Matt Jones</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>44:04.011</t>
         </is>
       </c>
       <c r="G271" t="inlineStr"/>
@@ -9963,22 +9975,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Philip Gill</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>45:14.312</t>
         </is>
       </c>
       <c r="G272" t="inlineStr"/>
@@ -9994,27 +10002,23 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Rikke Rasmussen #DBM#</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>DBM</t>
-        </is>
-      </c>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:16.878</t>
         </is>
       </c>
       <c r="G273" t="inlineStr"/>
@@ -10040,17 +10044,17 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
+          <t>Kim Bryan &amp;#127800;</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>45:41.917</t>
         </is>
       </c>
       <c r="G274" t="inlineStr"/>
@@ -10076,17 +10080,17 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Adrian ZC</t>
+          <t>Rikke Rasmussen #DBM#</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Momentum CR</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>51:07.527</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="G275" t="inlineStr"/>
@@ -10112,17 +10116,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Jamie Roy</t>
+          <t>Mailan Kimsuan [ZIRT]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Stages Cycling</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>57:26.520</t>
+          <t>50:00.950</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
@@ -10138,27 +10142,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Ant Vine</t>
+          <t>Adrian ZC</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Momentum CR</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>57:31.627</t>
+          <t>51:07.527</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
@@ -10179,22 +10183,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>sean carter [WMZ]</t>
+          <t>Jamie Roy</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>Stages Cycling</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>57:32.338</t>
+          <t>57:26.520</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
@@ -10215,18 +10219,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Jason Gillespie (Orkney CC)</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
+          <t>Ant Vine</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>58:45.630</t>
+          <t>57:31.627</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
@@ -10247,22 +10255,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Arif Wijayanto</t>
+          <t>sean carter [WMZ]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>ZID</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>01:02:24.672</t>
+          <t>57:32.338</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
@@ -10283,22 +10291,18 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Armitage  Herc </t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Jason Gillespie (Orkney CC)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>01:03:30.326</t>
+          <t>58:45.630</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -10314,27 +10318,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Ron Clarino TeamODZ</t>
+          <t>Arif Wijayanto</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>TeamODZ</t>
+          <t>ZID</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>01:05:07.663</t>
+          <t>01:02:24.672</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
@@ -10360,13 +10364,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Danny Postell GCC</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr"/>
+          <t xml:space="preserve">Robert Armitage  Herc </t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>01:05:25.276</t>
+          <t>01:03:30.326</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
@@ -10382,23 +10390,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>&amp;#321;ukasz Karasi&amp;#324;ski</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr"/>
+          <t>Ron Clarino TeamODZ</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>TeamODZ</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>01:09:46.960</t>
+          <t>01:05:07.663</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
@@ -10409,7 +10421,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10424,13 +10436,13 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>John Rae</t>
+          <t>Danny Postell GCC</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>27:07.445</t>
+          <t>01:05:25.276</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
@@ -10441,7 +10453,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10456,13 +10468,13 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Philip Gkikas CAAT &amp;#128076;</t>
+          <t>&amp;#321;ukasz Karasi&amp;#324;ski</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>28:25.665</t>
+          <t>01:09:46.960</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
@@ -10483,18 +10495,18 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Leslie Koh</t>
+          <t>John Rae</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>51:08.233</t>
+          <t>27:07.445</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
@@ -10515,18 +10527,18 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Stuart Haigh</t>
+          <t xml:space="preserve"> Philip Gkikas CAAT &amp;#128076;</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>58:30.748</t>
+          <t>28:25.665</t>
         </is>
       </c>
       <c r="G288" t="inlineStr"/>
@@ -10547,22 +10559,86 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Benjamin Sommervoll</t>
+          <t>Leslie Koh</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>01:01:28.928</t>
+          <t>51:08.233</t>
         </is>
       </c>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Stuart Haigh</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>58:30.748</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Snr</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Benjamin Sommervoll</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>01:01:28.928</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13396,7 +13472,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>05:16:09.650</t>
+          <t>06:48:33.533</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -13405,7 +13481,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -13433,11 +13509,11 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:32:23.883</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -13676,12 +13752,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COERS</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01:40:04.671</t>
+          <t>03:21:20.600</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -13690,11 +13766,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>33:33.586</t>
+          <t>37:22.000</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -13702,7 +13778,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>48:57.524</t>
+          <t>51:56.322</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -13710,7 +13786,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>17:33.561</t>
+          <t>20:44.865</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -13718,11 +13794,11 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:31:17.413</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -13733,12 +13809,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01:49:49.731</t>
+          <t>01:40:04.671</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -13751,7 +13827,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>35:41.512</t>
+          <t>33:33.586</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -13759,7 +13835,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>55:10.094</t>
+          <t>48:57.524</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -13767,7 +13843,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>18:58.125</t>
+          <t>17:33.561</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -13790,12 +13866,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HERD</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01:50:03.187</t>
+          <t>01:49:49.731</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -13808,7 +13884,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>37:22.000</t>
+          <t>35:41.512</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -13816,7 +13892,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>51:56.322</t>
+          <t>55:10.094</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -13824,7 +13900,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>20:44.865</t>
+          <t>18:58.125</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -15505,7 +15581,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>05:45:17.311</t>
+          <t>07:39:59.835</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -15514,7 +15590,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -15542,11 +15618,11 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:54:42.524</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -15785,12 +15861,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>20:22.224</t>
+          <t>02:28:57.045</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15799,7 +15875,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -15811,27 +15887,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>53:25.685</t>
         </is>
       </c>
       <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
         <v>0</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>20:22.224</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:35:31.360</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -15842,12 +15918,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TBR Racing</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>33:36.908</t>
+          <t>20:22.224</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15860,11 +15936,11 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>33:36.908</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -15876,11 +15952,11 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>20:22.224</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -15899,12 +15975,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>TBR Racing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>33:36.908</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15917,7 +15993,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>33:36.908</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15956,12 +16032,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>38:04.051</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15974,7 +16050,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>38:04.051</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -16013,12 +16089,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:04.051</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -16031,7 +16107,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:04.051</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -16070,12 +16146,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BAKPDL</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>39:05.483</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,7 +16164,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>39:05.483</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -16127,12 +16203,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZRG</t>
+          <t>BAKPDL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>39:07.844</t>
+          <t>39:05.483</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16145,7 +16221,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>39:07.844</t>
+          <t>39:05.483</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16184,12 +16260,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ZRG</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>39:07.844</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16202,7 +16278,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>39:07.844</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16241,12 +16317,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>39:26.642</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16259,7 +16335,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>39:26.642</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16298,12 +16374,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SWCC</t>
+          <t>Velo&amp;#039;Z</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>40:55.101</t>
+          <t>39:26.642</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16316,7 +16392,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>40:55.101</t>
+          <t>39:26.642</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16355,12 +16431,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TBG</t>
+          <t>SWCC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>40:55.101</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16373,7 +16449,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>40:55.101</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16412,12 +16488,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CTT</t>
+          <t>TBG</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16430,7 +16506,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16469,12 +16545,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>CTT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>53:25.685</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16487,19 +16563,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
         <v>0</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>53:25.685</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>1</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -17897,7 +17973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18268,7 +18344,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4166463</v>
+        <v>3614977</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -18282,33 +18358,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Heinz Ensen (Herd)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HERD</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>14.418</v>
+        <v>14.033</v>
       </c>
       <c r="I9" t="n">
-        <v>39.254</v>
+        <v>33.531</v>
       </c>
       <c r="J9" t="n">
         <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1005102</v>
+        <v>4166463</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -18317,56 +18397,52 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>14.879</v>
+        <v>14.418</v>
       </c>
       <c r="I10" t="n">
-        <v>38.036</v>
+        <v>39.254</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>1005102</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -18375,72 +18451,72 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>14.251</v>
+        <v>14.879</v>
       </c>
       <c r="I11" t="n">
-        <v>36.92</v>
+        <v>38.036</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7779078</v>
+        <v>9152</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>13.51</v>
+        <v>15.217</v>
       </c>
       <c r="I12" t="n">
-        <v>39.066</v>
+        <v>40.763</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1379058</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -18454,7 +18530,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -18469,22 +18545,22 @@
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>14.296</v>
+        <v>14.251</v>
       </c>
       <c r="I13" t="n">
-        <v>35.821</v>
+        <v>36.92</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>832585</v>
+        <v>7779078</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -18498,7 +18574,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -18507,42 +18583,42 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>15.301</v>
+        <v>13.51</v>
       </c>
       <c r="I14" t="n">
-        <v>46.554</v>
+        <v>39.066</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3294901</v>
+        <v>1379058</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -18551,24 +18627,156 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>15.678</v>
+        <v>14.296</v>
       </c>
       <c r="I15" t="n">
-        <v>41.622</v>
+        <v>35.821</v>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
         <v>20</v>
       </c>
       <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>832585</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>26</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.301</v>
+      </c>
+      <c r="I16" t="n">
+        <v>46.554</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1475359</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Andy Morton (TNP)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15.923</v>
+      </c>
+      <c r="I17" t="n">
+        <v>41.443</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15.678</v>
+      </c>
+      <c r="I18" t="n">
+        <v>41.622</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18581,7 +18789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19184,7 +19392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1005102</v>
+        <v>3614977</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -19193,48 +19401,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Heinz Ensen (Herd)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>225.194</v>
+        <v>218.813</v>
       </c>
       <c r="I8" t="n">
-        <v>126.855</v>
+        <v>132.454</v>
       </c>
       <c r="J8" t="n">
-        <v>63.616</v>
+        <v>61.029</v>
       </c>
       <c r="K8" t="n">
-        <v>41.705</v>
+        <v>34.43</v>
       </c>
       <c r="L8" t="n">
-        <v>35.459</v>
+        <v>31.797</v>
       </c>
       <c r="M8" t="n">
-        <v>436.881</v>
+        <v>452.718</v>
       </c>
       <c r="N8" t="n">
-        <v>456.436</v>
+        <v>454.125</v>
       </c>
       <c r="O8" t="n">
-        <v>923.126</v>
+        <v>859.929</v>
       </c>
       <c r="P8" t="n">
         <v>5</v>
@@ -19246,13 +19454,13 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
         <v>10</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
         <v>10</v>
@@ -19264,7 +19472,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4166463</v>
+        <v>1005102</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -19273,44 +19481,48 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>235.73</v>
+        <v>225.194</v>
       </c>
       <c r="I9" t="n">
-        <v>130.272</v>
+        <v>126.855</v>
       </c>
       <c r="J9" t="n">
-        <v>64.881</v>
+        <v>63.616</v>
       </c>
       <c r="K9" t="n">
-        <v>42.775</v>
+        <v>41.705</v>
       </c>
       <c r="L9" t="n">
-        <v>34.856</v>
+        <v>35.459</v>
       </c>
       <c r="M9" t="n">
-        <v>459.985</v>
+        <v>436.881</v>
       </c>
       <c r="N9" t="n">
-        <v>501.366</v>
+        <v>456.436</v>
       </c>
       <c r="O9" t="n">
-        <v>973.654</v>
+        <v>923.126</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -19319,28 +19531,28 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
         <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
         <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72072</v>
+        <v>9152</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -19354,77 +19566,77 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>340.667</v>
+        <v>248.257</v>
       </c>
       <c r="I10" t="n">
-        <v>169.228</v>
+        <v>137.214</v>
       </c>
       <c r="J10" t="n">
-        <v>85.53100000000001</v>
+        <v>68.46599999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>55.795</v>
+        <v>45.483</v>
       </c>
       <c r="L10" t="n">
-        <v>50.332</v>
+        <v>30.864</v>
       </c>
       <c r="M10" t="n">
-        <v>401.691</v>
+        <v>451.283</v>
       </c>
       <c r="N10" t="n">
-        <v>619.936</v>
+        <v>462.071</v>
       </c>
       <c r="O10" t="n">
-        <v>1249.316</v>
+        <v>890.422</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
         <v>6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>10</v>
       </c>
       <c r="V10" t="n">
         <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>4166463</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -19434,87 +19646,83 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>246.415</v>
+        <v>235.73</v>
       </c>
       <c r="I11" t="n">
-        <v>143.226</v>
+        <v>130.272</v>
       </c>
       <c r="J11" t="n">
-        <v>63.67</v>
+        <v>64.881</v>
       </c>
       <c r="K11" t="n">
-        <v>42.136</v>
+        <v>42.775</v>
       </c>
       <c r="L11" t="n">
-        <v>44.269</v>
+        <v>34.856</v>
       </c>
       <c r="M11" t="n">
-        <v>482.245</v>
+        <v>459.985</v>
       </c>
       <c r="N11" t="n">
-        <v>494.751</v>
+        <v>501.366</v>
       </c>
       <c r="O11" t="n">
-        <v>1013.833</v>
+        <v>973.654</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
         <v>10</v>
-      </c>
-      <c r="T11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U11" t="n">
-        <v>10</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15</v>
       </c>
       <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7779078</v>
+        <v>72072</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>2. Burrito &amp;#127791;</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -19523,64 +19731,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>269.648</v>
+        <v>340.667</v>
       </c>
       <c r="I12" t="n">
-        <v>147.455</v>
+        <v>169.228</v>
       </c>
       <c r="J12" t="n">
-        <v>75.449</v>
+        <v>85.53100000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>36.355</v>
+        <v>55.795</v>
       </c>
       <c r="L12" t="n">
-        <v>35.063</v>
+        <v>50.332</v>
       </c>
       <c r="M12" t="n">
-        <v>484.61</v>
+        <v>401.691</v>
       </c>
       <c r="N12" t="n">
-        <v>510.846</v>
+        <v>619.936</v>
       </c>
       <c r="O12" t="n">
-        <v>994.575</v>
+        <v>1249.316</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
         <v>8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>20</v>
       </c>
       <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1379058</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -19594,7 +19802,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -19603,64 +19811,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>273.644</v>
+        <v>246.415</v>
       </c>
       <c r="I13" t="n">
-        <v>147.985</v>
+        <v>143.226</v>
       </c>
       <c r="J13" t="n">
-        <v>67.021</v>
+        <v>63.67</v>
       </c>
       <c r="K13" t="n">
-        <v>36.63</v>
+        <v>42.136</v>
       </c>
       <c r="L13" t="n">
-        <v>31.796</v>
+        <v>44.269</v>
       </c>
       <c r="M13" t="n">
-        <v>543.125</v>
+        <v>482.245</v>
       </c>
       <c r="N13" t="n">
-        <v>620.603</v>
+        <v>494.751</v>
       </c>
       <c r="O13" t="n">
-        <v>1243.93</v>
+        <v>1013.833</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>832585</v>
+        <v>7779078</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -19674,7 +19882,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -19683,78 +19891,78 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>273.7</v>
+        <v>269.648</v>
       </c>
       <c r="I14" t="n">
-        <v>149.223</v>
+        <v>147.455</v>
       </c>
       <c r="J14" t="n">
-        <v>74.93899999999999</v>
+        <v>75.449</v>
       </c>
       <c r="K14" t="n">
-        <v>43.439</v>
+        <v>36.355</v>
       </c>
       <c r="L14" t="n">
-        <v>39.652</v>
+        <v>35.063</v>
       </c>
       <c r="M14" t="n">
-        <v>553.567</v>
+        <v>484.61</v>
       </c>
       <c r="N14" t="n">
-        <v>619.588</v>
+        <v>510.846</v>
       </c>
       <c r="O14" t="n">
-        <v>1246.293</v>
+        <v>994.575</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3294901</v>
+        <v>1379058</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -19763,60 +19971,300 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>352.066</v>
+        <v>273.644</v>
       </c>
       <c r="I15" t="n">
-        <v>180.835</v>
+        <v>147.985</v>
       </c>
       <c r="J15" t="n">
-        <v>87.05</v>
+        <v>67.021</v>
       </c>
       <c r="K15" t="n">
-        <v>51.897</v>
+        <v>36.63</v>
       </c>
       <c r="L15" t="n">
-        <v>40.523</v>
+        <v>31.796</v>
       </c>
       <c r="M15" t="n">
-        <v>564.154</v>
+        <v>543.125</v>
       </c>
       <c r="N15" t="n">
-        <v>622.101</v>
+        <v>620.603</v>
       </c>
       <c r="O15" t="n">
-        <v>1253.308</v>
+        <v>1243.93</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>5</v>
       </c>
       <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="n">
         <v>10</v>
       </c>
-      <c r="T15" t="n">
+      <c r="X15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>832585</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>149.223</v>
+      </c>
+      <c r="J16" t="n">
+        <v>74.93899999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>43.439</v>
+      </c>
+      <c r="L16" t="n">
+        <v>39.652</v>
+      </c>
+      <c r="M16" t="n">
+        <v>553.567</v>
+      </c>
+      <c r="N16" t="n">
+        <v>619.588</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1246.293</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1475359</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Andy Morton (TNP)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>294.757</v>
+      </c>
+      <c r="I17" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="J17" t="n">
+        <v>76.681</v>
+      </c>
+      <c r="K17" t="n">
+        <v>51.119</v>
+      </c>
+      <c r="L17" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>594.284</v>
+      </c>
+      <c r="N17" t="n">
+        <v>673.405</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1217.002</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>12</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>352.066</v>
+      </c>
+      <c r="I18" t="n">
+        <v>180.835</v>
+      </c>
+      <c r="J18" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="K18" t="n">
+        <v>51.897</v>
+      </c>
+      <c r="L18" t="n">
+        <v>40.523</v>
+      </c>
+      <c r="M18" t="n">
+        <v>564.154</v>
+      </c>
+      <c r="N18" t="n">
+        <v>622.101</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1253.308</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="n">
         <v>10</v>
       </c>
-      <c r="U15" t="n">
+      <c r="T18" t="n">
         <v>10</v>
       </c>
-      <c r="V15" t="n">
+      <c r="U18" t="n">
         <v>10</v>
       </c>
-      <c r="W15" t="n">
+      <c r="V18" t="n">
+        <v>10</v>
+      </c>
+      <c r="W18" t="n">
         <v>20</v>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33326,7 +33774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33413,51 +33861,51 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72072</v>
+        <v>9152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01:48:24.069</t>
+          <t>01:32:23.883</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88513</v>
+        <v>72072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jacob Ingram</t>
+          <t>2. Burrito &amp;#127791;</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -33467,73 +33915,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01:19:44.784</t>
+          <t>01:48:24.069</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>144651</v>
+        <v>83438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sho  Shimada[RD]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SZ</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01:17:12.707</t>
+          <t>01:35:31.360</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>260262</v>
+        <v>88513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>Jacob Ingram</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01:40:32.802</t>
+          <t>01:19:44.784</t>
         </is>
       </c>
     </row>
@@ -33545,90 +33997,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>374410</v>
+        <v>144651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tom R Everested  (TNP)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>BIKELY</t>
-        </is>
-      </c>
+          <t>Sho  Shimada[RD]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01:24:12.287</t>
+          <t>01:17:12.707</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>394612</v>
+        <v>252310</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>Park Jinhea3000[TEC]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01:25:26.808</t>
+          <t>01:44:16.860</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>711180</v>
+        <v>260262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jan [CCC]</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ZLDR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -33638,49 +34082,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01:15:08.760</t>
+          <t>01:40:32.802</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>832585</v>
+        <v>374410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Tom R Everested  (TNP)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01:50:59.699</t>
+          <t>01:24:12.287</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -33689,16 +34133,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1005102</v>
+        <v>394612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -33708,42 +34152,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01:34:38.630</t>
+          <t>01:25:26.808</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1379058</v>
+        <v>711180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Jan [CCC]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>ZLDR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01:50:55.251</t>
+          <t>01:15:08.760</t>
         </is>
       </c>
     </row>
@@ -33759,11 +34203,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1563175</v>
+        <v>832585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -33778,30 +34222,34 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01:43:08.050</t>
+          <t>01:50:59.699</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2213032</v>
+        <v>1005102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -33809,65 +34257,65 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01:14:31.682</t>
+          <t>01:34:38.630</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2881429</v>
+        <v>1260509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>eiji yama</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01:50:59.442</t>
+          <t>01:36:55.390</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3188498</v>
+        <v>1379058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Eric Auder</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>david white (HERC)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>60+</t>
@@ -33875,32 +34323,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01:16:09.689</t>
+          <t>01:50:55.251</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3294901</v>
+        <v>1475359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -33910,7 +34358,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01:53:23.572</t>
+          <t>01:54:42.524</t>
         </is>
       </c>
     </row>
@@ -33922,15 +34370,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3477462</v>
+        <v>1563175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jay ONeil</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -33940,78 +34388,78 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01:31:17.826</t>
+          <t>01:43:08.050</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4166463</v>
+        <v>2213032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
+          <t>Ben Howell</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01:33:50.026</t>
+          <t>01:14:31.682</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4865109</v>
+        <v>2881429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ryo Nakajima(CAP)[FRR]</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FRR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01:14:28.772</t>
+          <t>01:50:59.442</t>
         </is>
       </c>
     </row>
@@ -34023,170 +34471,162 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4980720</v>
+        <v>3188498</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+          <t>Eric Auder</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01:14:10.486</t>
+          <t>01:16:09.689</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5273300</v>
+        <v>3294901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nate Berkopec</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01:22:41.358</t>
+          <t>01:53:23.572</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5402095</v>
+        <v>3477462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Jay ONeil</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01:19:46.295</t>
+          <t>01:31:17.826</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5893609</v>
+        <v>3614977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
+          <t>Heinz Ensen (Herd)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01:19:24.540</t>
+          <t>01:31:17.413</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5959135</v>
+        <v>4166463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ben  Spedding [TNP]</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01:19:25.004</t>
+          <t>01:33:50.026</t>
         </is>
       </c>
     </row>
@@ -34198,18 +34638,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6052283</v>
+        <v>4865109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Henning S&amp;oslash;ndergaard</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Ryo Nakajima(CAP)[FRR]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FRR</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -34217,38 +34661,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01:14:17.401</t>
+          <t>01:14:28.772</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7072713</v>
+        <v>4980720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>olivier fonquerne</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Christopher Keogh [eSRT]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01:29:26.948</t>
+          <t>01:14:10.486</t>
         </is>
       </c>
     </row>
@@ -34260,59 +34708,261 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7552376</v>
+        <v>5273300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HaG TaK</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>Nate Berkopec</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01:14:31.859</t>
+          <t>01:22:41.358</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>5402095</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Quentin Vee [EVO]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01:19:46.295</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5893609</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Aled Jones</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>01:19:24.540</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5959135</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ben  Spedding [TNP]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01:19:25.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6052283</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Henning S&amp;oslash;ndergaard</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>01:14:17.401</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>7072713</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>olivier fonquerne</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01:29:26.948</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7552376</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HaG TaK</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01:14:31.859</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>7779078</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>David Irwin</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>HERC</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>50+</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>01:38:22.582</t>
         </is>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7823,27 +7823,27 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>03:52:37.832</t>
+          <t>03:43:31.151</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>22:11.804</t>
+          <t>13:05.123</t>
         </is>
       </c>
       <c r="H208" t="n">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>03:54:07.411</t>
+          <t>03:52:37.832</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>23:41.383</t>
+          <t>22:11.804</t>
         </is>
       </c>
       <c r="H209" t="n">
@@ -7903,27 +7903,27 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>04:01:16.001</t>
+          <t>03:52:59.161</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>30:49.973</t>
+          <t>22:33.133</t>
         </is>
       </c>
       <c r="H210" t="n">
@@ -7938,28 +7938,36 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Olivier Simonin</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>01:52:50.242</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr"/>
+          <t>03:54:07.411</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>23:41.383</t>
+        </is>
+      </c>
       <c r="H211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -7975,12 +7983,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7990,12 +7998,16 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>01:58:21.471</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr"/>
+          <t>04:01:16.001</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>30:49.973</t>
+        </is>
+      </c>
       <c r="H212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213">
@@ -8006,23 +8018,23 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Jason Spiker (DDIRC)</t>
+          <t>Olivier Simonin</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>02:07:16.610</t>
+          <t>01:52:50.242</t>
         </is>
       </c>
       <c r="G213" t="inlineStr"/>
@@ -8038,32 +8050,28 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Cara Lockwood (RollCo)</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>RollCo</t>
-        </is>
-      </c>
+          <t>Jason Spiker (DDIRC)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>01:01:16.590</t>
+          <t>02:07:16.610</t>
         </is>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
@@ -8074,7 +8082,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8084,17 +8092,17 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Javier (HERC) </t>
+          <t>Cara Lockwood (RollCo)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>01:34:05.691</t>
+          <t>01:01:16.590</t>
         </is>
       </c>
       <c r="G215" t="inlineStr"/>
@@ -8115,18 +8123,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Evan  Carouchio</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
+          <t xml:space="preserve">3 Javier (HERC) </t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>01:40:13.863</t>
+          <t>01:34:05.691</t>
         </is>
       </c>
       <c r="G216" t="inlineStr"/>
@@ -8142,27 +8154,23 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>SZ</t>
-        </is>
-      </c>
+          <t>Evan  Carouchio</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>02:28:57.045</t>
+          <t>01:40:13.863</t>
         </is>
       </c>
       <c r="G217" t="inlineStr"/>
@@ -8178,28 +8186,32 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Prz Luca</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr"/>
+          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>SZ</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>20:25.170</t>
+          <t>02:28:57.045</t>
         </is>
       </c>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -8215,18 +8227,18 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Matt Whisker</t>
+          <t>Prz Luca</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>20:44.463</t>
+          <t>20:25.170</t>
         </is>
       </c>
       <c r="G219" t="inlineStr"/>
@@ -8247,22 +8259,18 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Ian Stokes</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Matt Whisker</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>22:09.403</t>
+          <t>20:44.463</t>
         </is>
       </c>
       <c r="G220" t="inlineStr"/>
@@ -8278,27 +8286,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Michael Leesing</t>
+          <t>Ian Stokes</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>TBR Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>33:36.908</t>
+          <t>22:09.403</t>
         </is>
       </c>
       <c r="G221" t="inlineStr"/>
@@ -8319,22 +8327,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Dag Eidesen</t>
+          <t>Michael Leesing</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>TBR Racing</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>35:10.925</t>
+          <t>33:36.908</t>
         </is>
       </c>
       <c r="G222" t="inlineStr"/>
@@ -8350,27 +8358,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t>Dag Eidesen</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>38:06.428</t>
+          <t>35:10.925</t>
         </is>
       </c>
       <c r="G223" t="inlineStr"/>
@@ -8386,27 +8394,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Sam Park &amp;#127475;&amp;#127487;</t>
+          <t>Scott Henderson (BON - GXY)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>38:58.416</t>
+          <t>38:06.428</t>
         </is>
       </c>
       <c r="G224" t="inlineStr"/>
@@ -8422,27 +8430,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>sheldon White (BAKPDL B3)</t>
+          <t>Sam Park &amp;#127475;&amp;#127487;</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>BAKPDL</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>39:05.483</t>
+          <t>38:58.416</t>
         </is>
       </c>
       <c r="G225" t="inlineStr"/>
@@ -8463,18 +8471,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Richard Finch</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>sheldon White (BAKPDL B3)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>BAKPDL</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>39:07.515</t>
+          <t>39:05.483</t>
         </is>
       </c>
       <c r="G226" t="inlineStr"/>
@@ -8495,22 +8507,18 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Dirk Richter</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>ZRG</t>
-        </is>
-      </c>
+          <t>Richard Finch</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>39:07.844</t>
+          <t>39:07.515</t>
         </is>
       </c>
       <c r="G227" t="inlineStr"/>
@@ -8536,17 +8544,17 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Ben Hartopp [SNOW]</t>
+          <t>Dirk Richter</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ZRG</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>39:16.112</t>
+          <t>39:07.844</t>
         </is>
       </c>
       <c r="G228" t="inlineStr"/>
@@ -8562,7 +8570,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8572,17 +8580,17 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Jorge Ar&amp;eacute;valo</t>
+          <t>Ben Hartopp [SNOW]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>39:26.642</t>
+          <t>39:16.112</t>
         </is>
       </c>
       <c r="G229" t="inlineStr"/>
@@ -8603,22 +8611,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Roberto Delgado Hynes</t>
+          <t>Jorge Ar&amp;eacute;valo</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Velo&amp;#039;Z</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>39:46.669</t>
+          <t>39:26.642</t>
         </is>
       </c>
       <c r="G230" t="inlineStr"/>
@@ -8634,7 +8642,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8644,7 +8652,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>John Swift</t>
+          <t>Roberto Delgado Hynes</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8654,7 +8662,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>39:51.976</t>
+          <t>39:46.669</t>
         </is>
       </c>
       <c r="G231" t="inlineStr"/>
@@ -8675,18 +8683,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Sebastian Borquez</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr"/>
+          <t>John Swift</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>40:39.786</t>
+          <t>39:51.976</t>
         </is>
       </c>
       <c r="G232" t="inlineStr"/>
@@ -8707,22 +8719,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andy Westall </t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>SWCC</t>
-        </is>
-      </c>
+          <t>Sebastian Borquez</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>40:55.101</t>
+          <t>40:39.786</t>
         </is>
       </c>
       <c r="G233" t="inlineStr"/>
@@ -8743,22 +8751,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Pearce </t>
+          <t xml:space="preserve">Andy Westall </t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>TBG</t>
+          <t>SWCC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>41:26.901</t>
+          <t>40:55.101</t>
         </is>
       </c>
       <c r="G234" t="inlineStr"/>
@@ -8774,7 +8782,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8784,17 +8792,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Mads Gronbek [DBR]</t>
+          <t xml:space="preserve">John Pearce </t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>TBG</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>42:08.148</t>
+          <t>41:26.901</t>
         </is>
       </c>
       <c r="G235" t="inlineStr"/>
@@ -8810,23 +8818,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Andrew Lowrie</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr"/>
+          <t>Mads Gronbek [DBR]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>DBR</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>42:29.930</t>
+          <t>42:08.148</t>
         </is>
       </c>
       <c r="G236" t="inlineStr"/>
@@ -8842,27 +8854,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Mark SMITH6725</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>CTT</t>
-        </is>
-      </c>
+          <t>Andrew Lowrie</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>44:34.144</t>
+          <t>42:29.930</t>
         </is>
       </c>
       <c r="G237" t="inlineStr"/>
@@ -8878,23 +8886,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Magnus Morel</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
+          <t>Mark SMITH6725</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>CTT</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>44:58.275</t>
+          <t>44:34.144</t>
         </is>
       </c>
       <c r="G238" t="inlineStr"/>
@@ -8910,7 +8922,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8920,13 +8932,13 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Sam Godfrey</t>
+          <t>Magnus Morel</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>45:17.857</t>
+          <t>44:58.275</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
@@ -8947,18 +8959,18 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Christophe Chris [BIKES-FR]</t>
+          <t>Sam Godfrey</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>50:43.002</t>
+          <t>45:17.857</t>
         </is>
       </c>
       <c r="G240" t="inlineStr"/>
@@ -8979,18 +8991,18 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adam Sternfield </t>
+          <t>Christophe Chris [BIKES-FR]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>51:57.148</t>
+          <t>50:43.002</t>
         </is>
       </c>
       <c r="G241" t="inlineStr"/>
@@ -9006,27 +9018,23 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Morten  Bach  Jepsen</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>DBR</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Adam Sternfield </t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>52:58.678</t>
+          <t>51:57.148</t>
         </is>
       </c>
       <c r="G242" t="inlineStr"/>
@@ -9047,22 +9055,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Richard Emblen</t>
+          <t>Morten  Bach  Jepsen</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>54:43.733</t>
+          <t>52:58.678</t>
         </is>
       </c>
       <c r="G243" t="inlineStr"/>
@@ -9083,22 +9091,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nick Kelly [4STAR] </t>
+          <t>Richard Emblen</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>54:45.613</t>
+          <t>54:43.733</t>
         </is>
       </c>
       <c r="G244" t="inlineStr"/>
@@ -9119,18 +9127,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Tom Bradley</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr"/>
+          <t xml:space="preserve">Nick Kelly [4STAR] </t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>54:59.827</t>
+          <t>54:45.613</t>
         </is>
       </c>
       <c r="G245" t="inlineStr"/>
@@ -9146,23 +9158,23 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Zsolt Kun-Szabo</t>
+          <t>Tom Bradley</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>55:01.241</t>
+          <t>54:59.827</t>
         </is>
       </c>
       <c r="G246" t="inlineStr"/>
@@ -9178,27 +9190,23 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steve Boon (GXY) </t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Zsolt Kun-Szabo</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>55:01.338</t>
+          <t>55:01.241</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
@@ -9219,22 +9227,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Marc Singer</t>
+          <t xml:space="preserve">Steve Boon (GXY) </t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>T3 Philly</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>55:10.735</t>
+          <t>55:01.338</t>
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
@@ -9255,22 +9263,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane King </t>
+          <t>Marc Singer</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>R4CF.</t>
+          <t>T3 Philly</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>55:20.717</t>
+          <t>55:10.735</t>
         </is>
       </c>
       <c r="G249" t="inlineStr"/>
@@ -9291,22 +9299,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Lorenzo Meciani (CAY)</t>
+          <t xml:space="preserve">Shane King </t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Dogs-Pigs</t>
+          <t>R4CF.</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>56:48.630</t>
+          <t>55:20.717</t>
         </is>
       </c>
       <c r="G250" t="inlineStr"/>
@@ -9332,13 +9340,17 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>john hoffmann6976</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr"/>
+          <t>Lorenzo Meciani (CAY)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Dogs-Pigs</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>57:28.007</t>
+          <t>56:48.630</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
@@ -9359,22 +9371,18 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Simon  Harvey</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>COALITION</t>
-        </is>
-      </c>
+          <t>john hoffmann6976</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>57:28.797</t>
+          <t>57:28.007</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -9395,18 +9403,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>oliver johnson</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr"/>
+          <t>Simon  Harvey</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>57:29.161</t>
+          <t>57:28.797</t>
         </is>
       </c>
       <c r="G253" t="inlineStr"/>
@@ -9427,22 +9439,18 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Ryan Dagooc</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4STAR </t>
-        </is>
-      </c>
+          <t>oliver johnson</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>57:29.768</t>
+          <t>57:29.161</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
@@ -9463,18 +9471,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis  Gouchie </t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr"/>
+          <t>Ryan Dagooc</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>57:31.232</t>
+          <t>57:29.768</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
@@ -9490,23 +9502,23 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Fabien V</t>
+          <t xml:space="preserve">Travis  Gouchie </t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>57:45.692</t>
+          <t>57:31.232</t>
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
@@ -9522,7 +9534,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9532,13 +9544,13 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>L Andersen</t>
+          <t>Fabien V</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>57:52.627</t>
+          <t>57:45.692</t>
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
@@ -9559,22 +9571,18 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Paul Potter (HERC)</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>L Andersen</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>57:58.030</t>
+          <t>57:52.627</t>
         </is>
       </c>
       <c r="G258" t="inlineStr"/>
@@ -9595,22 +9603,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>70+</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Michael Lindsay</t>
+          <t>Paul Potter (HERC)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>58:05.278</t>
+          <t>57:58.030</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
@@ -9631,22 +9639,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Christopher Lindskjold</t>
+          <t>Michael Lindsay</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>58:17.985</t>
+          <t>58:05.278</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
@@ -9667,22 +9675,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Christopher Lindskjold</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>59:33.723</t>
+          <t>58:17.985</t>
         </is>
       </c>
       <c r="G261" t="inlineStr"/>
@@ -9703,18 +9711,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Shige Haru</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
+          <t xml:space="preserve">Kim YUU </t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>59:49.958</t>
+          <t>59:33.723</t>
         </is>
       </c>
       <c r="G262" t="inlineStr"/>
@@ -9730,27 +9742,23 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Carl</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Shige Haru</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>59:57.500</t>
+          <t>59:49.958</t>
         </is>
       </c>
       <c r="G263" t="inlineStr"/>
@@ -9766,27 +9774,27 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artur Burdasz </t>
+          <t>Carl</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>ZTPL.CC</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>01:01:28.813</t>
+          <t>59:57.500</t>
         </is>
       </c>
       <c r="G264" t="inlineStr"/>
@@ -9807,22 +9815,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>psf</t>
+          <t xml:space="preserve">Artur Burdasz </t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>ZTPL.CC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>01:01:36.829</t>
+          <t>01:01:28.813</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -9838,7 +9846,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9848,17 +9856,17 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luke O&amp;#039;Connor </t>
+          <t>psf</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Tamworth CC</t>
+          <t>WCC</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>01:04:59.019</t>
+          <t>01:01:36.829</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
@@ -9884,17 +9892,17 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t xml:space="preserve">Luke O&amp;#039;Connor </t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Tamworth CC</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>01:05:04.959</t>
+          <t>01:04:59.019</t>
         </is>
       </c>
       <c r="G267" t="inlineStr"/>
@@ -9915,22 +9923,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Rasmus Dahlin (DZR)</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>01:23:53.525</t>
+          <t>01:05:04.959</t>
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
@@ -9951,22 +9959,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Karlheinz Engel - [KC&amp;#128029;]</t>
+          <t>Rasmus Dahlin (DZR)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>01:30:39.384</t>
+          <t>01:23:53.525</t>
         </is>
       </c>
       <c r="G269" t="inlineStr"/>
@@ -9987,22 +9995,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Jay ONeil</t>
+          <t>Karlheinz Engel - [KC&amp;#128029;]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>01:31:17.826</t>
+          <t>01:30:39.384</t>
         </is>
       </c>
       <c r="G270" t="inlineStr"/>
@@ -10028,13 +10036,17 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>eiji yama</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
+          <t>Jay ONeil</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>01:36:55.390</t>
+          <t>01:31:17.826</t>
         </is>
       </c>
       <c r="G271" t="inlineStr"/>
@@ -10050,27 +10062,23 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>eiji yama</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>01:43:08.050</t>
+          <t>01:36:55.390</t>
         </is>
       </c>
       <c r="G272" t="inlineStr"/>
@@ -10091,18 +10099,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Park Jinhea3000[TEC]</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr"/>
+          <t>AL C SimpSimpHea</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>01:44:16.860</t>
+          <t>01:43:08.050</t>
         </is>
       </c>
       <c r="G273" t="inlineStr"/>
@@ -10113,47 +10125,39 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Eduardo Rojas Rojas</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>04:01:35.392</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:44:16.850</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10163,27 +10167,23 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Park Jinhea3000[TEC]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>02:08:02.879</t>
+          <t>01:44:16.860</t>
         </is>
       </c>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -10199,27 +10199,31 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>02:09:46.608</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr"/>
+          <t>04:01:35.392</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
       <c r="H276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
@@ -10230,32 +10234,32 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
+          <t>Aidan Novis (RHINO)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>01:17:01.165</t>
+          <t>02:09:46.608</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -10271,22 +10275,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Simon Richardson MBE PLY (Zwift)(PDQ Coaching)(ZTeam GXY/PDQ)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>01:24:31.213</t>
+          <t>01:17:01.165</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
@@ -10302,7 +10306,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10312,7 +10316,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -10322,7 +10326,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>01:26:11.009</t>
+          <t>01:24:31.213</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
@@ -10338,7 +10342,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10348,22 +10352,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Matt Taylor (Charlies Angels Full Throttle)</t>
+          <t>Brian Benner (HERC)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>CAFT</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>21:38.777</t>
+          <t>01:26:11.009</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -10374,7 +10378,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10384,17 +10388,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Stefaan Lampaert</t>
+          <t>Matt Taylor (Charlies Angels Full Throttle)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>BZR eCycling Club</t>
+          <t>CAFT</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>22:33.716</t>
+          <t>21:38.777</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -10410,23 +10414,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>FELIX CALVO POO</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
+          <t>Stefaan Lampaert</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>BZR eCycling Club</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>22:39.179</t>
+          <t>22:33.716</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
@@ -10452,17 +10460,13 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Julia Umbrello [eSRT]</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+          <t>FELIX CALVO POO</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>22:54.914</t>
+          <t>22:39.179</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
@@ -10478,23 +10482,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Austin H</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr"/>
+          <t>Julia Umbrello [eSRT]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>24:27.518</t>
+          <t>22:54.914</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
@@ -10520,13 +10528,13 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Ryan Gower</t>
+          <t>Austin H</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>25:21.604</t>
+          <t>24:27.518</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
@@ -10547,18 +10555,18 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Ian Lovely</t>
+          <t>Ryan Gower</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>26:35.426</t>
+          <t>25:21.604</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
@@ -10574,7 +10582,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10584,13 +10592,13 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Joe Limke</t>
+          <t>Ian Lovely</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>29:31.924</t>
+          <t>26:35.426</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
@@ -10606,27 +10614,23 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>COALITION</t>
-        </is>
-      </c>
+          <t>Joe Limke</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>30:35.758</t>
+          <t>29:31.924</t>
         </is>
       </c>
       <c r="G288" t="inlineStr"/>
@@ -10652,13 +10656,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Matt Jones</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr"/>
+          <t>Steve D&amp;#039;Alessandro (Coalition)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>44:04.011</t>
+          <t>30:35.758</t>
         </is>
       </c>
       <c r="G289" t="inlineStr"/>
@@ -10679,18 +10687,18 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Philip Gill</t>
+          <t>Matt Jones</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>45:14.312</t>
+          <t>44:04.011</t>
         </is>
       </c>
       <c r="G290" t="inlineStr"/>
@@ -10711,18 +10719,18 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>@ arrows</t>
+          <t>Philip Gill</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>45:16.878</t>
+          <t>45:14.312</t>
         </is>
       </c>
       <c r="G291" t="inlineStr"/>
@@ -10743,22 +10751,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Kim Bryan &amp;#127800;</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>@ arrows</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>45:41.917</t>
+          <t>45:16.878</t>
         </is>
       </c>
       <c r="G292" t="inlineStr"/>
@@ -10774,7 +10778,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10784,17 +10788,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Rikke Rasmussen #DBM#</t>
+          <t>Kim Bryan &amp;#127800;</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>45:41.917</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
@@ -10810,7 +10814,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10820,17 +10824,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Mailan Kimsuan [ZIRT]</t>
+          <t>Rikke Rasmussen #DBM#</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="G294" t="inlineStr"/>
@@ -10846,7 +10850,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10856,17 +10860,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Adrian ZC</t>
+          <t>Mailan Kimsuan [ZIRT]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Momentum CR</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>51:07.527</t>
+          <t>50:00.950</t>
         </is>
       </c>
       <c r="G295" t="inlineStr"/>
@@ -10882,7 +10886,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10892,17 +10896,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Jamie Roy</t>
+          <t>Adrian ZC</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Stages Cycling</t>
+          <t>Momentum CR</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>57:26.520</t>
+          <t>51:07.527</t>
         </is>
       </c>
       <c r="G296" t="inlineStr"/>
@@ -10923,22 +10927,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Ant Vine</t>
+          <t>Jamie Roy</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Stages Cycling</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>57:31.627</t>
+          <t>57:26.520</t>
         </is>
       </c>
       <c r="G297" t="inlineStr"/>
@@ -10964,17 +10968,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>sean carter [WMZ]</t>
+          <t>Ant Vine</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>57:32.338</t>
+          <t>57:31.627</t>
         </is>
       </c>
       <c r="G298" t="inlineStr"/>
@@ -10995,18 +10999,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Jason Gillespie (Orkney CC)</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>sean carter [WMZ]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>WMZ</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>58:45.630</t>
+          <t>57:32.338</t>
         </is>
       </c>
       <c r="G299" t="inlineStr"/>
@@ -11032,17 +11040,13 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Arif Wijayanto</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>ZID</t>
-        </is>
-      </c>
+          <t>Jason Gillespie (Orkney CC)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>01:02:24.672</t>
+          <t>58:45.630</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
@@ -11063,22 +11067,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Armitage  Herc </t>
+          <t>Arif Wijayanto</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>ZID</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>01:03:30.326</t>
+          <t>01:02:24.672</t>
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
@@ -11094,27 +11098,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Ron Clarino TeamODZ</t>
+          <t xml:space="preserve">Robert Armitage  Herc </t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>TeamODZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>01:05:07.663</t>
+          <t>01:03:30.326</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
@@ -11130,23 +11134,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Danny Postell GCC</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>Ron Clarino TeamODZ</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>TeamODZ</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>01:05:25.276</t>
+          <t>01:05:07.663</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -11167,18 +11175,18 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>&amp;#321;ukasz Karasi&amp;#324;ski</t>
+          <t>Danny Postell GCC</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>01:09:46.960</t>
+          <t>01:05:25.276</t>
         </is>
       </c>
       <c r="G304" t="inlineStr"/>
@@ -11189,7 +11197,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -11199,18 +11207,18 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>John Rae</t>
+          <t>&amp;#321;ukasz Karasi&amp;#324;ski</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>27:07.445</t>
+          <t>01:09:46.960</t>
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
@@ -11231,18 +11239,18 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Philip Gkikas CAAT &amp;#128076;</t>
+          <t>John Rae</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>28:25.665</t>
+          <t>27:07.445</t>
         </is>
       </c>
       <c r="G306" t="inlineStr"/>
@@ -11263,18 +11271,18 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Leslie Koh</t>
+          <t xml:space="preserve"> Philip Gkikas CAAT &amp;#128076;</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>51:08.233</t>
+          <t>28:25.665</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
@@ -11295,18 +11303,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Stuart Haigh</t>
+          <t>Leslie Koh</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>58:30.748</t>
+          <t>51:08.233</t>
         </is>
       </c>
       <c r="G308" t="inlineStr"/>
@@ -11327,22 +11335,54 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Benjamin Sommervoll</t>
+          <t>Stuart Haigh</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>01:01:28.928</t>
+          <t>58:30.748</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Snr</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Benjamin Sommervoll</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>01:01:28.928</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11357,7 +11397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16741,16 +16781,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09:18:26.842</t>
+          <t>11:03:36.522</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>29:40.427</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -16778,11 +16818,11 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>03:33:09.531</t>
+          <t>05:18:19.211</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -18384,17 +18424,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>06:48:20.090</t>
+          <t>01:44:56.282</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -18403,35 +18443,35 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>45:22.447</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>02:54:54.011</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>01:14:40.060</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>01:53:23.572</t>
+          <t>01:44:56.282</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -18446,12 +18486,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>04:17:49.487</t>
+          <t>06:48:20.090</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18460,39 +18500,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>01:27:09.400</t>
+          <t>45:22.447</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>02:04:27.935</t>
+          <t>02:54:54.011</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>46:12.152</t>
+          <t>01:14:40.060</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:53:23.572</t>
         </is>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -18503,12 +18543,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>02:02:43.082</t>
+          <t>04:17:49.487</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18517,11 +18557,11 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>01:37:25.938</t>
+          <t>01:27:09.400</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18529,19 +18569,19 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>02:04:27.935</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>25:17.144</t>
+          <t>46:12.152</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -18560,12 +18600,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>01:05:04.662</t>
+          <t>02:02:43.082</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18574,16 +18614,16 @@
         </is>
       </c>
       <c r="E127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>01:37:25.938</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
         <v>2</v>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>41:36.187</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>1</v>
-      </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>00.000</t>
@@ -18594,7 +18634,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>23:28.475</t>
+          <t>25:17.144</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -18617,12 +18657,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CAFT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>21:38.777</t>
+          <t>01:05:04.662</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18631,15 +18671,15 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>41:36.187</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18651,7 +18691,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>21:38.777</t>
+          <t>23:28.475</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -18674,12 +18714,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BZR eCycling Club</t>
+          <t>CAFT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>22:33.716</t>
+          <t>21:38.777</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18708,7 +18748,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>22:33.716</t>
+          <t>21:38.777</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -18731,12 +18771,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>BZR eCycling Club</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>22:54.914</t>
+          <t>22:33.716</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18765,7 +18805,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>22:54.914</t>
+          <t>22:33.716</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -18788,12 +18828,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>30:35.758</t>
+          <t>22:54.914</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18822,7 +18862,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30:35.758</t>
+          <t>22:54.914</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -18845,12 +18885,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>30:35.758</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18863,11 +18903,11 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>48:08.706</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18879,11 +18919,11 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>30:35.758</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -18902,12 +18942,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -18920,7 +18960,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>50:00.950</t>
+          <t>48:08.706</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18959,12 +18999,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Momentum CR</t>
+          <t xml:space="preserve"> &amp;#127470;&amp;#127465; Z I R T</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>51:07.527</t>
+          <t>50:00.950</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18977,7 +19017,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>51:07.527</t>
+          <t>50:00.950</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19016,12 +19056,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stages Cycling</t>
+          <t>Momentum CR</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>57:26.520</t>
+          <t>51:07.527</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19034,19 +19074,19 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>51:07.527</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>57:26.520</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -19073,12 +19113,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>Stages Cycling</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>57:32.338</t>
+          <t>57:26.520</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19099,7 +19139,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>57:32.338</t>
+          <t>57:26.520</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -19130,12 +19170,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZID</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>01:02:24.672</t>
+          <t>57:32.338</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19156,7 +19196,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01:02:24.672</t>
+          <t>57:32.338</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -19187,52 +19227,109 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>ZID</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>01:02:24.672</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>01:02:24.672</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>TeamODZ</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>01:05:07.663</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="inlineStr">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr">
         <is>
           <t>01:05:07.663</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
-      <c r="M138" t="n">
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="M139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19247,7 +19344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20710,7 +20807,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>832585</v>
+        <v>6842342</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -20724,12 +20821,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -20739,10 +20836,10 @@
         <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>15.301</v>
+        <v>14.968</v>
       </c>
       <c r="I34" t="n">
-        <v>46.554</v>
+        <v>40.369</v>
       </c>
       <c r="J34" t="n">
         <v>14</v>
@@ -20754,7 +20851,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1475359</v>
+        <v>8149174</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -20768,7 +20865,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -20777,19 +20874,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G35" t="n">
         <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>15.923</v>
+        <v>16.08</v>
       </c>
       <c r="I35" t="n">
-        <v>41.443</v>
+        <v>39.987</v>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
         <v>14</v>
@@ -20798,21 +20895,21 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3294901</v>
+        <v>832585</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -20821,24 +20918,112 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
       </c>
       <c r="H36" t="n">
+        <v>15.301</v>
+      </c>
+      <c r="I36" t="n">
+        <v>46.554</v>
+      </c>
+      <c r="J36" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1475359</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Andy Morton (TNP)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>15.923</v>
+      </c>
+      <c r="I37" t="n">
+        <v>41.443</v>
+      </c>
+      <c r="J37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
         <v>15.678</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I38" t="n">
         <v>41.622</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J38" t="n">
         <v>20</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K38" t="n">
         <v>20</v>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20851,7 +21036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23309,7 +23494,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
         <v>4</v>
@@ -23354,7 +23539,7 @@
         <v>10</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
         <v>10</v>
@@ -23389,7 +23574,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G32" t="n">
         <v>4</v>
@@ -23419,7 +23604,7 @@
         <v>994.575</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>5</v>
@@ -23431,10 +23616,10 @@
         <v>8</v>
       </c>
       <c r="T32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
         <v>8</v>
@@ -23469,7 +23654,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -23511,22 +23696,22 @@
         <v>6</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>832585</v>
+        <v>8149174</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -23540,73 +23725,73 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
         <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>273.7</v>
+        <v>249.148</v>
       </c>
       <c r="I34" t="n">
-        <v>149.223</v>
+        <v>162.06</v>
       </c>
       <c r="J34" t="n">
-        <v>74.93899999999999</v>
+        <v>68.562</v>
       </c>
       <c r="K34" t="n">
-        <v>43.439</v>
+        <v>44.718</v>
       </c>
       <c r="L34" t="n">
-        <v>39.652</v>
+        <v>49.544</v>
       </c>
       <c r="M34" t="n">
-        <v>553.567</v>
+        <v>480.645</v>
       </c>
       <c r="N34" t="n">
-        <v>619.588</v>
+        <v>667.727</v>
       </c>
       <c r="O34" t="n">
-        <v>1246.293</v>
+        <v>1066.531</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1475359</v>
+        <v>6842342</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -23620,46 +23805,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G35" t="n">
         <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>294.757</v>
+        <v>277.114</v>
       </c>
       <c r="I35" t="n">
-        <v>154.64</v>
+        <v>163.575</v>
       </c>
       <c r="J35" t="n">
-        <v>76.681</v>
+        <v>72.70399999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>51.119</v>
+        <v>44.468</v>
       </c>
       <c r="L35" t="n">
-        <v>41.6</v>
+        <v>41.404</v>
       </c>
       <c r="M35" t="n">
-        <v>594.284</v>
+        <v>523.732</v>
       </c>
       <c r="N35" t="n">
-        <v>673.405</v>
+        <v>570.491</v>
       </c>
       <c r="O35" t="n">
-        <v>1217.002</v>
+        <v>1051.255</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -23668,16 +23853,16 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W35" t="n">
         <v>12</v>
@@ -23686,21 +23871,21 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3294901</v>
+        <v>832585</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -23709,60 +23894,220 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
       </c>
       <c r="H36" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>149.223</v>
+      </c>
+      <c r="J36" t="n">
+        <v>74.93899999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>43.439</v>
+      </c>
+      <c r="L36" t="n">
+        <v>39.652</v>
+      </c>
+      <c r="M36" t="n">
+        <v>553.567</v>
+      </c>
+      <c r="N36" t="n">
+        <v>619.588</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1246.293</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>6</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1475359</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Andy Morton (TNP)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>18</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>294.757</v>
+      </c>
+      <c r="I37" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="J37" t="n">
+        <v>76.681</v>
+      </c>
+      <c r="K37" t="n">
+        <v>51.119</v>
+      </c>
+      <c r="L37" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="M37" t="n">
+        <v>594.284</v>
+      </c>
+      <c r="N37" t="n">
+        <v>673.405</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1217.002</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>8</v>
+      </c>
+      <c r="X37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3294901</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
         <v>352.066</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I38" t="n">
         <v>180.835</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J38" t="n">
         <v>87.05</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K38" t="n">
         <v>51.897</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L38" t="n">
         <v>40.523</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M38" t="n">
         <v>564.154</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N38" t="n">
         <v>622.101</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O38" t="n">
         <v>1253.308</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P38" t="n">
         <v>5</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q38" t="n">
         <v>5</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S38" t="n">
         <v>10</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T38" t="n">
         <v>10</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U38" t="n">
         <v>10</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V38" t="n">
         <v>10</v>
       </c>
-      <c r="W36" t="n">
+      <c r="W38" t="n">
         <v>20</v>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37272,7 +37617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38275,58 +38620,54 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2213032</v>
+        <v>2206420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
+          <t>Eduardo Rojas Rojas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01:14:31.682</t>
+          <t>01:44:16.850</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2236225</v>
+        <v>2213032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Andy Ebbage (No GC)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>DraftingDinos</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -38334,77 +38675,77 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01:25:26.589</t>
+          <t>01:14:31.682</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2392598</v>
+        <v>2236225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>David Pugh &amp;#127793; [Team Vegan]</t>
+          <t>Andy Ebbage (No GC)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Vegan</t>
+          <t>DraftingDinos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01:15:38.067</t>
+          <t>01:25:26.589</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2602856</v>
+        <v>2392598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t>David Pugh &amp;#127793; [Team Vegan]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Vegan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01:39:51.187</t>
+          <t>01:15:38.067</t>
         </is>
       </c>
     </row>
@@ -38416,116 +38757,120 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2881429</v>
+        <v>2602856</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>01:50:59.442</t>
+          <t>01:39:51.187</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3044689</v>
+        <v>2881429</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yassine Sissi</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01:14:42.676</t>
+          <t>01:50:59.442</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3060368</v>
+        <v>3044689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Andr&amp;eacute; Neault</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Yassine Sissi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01:25:22.599</t>
+          <t>01:14:42.676</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3188498</v>
+        <v>3060368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Eric Auder</t>
+          <t>Andr&amp;eacute; Neault</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -38536,62 +38881,58 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01:16:09.689</t>
+          <t>01:25:22.599</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3294901</v>
+        <v>3188498</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Eric Auder</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01:53:23.572</t>
+          <t>01:16:09.689</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3477462</v>
+        <v>3294901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Jay ONeil</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -38606,42 +38947,42 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01:31:17.826</t>
+          <t>01:53:23.572</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3614977</v>
+        <v>3477462</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Heinz Ensen (Herd)</t>
+          <t>Jay ONeil</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HERD</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01:31:17.413</t>
+          <t>01:31:17.826</t>
         </is>
       </c>
     </row>
@@ -38657,82 +38998,82 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4166463</v>
+        <v>3614977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>Heinz Ensen (Herd)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HERD</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01:33:50.026</t>
+          <t>01:31:17.413</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4730842</v>
+        <v>4166463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ATGNI</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01:20:00.578</t>
+          <t>01:33:50.026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4752321</v>
+        <v>4730842</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Alexey Tikhov (B)</t>
+          <t>Harris Waters(ATGNI)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -38742,32 +39083,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01:27:14.435</t>
+          <t>01:20:00.578</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4865109</v>
+        <v>4752321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ryo Nakajima(CAP)[FRR]</t>
+          <t>Alexey Tikhov (B)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FRR</t>
+          <t>MTBtraining</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -38777,7 +39118,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01:14:28.772</t>
+          <t>01:27:14.435</t>
         </is>
       </c>
     </row>
@@ -38789,20 +39130,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4980720</v>
+        <v>4865109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>Ryo Nakajima(CAP)[FRR]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>FRR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -38812,7 +39153,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>01:14:10.486</t>
+          <t>01:14:28.772</t>
         </is>
       </c>
     </row>
@@ -38824,37 +39165,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5023963</v>
+        <v>4980720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Coach lak (TNP)</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>01:21:13.104</t>
+          <t>01:14:10.486</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -38863,14 +39204,18 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5139632</v>
+        <v>5023963</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Coach lak (TNP)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -38878,42 +39223,38 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01:23:05.402</t>
+          <t>01:21:13.104</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5273193</v>
+        <v>5139632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raul Nieto Luque </t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>TEZH Racing</t>
-        </is>
-      </c>
+          <t>Thomas Mutz</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01:12:19.724</t>
+          <t>01:23:05.402</t>
         </is>
       </c>
     </row>
@@ -38925,30 +39266,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5273300</v>
+        <v>5273193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Nate Berkopec</t>
+          <t xml:space="preserve">Raul Nieto Luque </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01:22:41.358</t>
+          <t>01:12:19.724</t>
         </is>
       </c>
     </row>
@@ -38960,20 +39301,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5402095</v>
+        <v>5273300</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Nate Berkopec</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -38983,42 +39324,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01:19:46.295</t>
+          <t>01:22:41.358</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5870438</v>
+        <v>5402095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t>Quentin Vee [EVO]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01:33:56.507</t>
+          <t>01:19:46.295</t>
         </is>
       </c>
     </row>
@@ -39034,26 +39375,26 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5877680</v>
+        <v>5870438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sem VH</t>
+          <t>Steffen Dahlin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>COERS</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01:22:37.115</t>
+          <t>01:33:56.507</t>
         </is>
       </c>
     </row>
@@ -39069,16 +39410,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5880054</v>
+        <v>5877680</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
+          <t>Sem VH</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -39088,30 +39429,34 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01:33:49.760</t>
+          <t>01:22:37.115</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5885126</v>
+        <v>5880054</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Vadim K.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>S R T</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -39119,77 +39464,73 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01:08:31.070</t>
+          <t>01:33:49.760</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5886245</v>
+        <v>5885126</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Rasmus Dahlin (DZR)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>DZR</t>
-        </is>
-      </c>
+          <t>Vadim K.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01:23:53.525</t>
+          <t>01:08:31.070</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5893609</v>
+        <v>5886245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
+          <t>Rasmus Dahlin (DZR)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01:19:24.540</t>
+          <t>01:23:53.525</t>
         </is>
       </c>
     </row>
@@ -39201,15 +39542,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5959135</v>
+        <v>5893609</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ben  Spedding [TNP]</t>
+          <t>Aled Jones</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -39219,72 +39560,72 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01:19:25.004</t>
+          <t>01:19:24.540</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5981378</v>
+        <v>5959135</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01:33:50.659</t>
+          <t>01:19:25.004</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6006740</v>
+        <v>5981378</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Keegan McCormick [A-P-V]</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -39294,7 +39635,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>01:15:38.167</t>
+          <t>01:33:50.659</t>
         </is>
       </c>
     </row>
@@ -39306,53 +39647,53 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6052283</v>
+        <v>6006740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Henning S&amp;oslash;ndergaard</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Keegan McCormick [A-P-V]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>A-P-V</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01:14:17.401</t>
+          <t>01:15:38.167</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6311857</v>
+        <v>6052283</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RollCo</t>
-        </is>
-      </c>
+          <t>Henning S&amp;oslash;ndergaard</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -39360,14 +39701,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01:28:21.685</t>
+          <t>01:14:17.401</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -39376,26 +39717,26 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6715306</v>
+        <v>6311857</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Jay Rowe</t>
+          <t>L ook mum no hands (RollCo)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01:23:40.244</t>
+          <t>01:28:21.685</t>
         </is>
       </c>
     </row>
@@ -39407,65 +39748,65 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6853346</v>
+        <v>6715306</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthieu De Smet </t>
+          <t>Jay Rowe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>01:08:54.803</t>
+          <t>01:23:40.244</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6863000</v>
+        <v>6842342</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Markus Schweizer</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>WEz pb Cycling District</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>01:06:43.833</t>
+          <t>01:44:56.282</t>
         </is>
       </c>
     </row>
@@ -39477,100 +39818,100 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6952720</v>
+        <v>6853346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Remco Vanhoutte [A-P-V]</t>
+          <t xml:space="preserve">Matthieu De Smet </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>01:15:38.454</t>
+          <t>01:08:54.803</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6991072</v>
+        <v>6863000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01:32:28.663</t>
+          <t>01:06:43.833</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6997588</v>
+        <v>6952720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
+          <t>Remco Vanhoutte [A-P-V]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01:34:32.983</t>
+          <t>01:15:38.454</t>
         </is>
       </c>
     </row>
@@ -39582,26 +39923,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7072713</v>
+        <v>6991072</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>olivier fonquerne</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Jorge Fernandez Fernandez</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01:29:26.948</t>
+          <t>01:32:28.663</t>
         </is>
       </c>
     </row>
@@ -39617,57 +39962,57 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7455653</v>
+        <v>6997588</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01:38:27.007</t>
+          <t>01:34:32.983</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7552376</v>
+        <v>7072713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>HaG TaK</t>
+          <t>olivier fonquerne</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01:14:31.859</t>
+          <t>01:29:26.948</t>
         </is>
       </c>
     </row>
@@ -39683,68 +40028,64 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7710371</v>
+        <v>7455653</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Karlheinz Engel - [KC&amp;#128029;]</t>
+          <t>Justin Draper [Fellowship]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01:30:39.384</t>
+          <t>01:38:27.007</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7779078</v>
+        <v>7552376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>David Irwin</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>HaG TaK</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01:38:22.582</t>
+          <t>01:14:31.859</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -39753,68 +40094,68 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7799511</v>
+        <v>7710371</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Karlheinz Engel - [KC&amp;#128029;]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01:28:11.675</t>
+          <t>01:30:39.384</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8106949</v>
+        <v>7779078</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A. K. Espiritu (TNP)</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>01:12:57.016</t>
+          <t>01:38:22.582</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -39823,47 +40164,51 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8159437</v>
+        <v>7799511</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ezna Ragrts</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>01:24:36.567</t>
+          <t>01:28:11.675</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8325416</v>
+        <v>8106949</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PedroJ. L&amp;oacute;pez (TEZH)</t>
+          <t>A. K. Espiritu (TNP)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -39873,36 +40218,137 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01:21:54.222</t>
+          <t>01:12:57.016</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8149174</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01:45:09.680</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>8159437</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ezna Ragrts</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01:24:36.567</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>8325416</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PedroJ. L&amp;oacute;pez (TEZH)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>TEZH Racing</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01:21:54.222</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C80" t="n">
         <v>8389020</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Tibo Peeters</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Vet</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>01:07:01.775</t>
         </is>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24925,6 +24925,11 @@
           <t>time1</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>race_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24960,6 +24965,9 @@
           <t>31:57.682</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24995,6 +25003,9 @@
           <t>32:25.335</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25030,6 +25041,9 @@
           <t>32:25.399</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25065,6 +25079,9 @@
           <t>32:26.658</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25096,6 +25113,9 @@
           <t>32:31.802</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25131,6 +25151,9 @@
           <t>32:42.296</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25166,6 +25189,9 @@
           <t>32:43.627</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25201,6 +25227,9 @@
           <t>33:00.660</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25236,6 +25265,9 @@
           <t>33:01.374</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25267,6 +25299,9 @@
           <t>33:01.392</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25302,6 +25337,9 @@
           <t>33:01.630</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25337,6 +25375,9 @@
           <t>33:01.766</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25368,6 +25409,9 @@
           <t>33:02.469</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25403,6 +25447,9 @@
           <t>33:09.429</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25438,6 +25485,9 @@
           <t>33:09.857</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25473,6 +25523,9 @@
           <t>33:15.776</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25508,6 +25561,9 @@
           <t>33:16.643</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25543,6 +25599,9 @@
           <t>33:17.955</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25578,6 +25637,9 @@
           <t>33:20.972</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25613,6 +25675,9 @@
           <t>33:20.990</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25648,6 +25713,9 @@
           <t>33:21.075</t>
         </is>
       </c>
+      <c r="H22" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25683,6 +25751,9 @@
           <t>33:21.121</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25718,6 +25789,9 @@
           <t>33:21.271</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25753,6 +25827,9 @@
           <t>33:22.006</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25784,6 +25861,9 @@
           <t>33:22.255</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25819,6 +25899,9 @@
           <t>33:22.401</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25854,6 +25937,9 @@
           <t>33:23.872</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25889,6 +25975,9 @@
           <t>33:24.482</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25924,6 +26013,9 @@
           <t>33:31.500</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25959,6 +26051,9 @@
           <t>33:32.562</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -25994,6 +26089,9 @@
           <t>33:32.697</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -26029,6 +26127,9 @@
           <t>33:32.885</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26064,6 +26165,9 @@
           <t>33:33.978</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26095,6 +26199,9 @@
           <t>33:34.316</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26130,6 +26237,9 @@
           <t>33:34.551</t>
         </is>
       </c>
+      <c r="H36" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26161,6 +26271,9 @@
           <t>33:35.041</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26196,6 +26309,9 @@
           <t>33:35.828</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26231,6 +26347,9 @@
           <t>33:45.002</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26262,6 +26381,9 @@
           <t>33:48.259</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26297,6 +26419,9 @@
           <t>33:56.989</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26332,6 +26457,9 @@
           <t>33:57.106</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26341,7 +26469,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -26367,6 +26495,9 @@
           <t>33:57.310</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26402,6 +26533,9 @@
           <t>33:57.721</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -26437,6 +26571,9 @@
           <t>33:58.293</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -26468,6 +26605,9 @@
           <t>34:04.668</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -26503,6 +26643,9 @@
           <t>34:53.668</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -26538,6 +26681,9 @@
           <t>35:32.720</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26573,6 +26719,9 @@
           <t>35:37.346</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -26608,6 +26757,9 @@
           <t>35:38.215</t>
         </is>
       </c>
+      <c r="H50" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -26643,6 +26795,9 @@
           <t>36:37.755</t>
         </is>
       </c>
+      <c r="H51" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26678,6 +26833,9 @@
           <t>36:39.066</t>
         </is>
       </c>
+      <c r="H52" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -26713,6 +26871,9 @@
           <t>37:17.875</t>
         </is>
       </c>
+      <c r="H53" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -26748,6 +26909,9 @@
           <t>37:38.816</t>
         </is>
       </c>
+      <c r="H54" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -26783,6 +26947,9 @@
           <t>37:50.496</t>
         </is>
       </c>
+      <c r="H55" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -26792,7 +26959,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -26818,6 +26985,9 @@
           <t>42:13.670</t>
         </is>
       </c>
+      <c r="H56" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -26853,6 +27023,9 @@
           <t>32:59.583</t>
         </is>
       </c>
+      <c r="H57" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26884,6 +27057,9 @@
           <t>33:33.347</t>
         </is>
       </c>
+      <c r="H58" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26919,6 +27095,9 @@
           <t>33:33.586</t>
         </is>
       </c>
+      <c r="H59" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -26954,6 +27133,9 @@
           <t>33:34.276</t>
         </is>
       </c>
+      <c r="H60" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26989,6 +27171,9 @@
           <t>33:49.490</t>
         </is>
       </c>
+      <c r="H61" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -27024,6 +27209,9 @@
           <t>34:11.228</t>
         </is>
       </c>
+      <c r="H62" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27059,6 +27247,9 @@
           <t>34:15.757</t>
         </is>
       </c>
+      <c r="H63" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -27094,6 +27285,9 @@
           <t>34:43.721</t>
         </is>
       </c>
+      <c r="H64" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -27125,6 +27319,9 @@
           <t>35:17.401</t>
         </is>
       </c>
+      <c r="H65" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -27160,6 +27357,9 @@
           <t>35:34.069</t>
         </is>
       </c>
+      <c r="H66" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -27195,6 +27395,9 @@
           <t>35:41.512</t>
         </is>
       </c>
+      <c r="H67" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -27230,6 +27433,9 @@
           <t>35:42.906</t>
         </is>
       </c>
+      <c r="H68" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -27265,6 +27471,9 @@
           <t>35:51.007</t>
         </is>
       </c>
+      <c r="H69" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -27300,6 +27509,9 @@
           <t>35:55.766</t>
         </is>
       </c>
+      <c r="H70" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -27335,6 +27547,9 @@
           <t>36:22.857</t>
         </is>
       </c>
+      <c r="H71" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -27370,6 +27585,9 @@
           <t>36:33.721</t>
         </is>
       </c>
+      <c r="H72" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -27405,6 +27623,9 @@
           <t>36:43.305</t>
         </is>
       </c>
+      <c r="H73" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -27440,6 +27661,9 @@
           <t>36:51.881</t>
         </is>
       </c>
+      <c r="H74" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -27475,6 +27699,9 @@
           <t>37:14.815</t>
         </is>
       </c>
+      <c r="H75" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -27510,6 +27737,9 @@
           <t>37:22.000</t>
         </is>
       </c>
+      <c r="H76" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -27545,6 +27775,9 @@
           <t>37:38.591</t>
         </is>
       </c>
+      <c r="H77" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -27580,6 +27813,9 @@
           <t>37:39.268</t>
         </is>
       </c>
+      <c r="H78" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -27615,6 +27851,9 @@
           <t>37:39.450</t>
         </is>
       </c>
+      <c r="H79" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -27650,6 +27889,9 @@
           <t>37:41.896</t>
         </is>
       </c>
+      <c r="H80" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -27681,6 +27923,9 @@
           <t>38:01.970</t>
         </is>
       </c>
+      <c r="H81" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27716,6 +27961,9 @@
           <t>38:05.091</t>
         </is>
       </c>
+      <c r="H82" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27751,6 +27999,9 @@
           <t>38:05.501</t>
         </is>
       </c>
+      <c r="H83" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -27786,6 +28037,9 @@
           <t>38:07.386</t>
         </is>
       </c>
+      <c r="H84" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -27821,6 +28075,9 @@
           <t>38:09.320</t>
         </is>
       </c>
+      <c r="H85" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -27856,6 +28113,9 @@
           <t>39:03.466</t>
         </is>
       </c>
+      <c r="H86" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -27891,6 +28151,9 @@
           <t>39:06.280</t>
         </is>
       </c>
+      <c r="H87" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27926,6 +28189,9 @@
           <t>39:15.657</t>
         </is>
       </c>
+      <c r="H88" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27957,6 +28223,9 @@
           <t>39:27.783</t>
         </is>
       </c>
+      <c r="H89" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27988,6 +28257,9 @@
           <t>39:28.748</t>
         </is>
       </c>
+      <c r="H90" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -28023,6 +28295,9 @@
           <t>39:45.253</t>
         </is>
       </c>
+      <c r="H91" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28058,6 +28333,9 @@
           <t>41:03.174</t>
         </is>
       </c>
+      <c r="H92" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28089,6 +28367,9 @@
           <t>41:31.989</t>
         </is>
       </c>
+      <c r="H93" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -28120,6 +28401,9 @@
           <t>42:04.672</t>
         </is>
       </c>
+      <c r="H94" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -28155,6 +28439,9 @@
           <t>42:47.362</t>
         </is>
       </c>
+      <c r="H95" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -28190,6 +28477,9 @@
           <t>44:56.361</t>
         </is>
       </c>
+      <c r="H96" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -28225,6 +28515,9 @@
           <t>33:36.908</t>
         </is>
       </c>
+      <c r="H97" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -28256,6 +28549,9 @@
           <t>34:08.238</t>
         </is>
       </c>
+      <c r="H98" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -28291,6 +28587,9 @@
           <t>35:10.925</t>
         </is>
       </c>
+      <c r="H99" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -28322,6 +28621,9 @@
           <t>38:03.039</t>
         </is>
       </c>
+      <c r="H100" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -28331,7 +28633,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -28357,6 +28659,9 @@
           <t>38:04.051</t>
         </is>
       </c>
+      <c r="H101" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -28392,6 +28697,9 @@
           <t>38:06.428</t>
         </is>
       </c>
+      <c r="H102" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -28427,6 +28735,9 @@
           <t>38:28.425</t>
         </is>
       </c>
+      <c r="H103" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -28462,6 +28773,9 @@
           <t>38:36.864</t>
         </is>
       </c>
+      <c r="H104" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -28497,6 +28811,9 @@
           <t>38:58.416</t>
         </is>
       </c>
+      <c r="H105" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -28532,6 +28849,9 @@
           <t>39:05.483</t>
         </is>
       </c>
+      <c r="H106" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -28563,6 +28883,9 @@
           <t>39:07.515</t>
         </is>
       </c>
+      <c r="H107" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -28598,6 +28921,9 @@
           <t>39:07.566</t>
         </is>
       </c>
+      <c r="H108" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -28633,6 +28959,9 @@
           <t>39:07.844</t>
         </is>
       </c>
+      <c r="H109" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -28668,6 +28997,9 @@
           <t>39:16.112</t>
         </is>
       </c>
+      <c r="H110" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -28703,6 +29035,9 @@
           <t>39:21.436</t>
         </is>
       </c>
+      <c r="H111" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -28738,6 +29073,9 @@
           <t>39:22.574</t>
         </is>
       </c>
+      <c r="H112" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -28773,6 +29111,9 @@
           <t>39:26.642</t>
         </is>
       </c>
+      <c r="H113" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -28808,6 +29149,9 @@
           <t>39:46.669</t>
         </is>
       </c>
+      <c r="H114" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -28843,6 +29187,9 @@
           <t>39:46.788</t>
         </is>
       </c>
+      <c r="H115" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -28878,6 +29225,9 @@
           <t>39:51.976</t>
         </is>
       </c>
+      <c r="H116" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -28909,6 +29259,9 @@
           <t>40:39.786</t>
         </is>
       </c>
+      <c r="H117" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -28944,6 +29297,9 @@
           <t>40:55.101</t>
         </is>
       </c>
+      <c r="H118" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -28979,6 +29335,9 @@
           <t>41:02.969</t>
         </is>
       </c>
+      <c r="H119" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -29014,6 +29373,9 @@
           <t>41:03.656</t>
         </is>
       </c>
+      <c r="H120" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -29049,6 +29411,9 @@
           <t>41:05.154</t>
         </is>
       </c>
+      <c r="H121" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -29084,6 +29449,9 @@
           <t>41:22.488</t>
         </is>
       </c>
+      <c r="H122" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -29119,6 +29487,9 @@
           <t>41:26.901</t>
         </is>
       </c>
+      <c r="H123" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -29150,6 +29521,9 @@
           <t>41:55.814</t>
         </is>
       </c>
+      <c r="H124" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -29185,6 +29559,9 @@
           <t>42:08.148</t>
         </is>
       </c>
+      <c r="H125" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -29216,6 +29593,9 @@
           <t>42:29.930</t>
         </is>
       </c>
+      <c r="H126" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -29251,6 +29631,9 @@
           <t>44:34.144</t>
         </is>
       </c>
+      <c r="H127" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -29282,6 +29665,9 @@
           <t>44:58.275</t>
         </is>
       </c>
+      <c r="H128" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -29313,6 +29699,9 @@
           <t>45:17.857</t>
         </is>
       </c>
+      <c r="H129" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -29348,6 +29737,9 @@
           <t>41:36.187</t>
         </is>
       </c>
+      <c r="H130" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -29383,6 +29775,9 @@
           <t>43:00.203</t>
         </is>
       </c>
+      <c r="H131" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -29414,6 +29809,9 @@
           <t>43:32.716</t>
         </is>
       </c>
+      <c r="H132" t="n">
+        <v>5604853</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -29445,6 +29843,9 @@
           <t>44:04.011</t>
         </is>
       </c>
+      <c r="H133" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -29454,7 +29855,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -29480,6 +29881,9 @@
           <t>44:09.197</t>
         </is>
       </c>
+      <c r="H134" t="n">
+        <v>5604851</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -29511,6 +29915,9 @@
           <t>45:14.312</t>
         </is>
       </c>
+      <c r="H135" t="n">
+        <v>5604850</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -29542,6 +29949,9 @@
           <t>45:16.878</t>
         </is>
       </c>
+      <c r="H136" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -29577,6 +29987,9 @@
           <t>45:22.447</t>
         </is>
       </c>
+      <c r="H137" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -29612,6 +30025,9 @@
           <t>45:41.917</t>
         </is>
       </c>
+      <c r="H138" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -29647,6 +30063,9 @@
           <t>48:08.706</t>
         </is>
       </c>
+      <c r="H139" t="n">
+        <v>5604849</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -29682,6 +30101,9 @@
           <t>50:00.950</t>
         </is>
       </c>
+      <c r="H140" t="n">
+        <v>5604852</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -29717,6 +30139,9 @@
           <t>51:07.527</t>
         </is>
       </c>
+      <c r="H141" t="n">
+        <v>5604853</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -29752,6 +30177,9 @@
           <t>51:44.021</t>
         </is>
       </c>
+      <c r="H142" t="n">
+        <v>5604847</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -29783,6 +30211,9 @@
           <t>51:08.233</t>
         </is>
       </c>
+      <c r="H143" t="n">
+        <v>5604853</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -29813,6 +30244,9 @@
         <is>
           <t>58:30.748</t>
         </is>
+      </c>
+      <c r="H144" t="n">
+        <v>5604849</v>
       </c>
     </row>
   </sheetData>
@@ -29826,7 +30260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29865,6 +30299,11 @@
           <t>time2</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>race_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29900,6 +30339,9 @@
           <t>46:28.636</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29935,6 +30377,9 @@
           <t>46:30.368</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29970,6 +30415,9 @@
           <t>46:30.405</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30001,6 +30449,9 @@
           <t>46:30.444</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30036,6 +30487,9 @@
           <t>46:30.481</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30067,6 +30521,9 @@
           <t>46:30.506</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30102,6 +30559,9 @@
           <t>46:30.531</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30137,6 +30597,9 @@
           <t>46:30.573</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30172,6 +30635,9 @@
           <t>46:31.047</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30207,6 +30673,9 @@
           <t>46:31.077</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30242,6 +30711,9 @@
           <t>46:31.604</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30277,6 +30749,9 @@
           <t>46:31.843</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30286,7 +30761,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -30312,6 +30787,9 @@
           <t>46:32.073</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30347,6 +30825,9 @@
           <t>46:32.458</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30382,6 +30863,9 @@
           <t>46:34.857</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30417,6 +30901,9 @@
           <t>46:35.039</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30452,6 +30939,9 @@
           <t>46:35.246</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30487,6 +30977,9 @@
           <t>46:35.517</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -30522,6 +31015,9 @@
           <t>48:05.426</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -30557,6 +31053,9 @@
           <t>48:13.278</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -30592,6 +31091,9 @@
           <t>48:21.796</t>
         </is>
       </c>
+      <c r="H22" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -30627,6 +31129,9 @@
           <t>48:55.379</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -30662,6 +31167,9 @@
           <t>48:55.816</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -30697,6 +31205,9 @@
           <t>48:55.822</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -30732,6 +31243,9 @@
           <t>48:56.045</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -30741,7 +31255,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -30767,6 +31281,9 @@
           <t>48:56.055</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -30802,6 +31319,9 @@
           <t>48:56.159</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -30837,6 +31357,9 @@
           <t>48:56.417</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -30872,6 +31395,9 @@
           <t>48:57.011</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -30903,6 +31429,9 @@
           <t>48:57.536</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -30938,6 +31467,9 @@
           <t>48:57.755</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -30973,6 +31505,9 @@
           <t>49:44.973</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -31008,6 +31543,9 @@
           <t>50:35.538</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -31043,6 +31581,9 @@
           <t>50:36.351</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -31078,6 +31619,9 @@
           <t>50:39.719</t>
         </is>
       </c>
+      <c r="H36" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -31109,6 +31653,9 @@
           <t>50:39.771</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -31144,6 +31691,9 @@
           <t>50:45.899</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -31179,6 +31729,9 @@
           <t>51:08.816</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -31214,6 +31767,9 @@
           <t>51:42.416</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -31249,6 +31805,9 @@
           <t>51:47.473</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -31284,6 +31843,9 @@
           <t>51:47.540</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -31319,6 +31881,9 @@
           <t>51:57.759</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -31354,6 +31919,9 @@
           <t>52:56.218</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -31389,6 +31957,9 @@
           <t>52:56.733</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -31424,6 +31995,9 @@
           <t>52:58.429</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -31459,6 +32033,9 @@
           <t>52:59.612</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -31494,6 +32071,9 @@
           <t>55:48.972</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -31529,6 +32109,9 @@
           <t>56:47.464</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -31560,6 +32143,9 @@
           <t>57:05.797</t>
         </is>
       </c>
+      <c r="H50" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -31595,6 +32181,9 @@
           <t>48:55.896</t>
         </is>
       </c>
+      <c r="H51" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -31630,6 +32219,9 @@
           <t>48:57.524</t>
         </is>
       </c>
+      <c r="H52" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -31661,6 +32253,9 @@
           <t>48:58.105</t>
         </is>
       </c>
+      <c r="H53" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -31692,6 +32287,9 @@
           <t>50:35.813</t>
         </is>
       </c>
+      <c r="H54" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -31723,6 +32321,9 @@
           <t>50:36.262</t>
         </is>
       </c>
+      <c r="H55" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -31758,6 +32359,9 @@
           <t>51:06.250</t>
         </is>
       </c>
+      <c r="H56" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -31793,6 +32397,9 @@
           <t>51:35.555</t>
         </is>
       </c>
+      <c r="H57" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -31802,7 +32409,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -31828,6 +32435,9 @@
           <t>51:55.202</t>
         </is>
       </c>
+      <c r="H58" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -31863,6 +32473,9 @@
           <t>51:55.316</t>
         </is>
       </c>
+      <c r="H59" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -31898,6 +32511,9 @@
           <t>51:56.202</t>
         </is>
       </c>
+      <c r="H60" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -31933,6 +32549,9 @@
           <t>51:56.322</t>
         </is>
       </c>
+      <c r="H61" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -31968,6 +32587,9 @@
           <t>51:56.396</t>
         </is>
       </c>
+      <c r="H62" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -32003,6 +32625,9 @@
           <t>51:56.407</t>
         </is>
       </c>
+      <c r="H63" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -32038,6 +32663,9 @@
           <t>51:56.937</t>
         </is>
       </c>
+      <c r="H64" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -32073,6 +32701,9 @@
           <t>51:57.484</t>
         </is>
       </c>
+      <c r="H65" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -32108,6 +32739,9 @@
           <t>51:57.589</t>
         </is>
       </c>
+      <c r="H66" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -32143,6 +32777,9 @@
           <t>51:59.819</t>
         </is>
       </c>
+      <c r="H67" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -32174,6 +32811,9 @@
           <t>52:00.120</t>
         </is>
       </c>
+      <c r="H68" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -32209,6 +32849,9 @@
           <t>52:00.560</t>
         </is>
       </c>
+      <c r="H69" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -32244,6 +32887,9 @@
           <t>52:01.437</t>
         </is>
       </c>
+      <c r="H70" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -32279,6 +32925,9 @@
           <t>52:01.710</t>
         </is>
       </c>
+      <c r="H71" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -32314,6 +32963,9 @@
           <t>52:08.859</t>
         </is>
       </c>
+      <c r="H72" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -32345,6 +32997,9 @@
           <t>52:28.109</t>
         </is>
       </c>
+      <c r="H73" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -32376,6 +33031,9 @@
           <t>52:43.417</t>
         </is>
       </c>
+      <c r="H74" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -32407,6 +33065,9 @@
           <t>53:06.439</t>
         </is>
       </c>
+      <c r="H75" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -32442,6 +33103,9 @@
           <t>53:11.780</t>
         </is>
       </c>
+      <c r="H76" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -32473,6 +33137,9 @@
           <t>53:13.838</t>
         </is>
       </c>
+      <c r="H77" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -32504,6 +33171,9 @@
           <t>53:14.384</t>
         </is>
       </c>
+      <c r="H78" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -32535,6 +33205,9 @@
           <t>54:07.843</t>
         </is>
       </c>
+      <c r="H79" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -32570,6 +33243,9 @@
           <t>54:11.206</t>
         </is>
       </c>
+      <c r="H80" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -32605,6 +33281,9 @@
           <t>54:25.661</t>
         </is>
       </c>
+      <c r="H81" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -32640,6 +33319,9 @@
           <t>54:36.848</t>
         </is>
       </c>
+      <c r="H82" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -32675,6 +33357,9 @@
           <t>54:38.070</t>
         </is>
       </c>
+      <c r="H83" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -32710,6 +33395,9 @@
           <t>54:39.996</t>
         </is>
       </c>
+      <c r="H84" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -32741,6 +33429,9 @@
           <t>54:41.448</t>
         </is>
       </c>
+      <c r="H85" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -32776,6 +33467,9 @@
           <t>54:44.888</t>
         </is>
       </c>
+      <c r="H86" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -32811,6 +33505,9 @@
           <t>54:50.554</t>
         </is>
       </c>
+      <c r="H87" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -32846,6 +33543,9 @@
           <t>54:58.285</t>
         </is>
       </c>
+      <c r="H88" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -32881,6 +33581,9 @@
           <t>55:01.809</t>
         </is>
       </c>
+      <c r="H89" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -32916,6 +33619,9 @@
           <t>55:01.843</t>
         </is>
       </c>
+      <c r="H90" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -32951,6 +33657,9 @@
           <t>55:01.965</t>
         </is>
       </c>
+      <c r="H91" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -32982,6 +33691,9 @@
           <t>55:09.451</t>
         </is>
       </c>
+      <c r="H92" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -33017,6 +33729,9 @@
           <t>55:10.094</t>
         </is>
       </c>
+      <c r="H93" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -33048,6 +33763,9 @@
           <t>55:17.063</t>
         </is>
       </c>
+      <c r="H94" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -33083,6 +33801,9 @@
           <t>57:23.726</t>
         </is>
       </c>
+      <c r="H95" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -33118,6 +33839,9 @@
           <t>57:29.074</t>
         </is>
       </c>
+      <c r="H96" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -33149,6 +33873,9 @@
           <t>01:00:47.732</t>
         </is>
       </c>
+      <c r="H97" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -33184,6 +33911,9 @@
           <t>01:01:21.073</t>
         </is>
       </c>
+      <c r="H98" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -33215,6 +33945,9 @@
           <t>01:03:18.565</t>
         </is>
       </c>
+      <c r="H99" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -33250,6 +33983,9 @@
           <t>01:47:04.108</t>
         </is>
       </c>
+      <c r="H100" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -33281,6 +34017,9 @@
           <t>50:43.002</t>
         </is>
       </c>
+      <c r="H101" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -33312,6 +34051,9 @@
           <t>51:57.148</t>
         </is>
       </c>
+      <c r="H102" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -33343,6 +34085,9 @@
           <t>52:44.047</t>
         </is>
       </c>
+      <c r="H103" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -33378,6 +34123,9 @@
           <t>52:58.002</t>
         </is>
       </c>
+      <c r="H104" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -33413,6 +34161,9 @@
           <t>52:58.678</t>
         </is>
       </c>
+      <c r="H105" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -33448,6 +34199,9 @@
           <t>53:25.685</t>
         </is>
       </c>
+      <c r="H106" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -33483,6 +34237,9 @@
           <t>53:36.027</t>
         </is>
       </c>
+      <c r="H107" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -33518,6 +34275,9 @@
           <t>54:43.733</t>
         </is>
       </c>
+      <c r="H108" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -33553,6 +34313,9 @@
           <t>54:44.255</t>
         </is>
       </c>
+      <c r="H109" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -33588,6 +34351,9 @@
           <t>54:45.283</t>
         </is>
       </c>
+      <c r="H110" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -33623,6 +34389,9 @@
           <t>54:45.613</t>
         </is>
       </c>
+      <c r="H111" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -33654,6 +34423,9 @@
           <t>54:59.827</t>
         </is>
       </c>
+      <c r="H112" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -33689,6 +34461,9 @@
           <t>55:00.987</t>
         </is>
       </c>
+      <c r="H113" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -33720,6 +34495,9 @@
           <t>55:01.241</t>
         </is>
       </c>
+      <c r="H114" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -33755,6 +34533,9 @@
           <t>55:01.338</t>
         </is>
       </c>
+      <c r="H115" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -33786,6 +34567,9 @@
           <t>55:05.548</t>
         </is>
       </c>
+      <c r="H116" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -33821,6 +34605,9 @@
           <t>55:10.735</t>
         </is>
       </c>
+      <c r="H117" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -33856,6 +34643,9 @@
           <t>55:20.717</t>
         </is>
       </c>
+      <c r="H118" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -33891,6 +34681,9 @@
           <t>56:48.630</t>
         </is>
       </c>
+      <c r="H119" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -33922,6 +34715,9 @@
           <t>57:28.007</t>
         </is>
       </c>
+      <c r="H120" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -33957,6 +34753,9 @@
           <t>57:28.797</t>
         </is>
       </c>
+      <c r="H121" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -33992,6 +34791,9 @@
           <t>57:29.030</t>
         </is>
       </c>
+      <c r="H122" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -34023,6 +34825,9 @@
           <t>57:29.161</t>
         </is>
       </c>
+      <c r="H123" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -34058,6 +34863,9 @@
           <t>57:29.768</t>
         </is>
       </c>
+      <c r="H124" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -34093,6 +34901,9 @@
           <t>57:30.270</t>
         </is>
       </c>
+      <c r="H125" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -34124,6 +34935,9 @@
           <t>57:31.232</t>
         </is>
       </c>
+      <c r="H126" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -34155,6 +34969,9 @@
           <t>57:45.692</t>
         </is>
       </c>
+      <c r="H127" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -34186,6 +35003,9 @@
           <t>57:52.627</t>
         </is>
       </c>
+      <c r="H128" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -34221,6 +35041,9 @@
           <t>57:58.030</t>
         </is>
       </c>
+      <c r="H129" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -34256,6 +35079,9 @@
           <t>58:05.278</t>
         </is>
       </c>
+      <c r="H130" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -34291,6 +35117,9 @@
           <t>58:17.985</t>
         </is>
       </c>
+      <c r="H131" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -34322,6 +35151,9 @@
           <t>58:18.049</t>
         </is>
       </c>
+      <c r="H132" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -34357,6 +35189,9 @@
           <t>59:33.723</t>
         </is>
       </c>
+      <c r="H133" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -34388,6 +35223,9 @@
           <t>59:49.958</t>
         </is>
       </c>
+      <c r="H134" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -34423,6 +35261,9 @@
           <t>59:57.500</t>
         </is>
       </c>
+      <c r="H135" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -34454,6 +35295,9 @@
           <t>01:00:19.202</t>
         </is>
       </c>
+      <c r="H136" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -34489,6 +35333,9 @@
           <t>01:01:28.813</t>
         </is>
       </c>
+      <c r="H137" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -34524,6 +35371,9 @@
           <t>01:01:28.815</t>
         </is>
       </c>
+      <c r="H138" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -34559,6 +35409,9 @@
           <t>01:01:36.829</t>
         </is>
       </c>
+      <c r="H139" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -34594,6 +35447,9 @@
           <t>01:04:59.019</t>
         </is>
       </c>
+      <c r="H140" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -34629,6 +35485,9 @@
           <t>01:05:04.959</t>
         </is>
       </c>
+      <c r="H141" t="n">
+        <v>5604924</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -34638,7 +35497,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -34664,6 +35523,9 @@
           <t>57:26.520</t>
         </is>
       </c>
+      <c r="H142" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -34699,6 +35561,9 @@
           <t>57:31.627</t>
         </is>
       </c>
+      <c r="H143" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -34734,6 +35599,9 @@
           <t>57:32.338</t>
         </is>
       </c>
+      <c r="H144" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -34769,6 +35637,9 @@
           <t>57:48.412</t>
         </is>
       </c>
+      <c r="H145" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -34800,6 +35671,9 @@
           <t>58:45.630</t>
         </is>
       </c>
+      <c r="H146" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -34835,6 +35709,9 @@
           <t>59:33.972</t>
         </is>
       </c>
+      <c r="H147" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -34870,6 +35747,9 @@
           <t>59:34.085</t>
         </is>
       </c>
+      <c r="H148" t="n">
+        <v>5604922</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -34905,6 +35785,9 @@
           <t>01:01:29.151</t>
         </is>
       </c>
+      <c r="H149" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -34940,6 +35823,9 @@
           <t>01:02:06.602</t>
         </is>
       </c>
+      <c r="H150" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -34975,6 +35861,9 @@
           <t>01:02:21.333</t>
         </is>
       </c>
+      <c r="H151" t="n">
+        <v>5604926</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -35010,6 +35899,9 @@
           <t>01:02:24.672</t>
         </is>
       </c>
+      <c r="H152" t="n">
+        <v>5604928</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -35045,6 +35937,9 @@
           <t>01:03:30.326</t>
         </is>
       </c>
+      <c r="H153" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -35080,6 +35975,9 @@
           <t>01:05:07.663</t>
         </is>
       </c>
+      <c r="H154" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -35111,6 +36009,9 @@
           <t>01:05:25.276</t>
         </is>
       </c>
+      <c r="H155" t="n">
+        <v>5604927</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -35142,6 +36043,9 @@
           <t>01:09:46.960</t>
         </is>
       </c>
+      <c r="H156" t="n">
+        <v>5604925</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -35172,6 +36076,9 @@
         <is>
           <t>01:01:28.928</t>
         </is>
+      </c>
+      <c r="H157" t="n">
+        <v>5604925</v>
       </c>
     </row>
   </sheetData>
@@ -35185,7 +36092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35224,6 +36131,11 @@
           <t>time3</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>race_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35259,6 +36171,9 @@
           <t>13:31.808</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35290,6 +36205,9 @@
           <t>13:49.473</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35299,7 +36217,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -35325,6 +36243,9 @@
           <t>14:08.328</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35360,6 +36281,9 @@
           <t>15:20.732</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35395,6 +36319,9 @@
           <t>15:34.480</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35426,6 +36353,9 @@
           <t>15:45.128</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35457,6 +36387,9 @@
           <t>15:46.930</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35492,6 +36425,9 @@
           <t>15:56.912</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35527,6 +36463,9 @@
           <t>15:59.978</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35562,6 +36501,9 @@
           <t>16:04.572</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35597,6 +36539,9 @@
           <t>16:18.778</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35632,6 +36577,9 @@
           <t>16:20.781</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35663,6 +36611,9 @@
           <t>16:21.472</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35698,6 +36649,9 @@
           <t>16:34.408</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35733,6 +36687,9 @@
           <t>16:44.828</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35768,6 +36725,9 @@
           <t>16:52.190</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>5604934</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -35803,6 +36763,9 @@
           <t>16:54.243</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35838,6 +36801,9 @@
           <t>17:06.997</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -35847,7 +36813,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -35873,6 +36839,9 @@
           <t>17:09.200</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -35908,6 +36877,9 @@
           <t>17:09.476</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -35943,6 +36915,9 @@
           <t>17:19.299</t>
         </is>
       </c>
+      <c r="H22" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -35974,6 +36949,9 @@
           <t>17:36.649</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -36009,6 +36987,9 @@
           <t>17:39.478</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -36040,6 +37021,9 @@
           <t>17:43.586</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>5604935</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -36075,6 +37059,9 @@
           <t>17:54.932</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -36106,6 +37093,9 @@
           <t>18:13.739</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -36141,6 +37131,9 @@
           <t>18:54.224</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -36176,6 +37169,9 @@
           <t>18:56.289</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -36211,6 +37207,9 @@
           <t>19:27.002</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -36242,6 +37241,9 @@
           <t>19:35.776</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -36277,6 +37279,9 @@
           <t>19:47.771</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -36312,6 +37317,9 @@
           <t>16:19.801</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -36343,6 +37351,9 @@
           <t>17:05.523</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -36378,6 +37389,9 @@
           <t>17:19.121</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -36413,6 +37427,9 @@
           <t>17:21.370</t>
         </is>
       </c>
+      <c r="H36" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -36444,6 +37461,9 @@
           <t>17:30.708</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -36479,6 +37499,9 @@
           <t>17:33.561</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -36510,6 +37533,9 @@
           <t>17:46.581</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -36545,6 +37571,9 @@
           <t>18:29.532</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -36580,6 +37609,9 @@
           <t>18:34.306</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>5604934</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -36615,6 +37647,9 @@
           <t>18:44.929</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -36650,6 +37685,9 @@
           <t>18:58.125</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -36685,6 +37723,9 @@
           <t>18:58.696</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -36720,6 +37761,9 @@
           <t>19:05.995</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -36729,7 +37773,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -36755,6 +37799,9 @@
           <t>19:15.645</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -36790,6 +37837,9 @@
           <t>19:18.935</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -36799,7 +37849,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -36825,6 +37875,9 @@
           <t>19:25.664</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -36860,6 +37913,9 @@
           <t>19:44.722</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -36895,6 +37951,9 @@
           <t>20:01.465</t>
         </is>
       </c>
+      <c r="H50" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -36930,6 +37989,9 @@
           <t>20:16.286</t>
         </is>
       </c>
+      <c r="H51" t="n">
+        <v>5604934</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -36939,7 +38001,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -36965,6 +38027,9 @@
           <t>20:18.104</t>
         </is>
       </c>
+      <c r="H52" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -37000,6 +38065,9 @@
           <t>20:29.534</t>
         </is>
       </c>
+      <c r="H53" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -37031,6 +38099,9 @@
           <t>20:41.230</t>
         </is>
       </c>
+      <c r="H54" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -37066,6 +38137,9 @@
           <t>20:44.865</t>
         </is>
       </c>
+      <c r="H55" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -37101,6 +38175,9 @@
           <t>20:55.077</t>
         </is>
       </c>
+      <c r="H56" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -37132,6 +38209,9 @@
           <t>20:57.635</t>
         </is>
       </c>
+      <c r="H57" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -37167,6 +38247,9 @@
           <t>21:40.789</t>
         </is>
       </c>
+      <c r="H58" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -37198,6 +38281,9 @@
           <t>22:08.029</t>
         </is>
       </c>
+      <c r="H59" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -37229,6 +38315,9 @@
           <t>22:44.080</t>
         </is>
       </c>
+      <c r="H60" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -37264,6 +38353,9 @@
           <t>25:01.968</t>
         </is>
       </c>
+      <c r="H61" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -37295,6 +38387,9 @@
           <t>38:31.471</t>
         </is>
       </c>
+      <c r="H62" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -37330,6 +38425,9 @@
           <t>19:21.109</t>
         </is>
       </c>
+      <c r="H63" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -37361,6 +38459,9 @@
           <t>19:41.655</t>
         </is>
       </c>
+      <c r="H64" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -37396,6 +38497,9 @@
           <t>19:54.102</t>
         </is>
       </c>
+      <c r="H65" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -37431,6 +38535,9 @@
           <t>20:22.224</t>
         </is>
       </c>
+      <c r="H66" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -37462,6 +38569,9 @@
           <t>20:25.170</t>
         </is>
       </c>
+      <c r="H67" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -37493,6 +38603,9 @@
           <t>20:44.463</t>
         </is>
       </c>
+      <c r="H68" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -37528,6 +38641,9 @@
           <t>20:55.667</t>
         </is>
       </c>
+      <c r="H69" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -37563,6 +38679,9 @@
           <t>21:04.413</t>
         </is>
       </c>
+      <c r="H70" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -37598,6 +38717,9 @@
           <t>21:28.793</t>
         </is>
       </c>
+      <c r="H71" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -37633,6 +38755,9 @@
           <t>21:45.940</t>
         </is>
       </c>
+      <c r="H72" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -37668,6 +38793,9 @@
           <t>22:09.403</t>
         </is>
       </c>
+      <c r="H73" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -37703,6 +38831,9 @@
           <t>22:28.473</t>
         </is>
       </c>
+      <c r="H74" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -37738,6 +38869,9 @@
           <t>23:09.895</t>
         </is>
       </c>
+      <c r="H75" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -37769,6 +38903,9 @@
           <t>23:24.692</t>
         </is>
       </c>
+      <c r="H76" t="n">
+        <v>5604935</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -37804,6 +38941,9 @@
           <t>21:38.777</t>
         </is>
       </c>
+      <c r="H77" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -37839,6 +38979,9 @@
           <t>22:33.716</t>
         </is>
       </c>
+      <c r="H78" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -37870,6 +39013,9 @@
           <t>22:39.179</t>
         </is>
       </c>
+      <c r="H79" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -37905,6 +39051,9 @@
           <t>22:54.914</t>
         </is>
       </c>
+      <c r="H80" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -37940,6 +39089,9 @@
           <t>22:56.074</t>
         </is>
       </c>
+      <c r="H81" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -37949,7 +39101,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -37975,6 +39127,9 @@
           <t>23:16.078</t>
         </is>
       </c>
+      <c r="H82" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -38010,6 +39165,9 @@
           <t>23:28.475</t>
         </is>
       </c>
+      <c r="H83" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -38041,6 +39199,9 @@
           <t>24:27.518</t>
         </is>
       </c>
+      <c r="H84" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -38076,6 +39237,9 @@
           <t>24:41.858</t>
         </is>
       </c>
+      <c r="H85" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -38111,6 +39275,9 @@
           <t>24:57.241</t>
         </is>
       </c>
+      <c r="H86" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -38146,6 +39313,9 @@
           <t>25:00.961</t>
         </is>
       </c>
+      <c r="H87" t="n">
+        <v>5604931</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -38181,6 +39351,9 @@
           <t>25:17.144</t>
         </is>
       </c>
+      <c r="H88" t="n">
+        <v>5604929</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -38212,6 +39385,9 @@
           <t>25:21.604</t>
         </is>
       </c>
+      <c r="H89" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -38243,6 +39419,9 @@
           <t>26:35.426</t>
         </is>
       </c>
+      <c r="H90" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -38274,6 +39453,9 @@
           <t>29:31.924</t>
         </is>
       </c>
+      <c r="H91" t="n">
+        <v>5604933</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -38309,6 +39491,9 @@
           <t>30:35.758</t>
         </is>
       </c>
+      <c r="H92" t="n">
+        <v>5604934</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -38340,6 +39525,9 @@
           <t>27:07.445</t>
         </is>
       </c>
+      <c r="H93" t="n">
+        <v>5604932</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -38370,6 +39558,9 @@
         <is>
           <t>28:25.665</t>
         </is>
+      </c>
+      <c r="H94" t="n">
+        <v>5604932</v>
       </c>
     </row>
   </sheetData>
@@ -38383,7 +39574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38422,145 +39613,150 @@
           <t>time4</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>race_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>6863000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>01:37:55.495</t>
-        </is>
+          <t>01:06:43.833</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9152</v>
+        <v>8389020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simon Baker</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Tibo Peeters</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01:32:23.883</t>
-        </is>
+          <t>01:07:01.775</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72072</v>
+        <v>196877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Jonathan Maloney</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01:48:24.069</t>
-        </is>
+          <t>01:07:55.334</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83438</v>
+        <v>5885126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SZ</t>
-        </is>
-      </c>
+          <t>Vadim K.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01:35:31.360</t>
-        </is>
+          <t>01:08:31.070</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="6">
@@ -38571,31 +39767,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88513</v>
+        <v>6853346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jacob Ingram</t>
+          <t xml:space="preserve">Matthieu De Smet </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01:19:44.784</t>
-        </is>
+          <t>01:08:54.803</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="7">
@@ -38606,27 +39805,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>144651</v>
+        <v>599879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sho  Shimada[RD]</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>J.MORENO (TEZH RACING)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TEZH Racing</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01:17:12.707</t>
-        </is>
+          <t>01:11:13.967</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="8">
@@ -38637,93 +39843,110 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>196877</v>
+        <v>7327056</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jonathan Maloney</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>Peru Reyzabal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01:07:55.334</t>
-        </is>
+          <t>01:11:56.741</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>252310</v>
+        <v>5273193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Park Jinhea3000[TEC]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t xml:space="preserve">Raul Nieto Luque </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TEZH Racing</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01:44:16.860</t>
-        </is>
+          <t>01:12:19.724</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>260262</v>
+        <v>8106949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>A. K. Espiritu (TNP)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01:40:32.802</t>
-        </is>
+          <t>01:12:57.016</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="11">
@@ -38734,31 +39957,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>374410</v>
+        <v>432656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tom R Everested  (TNP)</t>
+          <t>Nick Baberuxki</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>Talent:frei p/b Baldiso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01:24:12.287</t>
-        </is>
+          <t>01:13:52.736</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="12">
@@ -38769,20 +39995,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>394612</v>
+        <v>1385998</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t>Andrey Galafeev[MTBtraining]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>MTBtraining</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -38792,43 +40018,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01:25:26.808</t>
-        </is>
+          <t>01:13:53.066</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>421191</v>
+        <v>4980720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Andy Davy</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02:15:04.201</t>
-        </is>
+          <t>01:14:10.486</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="14">
@@ -38843,18 +40075,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>429749</v>
+        <v>6052283</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brage Bergeng [V] </t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Vikings</t>
-        </is>
-      </c>
+          <t>Henning S&amp;oslash;ndergaard</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -38862,8 +40090,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01:18:18.232</t>
-        </is>
+          <t>01:14:17.401</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="15">
@@ -38878,27 +40109,30 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>432656</v>
+        <v>4865109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nick Baberuxki</t>
+          <t>Ryo Nakajima(CAP)[FRR]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Talent:frei p/b Baldiso</t>
+          <t>FRR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01:13:52.736</t>
-        </is>
+          <t>01:14:28.772</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="16">
@@ -38909,31 +40143,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>478958</v>
+        <v>2213032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>David Johnson</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01:26:42.616</t>
-        </is>
+          <t>01:14:31.682</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="17">
@@ -38944,22 +40177,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>599879</v>
+        <v>7552376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>J.MORENO (TEZH RACING)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TEZH Racing</t>
-        </is>
-      </c>
+          <t>HaG TaK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -38967,27 +40196,30 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01:11:13.967</t>
-        </is>
+          <t>01:14:31.859</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>619770</v>
+        <v>3044689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>Yassine Sissi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -39002,8 +40234,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01:24:17.286</t>
-        </is>
+          <t>01:14:42.676</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="19">
@@ -39040,29 +40275,32 @@
           <t>01:15:08.760</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>5604938</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>832585</v>
+        <v>1898646</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -39072,67 +40310,73 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01:50:59.699</t>
-        </is>
+          <t>01:15:37.653</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1005102</v>
+        <v>2392598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>David Pugh &amp;#127793; [Team Vegan]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Vegan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01:34:38.630</t>
-        </is>
+          <t>01:15:38.067</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1038506</v>
+        <v>6006740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
+          <t>Keegan McCormick [A-P-V]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -39142,8 +40386,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01:31:23.239</t>
-        </is>
+          <t>01:15:38.167</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="23">
@@ -39154,20 +40401,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1056287</v>
+        <v>6952720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Daniela Istrate (AEO)</t>
+          <t>Remco Vanhoutte [A-P-V]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AEO</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -39177,109 +40424,117 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01:19:20.100</t>
-        </is>
+          <t>01:15:38.454</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1121198</v>
+        <v>3188498</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos Cubas </t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Eric Auder</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01:29:57.538</t>
-        </is>
+          <t>01:16:09.689</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1260509</v>
+        <v>144651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>eiji yama</t>
+          <t>Sho  Shimada[RD]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01:36:55.390</t>
-        </is>
+          <t>01:17:12.707</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1379058</v>
+        <v>429749</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t xml:space="preserve">Brage Bergeng [V] </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01:50:55.251</t>
-        </is>
+          <t>01:18:18.232</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="27">
@@ -39290,50 +40545,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1385998</v>
+        <v>1056287</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Andrey Galafeev[MTBtraining]</t>
+          <t>Daniela Istrate (AEO)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>AEO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01:13:53.066</t>
-        </is>
+          <t>01:19:20.100</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1475359</v>
+        <v>5893609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Aled Jones</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -39343,37 +40601,40 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01:54:42.524</t>
-        </is>
+          <t>01:19:24.540</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1563175</v>
+        <v>5959135</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Ben  Spedding [TNP]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -39383,8 +40644,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01:43:08.050</t>
-        </is>
+          <t>01:19:25.004</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="30">
@@ -39399,23 +40663,30 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1572223</v>
+        <v>88513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Isamu Matsuyama</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Jacob Ingram</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01:24:13.334</t>
-        </is>
+          <t>01:19:44.784</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="31">
@@ -39430,16 +40701,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1672024</v>
+        <v>5402095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mark Vardy (INC Innovation)</t>
+          <t>Quentin Vee [EVO]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -39449,8 +40720,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01:22:37.355</t>
-        </is>
+          <t>01:19:46.295</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="32">
@@ -39465,16 +40739,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1898646</v>
+        <v>4730842</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Harris Waters(ATGNI)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -39484,8 +40758,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01:15:37.653</t>
-        </is>
+          <t>01:20:00.578</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="33">
@@ -39500,33 +40777,32 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2050391</v>
+        <v>2931254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Joice Castelo</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TugaZ</t>
-        </is>
-      </c>
+          <t>Maxime Samaille</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01:22:36.293</t>
-        </is>
+          <t>01:21:09.129</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -39535,23 +40811,30 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2206420</v>
+        <v>5023963</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Eduardo Rojas Rojas</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>Coach lak (TNP)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>01:44:16.850</t>
-        </is>
+          <t>01:21:13.104</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="35">
@@ -39562,18 +40845,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2213032</v>
+        <v>2050391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Joice Castelo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>TugaZ</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -39581,43 +40868,49 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01:14:31.682</t>
-        </is>
+          <t>01:22:36.293</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2236225</v>
+        <v>1672024</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Andy Ebbage (No GC)</t>
+          <t>Mark Vardy (INC Innovation)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DraftingDinos</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01:25:26.589</t>
-        </is>
+          <t>01:22:37.355</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="37">
@@ -39628,20 +40921,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2392598</v>
+        <v>5273300</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>David Pugh &amp;#127793; [Team Vegan]</t>
+          <t>Nate Berkopec</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Team Vegan</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -39651,14 +40944,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01:15:38.067</t>
-        </is>
+          <t>01:22:41.358</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -39667,33 +40963,36 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2560943</v>
+        <v>6715306</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mads Gronbek [DBR]</t>
+          <t>Jay Rowe</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01:37:21.282</t>
-        </is>
+          <t>01:23:40.244</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -39702,62 +41001,64 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2602856</v>
+        <v>374410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t>Tom R Everested  (TNP)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01:39:51.187</t>
-        </is>
+          <t>01:24:12.287</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2881429</v>
+        <v>1572223</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Isamu Matsuyama</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01:50:59.442</t>
-        </is>
+          <t>01:24:13.334</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="41">
@@ -39772,11 +41073,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2931254</v>
+        <v>8159437</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Maxime Samaille</t>
+          <t>Ezna Ragrts</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -39787,8 +41088,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01:21:09.129</t>
-        </is>
+          <t>01:24:36.567</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="42">
@@ -39799,20 +41103,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3044689</v>
+        <v>394612</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Yassine Sissi</t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -39822,39 +41126,49 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01:14:42.676</t>
-        </is>
+          <t>01:25:26.808</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3060368</v>
+        <v>478958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Andr&amp;eacute; Neault</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>David Johnson</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01:25:22.599</t>
-        </is>
+          <t>01:26:42.616</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="44">
@@ -39865,103 +41179,108 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3188498</v>
+        <v>3368617</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Eric Auder</t>
+          <t>David McLaughlin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01:16:09.689</t>
-        </is>
+          <t>01:26:47.311</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3228186</v>
+        <v>7053041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>William Smith (RollCo/TNP)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>01:47:17.718</t>
-        </is>
+          <t>01:28:05.211</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3294901</v>
+        <v>4350425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Sebastian Stewen</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>01:53:23.572</t>
-        </is>
+          <t>01:19:48.348</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -39970,29 +41289,36 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3368617</v>
+        <v>8325416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>David McLaughlin</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>PedroJ. L&amp;oacute;pez (TEZH)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TEZH Racing</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01:26:47.311</t>
-        </is>
+          <t>01:21:54.222</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -40001,27 +41327,30 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3477462</v>
+        <v>5877680</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Jay ONeil</t>
+          <t>Sem VH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01:31:17.826</t>
-        </is>
+          <t>01:22:37.115</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="49">
@@ -40032,31 +41361,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3614977</v>
+        <v>5139632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Heinz Ensen (Herd)</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>HERD</t>
-        </is>
-      </c>
+          <t>Thomas Mutz</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01:31:17.413</t>
-        </is>
+          <t>01:23:05.402</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="50">
@@ -40067,53 +41395,56 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4166463</v>
+        <v>619770</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t xml:space="preserve">Robert McEwan </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01:33:50.026</t>
-        </is>
+          <t>01:24:17.286</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4266511</v>
+        <v>3060368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fabio Capodei [SISU]</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Andr&amp;eacute; Neault</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>60+</t>
@@ -40121,8 +41452,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01:55:13.411</t>
-        </is>
+          <t>01:25:22.599</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="52">
@@ -40133,18 +41467,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4350425</v>
+        <v>2236225</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sebastian Stewen</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Andy Ebbage (No GC)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DraftingDinos</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -40152,32 +41490,35 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01:19:48.348</t>
-        </is>
+          <t>01:25:26.589</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4730842</v>
+        <v>4752321</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
+          <t>Alexey Tikhov (B)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ATGNI</t>
+          <t>MTBtraining</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -40187,8 +41528,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01:20:00.578</t>
-        </is>
+          <t>01:27:14.435</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="54">
@@ -40203,16 +41547,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4752321</v>
+        <v>7799511</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Alexey Tikhov (B)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -40222,32 +41566,35 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01:27:14.435</t>
-        </is>
+          <t>01:28:11.675</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4865109</v>
+        <v>6311857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ryo Nakajima(CAP)[FRR]</t>
+          <t>L ook mum no hands (RollCo)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FRR</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -40257,49 +41604,51 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01:14:28.772</t>
-        </is>
+          <t>01:28:21.685</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4980720</v>
+        <v>7072713</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+          <t>olivier fonquerne</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01:14:10.486</t>
-        </is>
+          <t>01:29:26.948</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -40308,27 +41657,26 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5023963</v>
+        <v>7410098</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Coach lak (TNP)</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Luke van Harskamp</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01:21:13.104</t>
-        </is>
+          <t>01:29:57.089</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="58">
@@ -40343,64 +41691,74 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5139632</v>
+        <v>1121198</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t xml:space="preserve">Carlos Cubas </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01:23:05.402</t>
-        </is>
+          <t>01:29:57.538</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5273193</v>
+        <v>3614977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raul Nieto Luque </t>
+          <t>Heinz Ensen (Herd)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>HERD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>01:12:19.724</t>
-        </is>
+          <t>01:31:17.413</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -40409,16 +41767,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5273300</v>
+        <v>1038506</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nate Berkopec</t>
+          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -40428,78 +41786,87 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01:22:41.358</t>
-        </is>
+          <t>01:31:23.239</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5402095</v>
+        <v>9152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01:19:46.295</t>
-        </is>
+          <t>01:32:23.883</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5491339</v>
+        <v>6991072</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>02:01:46.997</t>
-        </is>
+          <t>01:32:28.663</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="63">
@@ -40514,27 +41881,30 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5870438</v>
+        <v>5880054</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>01:33:56.507</t>
-        </is>
+          <t>01:33:49.760</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="64">
@@ -40545,22 +41915,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5877680</v>
+        <v>4166463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sem VH</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>COERS</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -40568,8 +41934,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>01:22:37.115</t>
-        </is>
+          <t>01:33:50.026</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="65">
@@ -40580,15 +41949,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5880054</v>
+        <v>5981378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -40603,45 +41972,55 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>01:33:49.760</t>
-        </is>
+          <t>01:33:50.659</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5885126</v>
+        <v>5870438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Vadim K.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>Steffen Dahlin</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DZR</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01:08:31.070</t>
-        </is>
+          <t>01:33:56.507</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -40650,68 +42029,74 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5886245</v>
+        <v>1005102</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Rasmus Dahlin (DZR)</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01:23:53.525</t>
-        </is>
+          <t>01:34:38.630</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5893609</v>
+        <v>2602856</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01:19:24.540</t>
-        </is>
+          <t>01:39:51.187</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -40720,27 +42105,30 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5959135</v>
+        <v>260262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ben  Spedding [TNP]</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01:19:25.004</t>
-        </is>
+          <t>01:40:32.802</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="70">
@@ -40751,20 +42139,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5981378</v>
+        <v>72072</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>2. Burrito &amp;#127791;</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -40774,80 +42162,93 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01:33:50.659</t>
-        </is>
+          <t>01:48:24.069</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6006740</v>
+        <v>2881429</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Keegan McCormick [A-P-V]</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01:15:38.167</t>
-        </is>
+          <t>01:50:59.442</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6052283</v>
+        <v>5886245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Henning S&amp;oslash;ndergaard</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>Rasmus Dahlin (DZR)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DZR</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01:14:17.401</t>
-        </is>
+          <t>01:23:53.525</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -40856,33 +42257,36 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6311857</v>
+        <v>7710371</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
+          <t>Karlheinz Engel - [KC&amp;#128029;]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01:28:21.685</t>
-        </is>
+          <t>01:30:39.384</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -40891,27 +42295,30 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6715306</v>
+        <v>3477462</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Jay Rowe</t>
+          <t>Jay ONeil</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>01:23:40.244</t>
-        </is>
+          <t>01:31:17.826</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="75">
@@ -40922,142 +42329,150 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6842342</v>
+        <v>6997588</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>01:44:56.282</t>
-        </is>
+          <t>01:34:32.983</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6853346</v>
+        <v>83438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthieu De Smet </t>
+          <t>Fredrik Ringstr&amp;ouml;m [SZ]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01:08:54.803</t>
-        </is>
+          <t>01:35:31.360</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6863000</v>
+        <v>1260509</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Markus Schweizer</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>WEz pb Cycling District</t>
-        </is>
-      </c>
+          <t>eiji yama</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>01:06:43.833</t>
-        </is>
+          <t>01:36:55.390</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6952720</v>
+        <v>2560943</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Remco Vanhoutte [A-P-V]</t>
+          <t>Mads Gronbek [DBR]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>01:15:38.454</t>
-        </is>
+          <t>01:37:21.282</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -41066,27 +42481,30 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6991072</v>
+        <v>25</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>01:32:28.663</t>
-        </is>
+          <t>01:37:55.495</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="80">
@@ -41097,20 +42515,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6997588</v>
+        <v>7779078</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -41120,14 +42538,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>01:34:32.983</t>
-        </is>
+          <t>01:38:22.582</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -41136,11 +42557,11 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7053041</v>
+        <v>7455653</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>William Smith (RollCo/TNP)</t>
+          <t>Justin Draper [Fellowship]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -41155,105 +42576,117 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01:28:05.211</t>
-        </is>
+          <t>01:38:27.007</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7072713</v>
+        <v>1563175</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>olivier fonquerne</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>AL C SimpSimpHea</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01:29:26.948</t>
-        </is>
+          <t>01:43:08.050</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7327056</v>
+        <v>2206420</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Peru Reyzabal</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>HISP</t>
-        </is>
-      </c>
+          <t>Eduardo Rojas Rojas</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>01:11:56.741</t>
-        </is>
+          <t>01:44:16.850</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7410098</v>
+        <v>252310</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Luke van Harskamp</t>
+          <t>Park Jinhea3000[TEC]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01:29:57.089</t>
-        </is>
+          <t>01:44:16.860</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="85">
@@ -41264,53 +42697,60 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7455653</v>
+        <v>6842342</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>01:38:27.007</t>
-        </is>
+          <t>01:44:56.282</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7552376</v>
+        <v>8149174</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>HaG TaK</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -41318,8 +42758,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>01:14:31.859</t>
-        </is>
+          <t>01:45:09.680</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="87">
@@ -41330,20 +42773,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7710371</v>
+        <v>1379058</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Karlheinz Engel - [KC&amp;#128029;]</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -41353,8 +42796,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>01:30:39.384</t>
-        </is>
+          <t>01:50:55.251</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="88">
@@ -41369,11 +42815,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7779078</v>
+        <v>832585</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -41383,32 +42829,35 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>01:38:22.582</t>
-        </is>
+          <t>01:50:59.699</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7799511</v>
+        <v>1475359</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -41418,180 +42867,206 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>01:28:11.675</t>
-        </is>
+          <t>01:54:42.524</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>5604938</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8106949</v>
+        <v>3228186</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>A. K. Espiritu (TNP)</t>
+          <t>Aidan Novis (RHINO)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>01:12:57.016</t>
-        </is>
+          <t>01:47:17.718</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8149174</v>
+        <v>3294901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Alex Stiene &amp;#127482;&amp;#127462; (TNP)</t>
+          <t>Stephen Groundwater [HERC)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>01:45:09.680</t>
-        </is>
+          <t>01:53:23.572</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>5604936</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8159437</v>
+        <v>4266511</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ezna Ragrts</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Fabio Capodei [SISU]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>SISU Racing</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01:24:36.567</t>
-        </is>
+          <t>01:55:13.411</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>5604940</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8325416</v>
+        <v>5491339</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PedroJ. L&amp;oacute;pez (TEZH)</t>
+          <t>Brian Benner (HERC)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>01:21:54.222</t>
-        </is>
+          <t>02:01:46.997</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>5604939</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8389020</v>
+        <v>421191</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tibo Peeters</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>Andy Davy</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>01:07:01.775</t>
-        </is>
+          <t>02:15:04.201</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>5604939</v>
       </c>
     </row>
   </sheetData>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2071</v>
+        <v>2032</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -785,7 +785,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2085</v>
+        <v>2069</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>1909</v>
+        <v>1870</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>2661</v>
+        <v>2645</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>1854</v>
+        <v>1866</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>A. K. Espiritu (TNP)</t>
+          <t>AKei Espiritu (TNP)</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>First &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
+          <t xml:space="preserve">  &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -6285,7 +6285,7 @@
         <v>5</v>
       </c>
       <c r="F140" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
@@ -6327,7 +6327,7 @@
         <v>4</v>
       </c>
       <c r="F141" t="n">
-        <v>1526</v>
+        <v>1539</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>5</v>
       </c>
       <c r="F145" t="n">
-        <v>1355</v>
+        <v>1372</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>4</v>
       </c>
       <c r="F150" t="n">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>4</v>
       </c>
       <c r="F153" t="n">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>1406</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>6</v>
       </c>
       <c r="F223" t="n">
-        <v>1225</v>
+        <v>1198</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>7</v>
       </c>
       <c r="F224" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>7</v>
       </c>
       <c r="F226" t="n">
-        <v>1068</v>
+        <v>1095</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>8</v>
       </c>
       <c r="F229" t="n">
-        <v>915</v>
+        <v>946</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F243" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F244" t="n">
-        <v>0</v>
+        <v>1287</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>8</v>
       </c>
       <c r="F299" t="n">
-        <v>868</v>
+        <v>808</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -13334,10 +13334,10 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr">
@@ -13410,10 +13410,10 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
@@ -13448,10 +13448,10 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A. K. Espiritu (TNP)</t>
+          <t>AKei Espiritu (TNP)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -43093,7 +43093,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>First &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
+          <t xml:space="preserve">  &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -46443,7 +46443,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C108" t="n">

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
+          <t>First &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -48395,7 +48395,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
+          <t>First &amp;#37030;&amp;#36784; &amp;#36786;&amp;#23567;&amp;#33775;</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -51986,73 +51986,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>6853346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t xml:space="preserve">Matthieu De Smet </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>46:57.756</t>
+          <t>38:50.090</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9152</v>
+        <v>6863000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simon Baker</t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>45:08.032</t>
+          <t>38:58.040</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -52062,25 +52062,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49722</v>
+        <v>877291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Charron </t>
+          <t>Nicolas Dricot</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.W.4.T</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -52090,7 +52090,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44:42.909</t>
+          <t>39:09.291</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -52100,97 +52100,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66794</v>
+        <v>6952720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Robby Parker</t>
+          <t>Remco Vanhoutte [A-P-V]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FinishStrong</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>52:19.248</t>
+          <t>40:19.734</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70401</v>
+        <v>8389020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Andy S</t>
+          <t>Tibo Peeters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>45:30.492</t>
+          <t>40:20.278</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74284</v>
+        <v>3044689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mark Feeney (COALITION)</t>
+          <t>Yassine Sissi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -52200,11 +52200,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>48:07.217</t>
+          <t>40:20.335</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="8">
@@ -52215,30 +52215,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94741</v>
+        <v>6279252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ben Bradley [ORB]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Orb</t>
-        </is>
-      </c>
+          <t>Yannik Magnussen</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>41:40.380</t>
+          <t>40:20.536</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -52248,25 +52244,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>123241</v>
+        <v>635562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M Kerry (WCC)</t>
+          <t>Charles McCarthy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>Cycling Experts</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -52276,7 +52272,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>46:45.263</t>
+          <t>40:20.734</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -52295,14 +52291,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149551</v>
+        <v>5402095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jack  Matthews</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Quentin Vee [EVO]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -52310,11 +52310,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>41:10.519</t>
+          <t>40:20.947</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="11">
@@ -52325,68 +52325,68 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>162661</v>
+        <v>4730842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cam Candelaria (CRYO-GEN)</t>
+          <t>Harris Waters(ATGNI)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>42:42.731</t>
+          <t>40:21.219</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>168494</v>
+        <v>2133020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TADEUSZ H (OMG)</t>
+          <t>Thomas Grill (TSE)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OMG</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>42:33.757</t>
+          <t>40:21.226</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -52405,64 +52405,64 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>176342</v>
+        <v>5893609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maurice Hessel (MoeDirt)</t>
+          <t>Aled Jones</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EFT p/b Eliel Cycling</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>42:43.264</t>
+          <t>40:21.924</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>193389</v>
+        <v>6006740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B.VERBEIREN (WATT)</t>
+          <t>Keegan McCormick [A-P-V]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>42:38.106</t>
+          <t>40:22.127</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -52477,36 +52477,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>226811</v>
+        <v>2165929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Adam Gascoigne</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Andreas Schitter (KC)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>41:10.210</t>
+          <t>40:23.625</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -52515,64 +52519,64 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>260262</v>
+        <v>6715306</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>Jay Rowe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45:42.621</t>
+          <t>40:26.761</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>284739</v>
+        <v>399059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mike Alford [EVO]</t>
+          <t>Alan   Glendinning</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>49:37.995</t>
+          <t>40:28.235</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -52582,39 +52586,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>356837</v>
+        <v>5687025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Joe Conley</t>
+          <t>Jonas Grunau</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>57:35.394</t>
+          <t>40:37.442</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="19">
@@ -52629,30 +52633,30 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>374410</v>
+        <v>5877680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tom R Everested  (TNP)</t>
+          <t>Sem VH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>42:57.567</t>
+          <t>40:37.948</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="20">
@@ -52663,20 +52667,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>399059</v>
+        <v>429749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Alan   Glendinning</t>
+          <t xml:space="preserve">Brage Bergeng [V] </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -52686,49 +52690,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>40:28.235</t>
+          <t>41:08.523</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>421191</v>
+        <v>795625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Andy Davy</t>
+          <t>Mike Saunders (OTR)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55:32.221</t>
+          <t>41:08.658</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="22">
@@ -52739,20 +52743,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>429749</v>
+        <v>2765354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brage Bergeng [V] </t>
+          <t>BEHE Peter Gilmore</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -52762,7 +52766,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41:08.523</t>
+          <t>41:08.704</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -52772,73 +52776,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>441381</v>
+        <v>226811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Russell Agius2 (Epsom Tri A)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Epsom Tri</t>
-        </is>
-      </c>
+          <t>Adam Gascoigne</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>52:02.863</t>
+          <t>41:10.210</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>461128</v>
+        <v>4506475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Andrew Walsh</t>
+          <t>Roman Bevz</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>46:30.530</t>
+          <t>41:10.290</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="25">
@@ -52849,40 +52849,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>478958</v>
+        <v>1161167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>David Johnson</t>
+          <t>Henrik Grundberg  [AAC]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>AAC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>45:27.660</t>
+          <t>41:10.326</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5604945</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -52891,36 +52891,32 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>504916</v>
+        <v>149551</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Simone Mado (ITA)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Team Italy</t>
-        </is>
-      </c>
+          <t>Jack  Matthews</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>42:57.390</t>
+          <t>41:10.519</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -52929,16 +52925,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>603773</v>
+        <v>6286619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eugenio Montecinos </t>
+          <t>U Will Drop Me</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>Coalition Cycling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -52948,49 +52944,49 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42:46.392</t>
+          <t>41:11.215</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>605707</v>
+        <v>4980720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jason Peters</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Glassforge</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>42:49.087</t>
+          <t>41:18.345</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="29">
@@ -53001,72 +52997,72 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>616981</v>
+        <v>94741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mike  Cuming (Saris | Nopinz)</t>
+          <t>Ben Bradley [ORB]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SARIS</t>
+          <t>Orb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>42:08.667</t>
+          <t>41:40.380</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>619770</v>
+        <v>8280250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>D L</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41:51.483</t>
+          <t>41:55.141</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="31">
@@ -53077,34 +53073,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>635562</v>
+        <v>6536177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Charles McCarthy</t>
+          <t>Jack Barton</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cycling Experts</t>
+          <t xml:space="preserve">4STAR </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>40:20.734</t>
+          <t>41:57.667</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="32">
@@ -53148,69 +53144,73 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>721114</v>
+        <v>616981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Craig Potter (WGW)</t>
+          <t>Mike  Cuming (Saris | Nopinz)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WGW</t>
+          <t>SARIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>46:29.600</t>
+          <t>42:08.667</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>722722</v>
+        <v>2005596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derek Lowe </t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>Genaro Nu&amp;ntilde;ez</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>42:43.993</t>
+          <t>42:23.474</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -53225,110 +53225,110 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>795625</v>
+        <v>162661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mike Saunders (OTR)</t>
+          <t>Cam Candelaria (CRYO-GEN)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>Team CRYO-GEN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>41:08.658</t>
+          <t>42:42.731</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>825484</v>
+        <v>7053041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jan van Leuverden</t>
+          <t>William Smith (RollCo/TNP)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BEAT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>46:42.278</t>
+          <t>42:42.775</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5604945</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>832585</v>
+        <v>176342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Maurice Hessel (MoeDirt)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>EFT p/b Eliel Cycling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>50:14.370</t>
+          <t>42:43.264</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="38">
@@ -53339,96 +53339,96 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>877291</v>
+        <v>4382631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nicolas Dricot</t>
+          <t>VICTOR MORALES  (CRP)&amp;#127483;&amp;#127466;</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>PETA-Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>39:09.291</t>
+          <t>42:43.267</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1005102</v>
+        <v>7484167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Edmund Tang</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>45:34.855</t>
+          <t>42:46.269</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1038506</v>
+        <v>5851455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
+          <t>taku hata</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -53438,17 +53438,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>45:31.368</t>
+          <t>42:54.445</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -53457,22 +53457,26 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1065618</v>
+        <v>4487255</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Yuru Kuzmin[VeloKavkaz]</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>Volker Kr&amp;uuml;ger  (WattFabrik)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WATTFabrik</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>46:48.325</t>
+          <t>42:56.762</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -53482,7 +53486,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -53491,49 +53495,49 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1106558</v>
+        <v>374410</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thomas Rattini  [SST]</t>
+          <t>Tom R Everested  (TNP)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Scannellatori</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>42:57.836</t>
+          <t>42:57.567</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1115697</v>
+        <v>2213032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mark Topham</t>
+          <t>Ben Howell</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -53544,11 +53548,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>46:17.216</t>
+          <t>42:58.803</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="44">
@@ -53563,102 +53567,102 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1161167</v>
+        <v>4192318</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Henrik Grundberg  [AAC]</t>
+          <t>Eli Jones</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>41:10.326</t>
+          <t>43:16.946</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1379058</v>
+        <v>2914276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Eugene Shuster</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>50:10.835</t>
+          <t>45:08.703</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1392843</v>
+        <v>478958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Zsolt Kun-Szabo</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>David Johnson</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>45:09.182</t>
+          <t>45:27.660</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="47">
@@ -53669,26 +53673,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1455555</v>
+        <v>5959135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Uli Diedrichsen</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Ben  Spedding [TNP]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>45:55.013</t>
+          <t>45:54.993</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -53698,63 +53706,59 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1475359</v>
+        <v>1455555</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Uli Diedrichsen</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>48:21.275</t>
+          <t>45:55.013</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5604947</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1516811</v>
+        <v>3006259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jamie Roy</t>
+          <t>Lennart Pol</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stages Cycling</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -53764,35 +53768,35 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>46:30.651</t>
+          <t>45:55.515</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5604950</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1563175</v>
+        <v>8262983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Tuco  Benedicto (TEZH)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -53802,11 +53806,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>46:54.038</t>
+          <t>45:58.245</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5604945</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="51">
@@ -53821,102 +53825,94 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1788830</v>
+        <v>5139632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Marlon Tang (EVO/FSR/HERC/MBC)</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Thomas Mutz</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45:32.056</t>
+          <t>41:06.208</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2005596</v>
+        <v>2690737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Genaro Nu&amp;ntilde;ez</t>
+          <t>Patrick Molinari (INTRCPTR-RT)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>Interceptor RT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>42:23.474</t>
+          <t>41:09.056</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2133020</v>
+        <v>4791080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thomas Grill (TSE)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>TSE</t>
-        </is>
-      </c>
+          <t>karl moreaux</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>40:21.226</t>
+          <t>41:11.882</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -53926,35 +53922,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2165929</v>
+        <v>619770</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Andreas Schitter (KC)</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>40:23.625</t>
+          <t>41:51.483</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -53964,65 +53960,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2208583</v>
+        <v>7410098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ethan Crain</t>
+          <t>Luke van Harskamp</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>46:31.341</t>
+          <t>42:23.934</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2213032</v>
+        <v>168494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ben Ben Howell</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>TADEUSZ H (OMG)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OMG</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>42:58.803</t>
+          <t>42:33.757</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -54041,16 +54041,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2236225</v>
+        <v>193389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Andy Ebbage (No GC)</t>
+          <t>B.VERBEIREN (WATT)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DraftingDinos</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -54060,7 +54060,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>42:57.334</t>
+          <t>42:38.106</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -54070,41 +54070,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2288977</v>
+        <v>722722</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>H Suzu&amp;#128150;</t>
+          <t xml:space="preserve">Derek Lowe </t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>54:25.788</t>
+          <t>42:43.993</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -54113,36 +54113,36 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2602856</v>
+        <v>603773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t xml:space="preserve">Eugenio Montecinos </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>45:09.122</t>
+          <t>42:46.392</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -54151,22 +54151,26 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2623657</v>
+        <v>605707</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nathan True2168</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Jason Peters</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Glassforge</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>42:47.371</t>
+          <t>42:49.087</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -54176,39 +54180,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2648548</v>
+        <v>6489023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Marko J&amp;auml;rvenp&amp;auml;&amp;auml;</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>50:14.634</t>
+          <t>42:56.346</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="62">
@@ -54223,16 +54223,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2690737</v>
+        <v>2236225</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Patrick Molinari (INTRCPTR-RT)</t>
+          <t>Andy Ebbage (No GC)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Interceptor RT</t>
+          <t>DraftingDinos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -54242,35 +54242,35 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>41:09.056</t>
+          <t>42:57.334</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2765354</v>
+        <v>504916</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BEHE Peter Gilmore</t>
+          <t>Simone Mado (ITA)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -54280,11 +54280,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>41:08.704</t>
+          <t>42:57.390</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="64">
@@ -54295,74 +54295,74 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2881429</v>
+        <v>1106558</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Thomas Rattini  [SST]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Scannellatori</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>45:30.177</t>
+          <t>42:57.836</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2901486</v>
+        <v>6866514</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ingrid Klocke</t>
+          <t>Dennis Livesay</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>52:05.019</t>
+          <t>43:56.130</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -54371,64 +54371,68 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2914276</v>
+        <v>7364132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Eugene Shuster</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>Eddie Adams</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>45:08.703</t>
+          <t>43:57.081</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2984059</v>
+        <v>5880054</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bruce Novis</t>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NOVIS</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>53:06.743</t>
+          <t>44:42.363</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="68">
@@ -54443,87 +54447,87 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2988740</v>
+        <v>49722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t xml:space="preserve">Xavier Charron </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>5.W.4.T</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>45:34.040</t>
+          <t>44:42.909</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3006259</v>
+        <v>5981378</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lennart Pol</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45:55.515</t>
+          <t>44:46.265</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>5604946</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3044689</v>
+        <v>6991072</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Yassine Sissi</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -54538,7 +54542,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>40:20.335</t>
+          <t>45:09.662</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -54548,7 +54552,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -54557,32 +54561,36 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3053558</v>
+        <v>6311857</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cristian Montero</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>L ook mum no hands (RollCo)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>44:08.751</t>
+          <t>45:09.971</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -54591,90 +54599,90 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3224040</v>
+        <v>5918191</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PAUL      ZU&amp;Ntilde;IGA</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>R&amp;eacute;gis Thomas (Bikes-FR)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>42:52.181</t>
+          <t>45:10.275</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3228186</v>
+        <v>2881429</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>53:00.922</t>
+          <t>45:30.177</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3294901</v>
+        <v>70401</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Andy S</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>50+</t>
@@ -54682,17 +54690,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>50:27.559</t>
+          <t>45:30.492</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5604945</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -54701,22 +54709,26 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3564783</v>
+        <v>1038506</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>P Colo</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Vikings</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>47:10.819</t>
+          <t>45:31.368</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -54726,23 +54738,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3732567</v>
+        <v>1788830</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Adam Levin</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>Marlon Tang (EVO/FSR/HERC/MBC)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -54750,35 +54766,35 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>57:35.811</t>
+          <t>45:32.056</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>5604950</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3894706</v>
+        <v>2988740</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mauro Malatesta</t>
+          <t>Tony Cal [TSE]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -54788,35 +54804,35 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>58:42.537</t>
+          <t>45:34.040</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4107226</v>
+        <v>1005102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lars Falck [V]</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -54826,55 +54842,55 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>50:02.253</t>
+          <t>45:34.855</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4127743</v>
+        <v>260262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jos&amp;eacute; Ignacio URZUA</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>50:03.243</t>
+          <t>45:42.621</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>5604950</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -54883,36 +54899,32 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4192318</v>
+        <v>1115697</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Eli Jones</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Mark Topham</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>43:16.946</t>
+          <t>46:17.216</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -54921,108 +54933,100 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4382631</v>
+        <v>6118343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VICTOR MORALES  (CRP)&amp;#127483;&amp;#127466;</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PETA-Z</t>
-        </is>
-      </c>
+          <t>Christophe Chris [BIKES-FR]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>42:43.267</t>
+          <t>46:24.649</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4487255</v>
+        <v>7376425</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Volker Kr&amp;uuml;ger  (WattFabrik)</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>WATTFabrik</t>
-        </is>
-      </c>
+          <t>JakOnWheels   Attack</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>42:56.762</t>
+          <t>46:27.196</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4506475</v>
+        <v>6559107</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Roman Bevz</t>
+          <t>S Thrashco</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>41:10.290</t>
+          <t>46:34.184</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -55031,30 +55035,26 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4730842</v>
+        <v>7589756</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ATGNI</t>
-        </is>
-      </c>
+          <t>Kasper Steadywheel</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>40:21.219</t>
+          <t>46:45.815</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="85">
@@ -55065,26 +55065,30 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4791080</v>
+        <v>5804361</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>karl moreaux</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>. WILLETTS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>BAKPDL</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>41:11.882</t>
+          <t>46:53.302</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -55094,7 +55098,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -55103,16 +55107,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4801108</v>
+        <v>74284</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jorge Ar&amp;eacute;valo</t>
+          <t>Mark Feeney (COALITION)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -55122,35 +55126,35 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>47:30.384</t>
+          <t>48:07.217</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4980720</v>
+        <v>7799511</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -55160,11 +55164,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>41:18.345</t>
+          <t>48:21.340</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="88">
@@ -55175,40 +55179,36 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5086087</v>
+        <v>2623657</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Miguel Loureiro</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Nathan True2168</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>49:18.384</t>
+          <t>42:47.371</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -55217,11 +55217,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5139632</v>
+        <v>3224040</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
+          <t>PAUL      ZU&amp;Ntilde;IGA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -55232,37 +55232,33 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>41:06.208</t>
+          <t>42:52.181</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5402095</v>
+        <v>5992789</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>Mathieu Gosselin</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -55270,83 +55266,79 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>40:20.947</t>
+          <t>42:56.888</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5491339</v>
+        <v>3053558</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Cristian Montero</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>50:01.560</t>
+          <t>44:08.751</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5687025</v>
+        <v>7582753</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Jonas Grunau</t>
+          <t>Dan Thomas</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>40:37.442</t>
+          <t>45:07.711</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -55356,35 +55348,35 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5804361</v>
+        <v>9152</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>. WILLETTS</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BAKPDL</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>46:53.302</t>
+          <t>45:08.032</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -55394,45 +55386,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5851455</v>
+        <v>2602856</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>taku hata</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>42:54.445</t>
+          <t>45:09.122</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -55441,26 +55433,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5877680</v>
+        <v>1392843</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sem VH</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>COERS</t>
-        </is>
-      </c>
+          <t>Zsolt Kun-Szabo</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>40:37.948</t>
+          <t>45:09.182</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -55470,77 +55458,73 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5880054</v>
+        <v>7105167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>S R T</t>
-        </is>
-      </c>
+          <t>Erik Grindbakken</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>44:42.363</t>
+          <t>46:27.111</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5893609</v>
+        <v>721114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
+          <t>Craig Potter (WGW)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>WGW</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>40:21.924</t>
+          <t>46:29.600</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="98">
@@ -55555,112 +55539,108 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5895690</v>
+        <v>461128</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Franco Borrini</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Team Italy</t>
-        </is>
-      </c>
+          <t>Andrew Walsh</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51:35.393</t>
+          <t>46:30.530</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5918191</v>
+        <v>1516811</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R&amp;eacute;gis Thomas (Bikes-FR)</t>
+          <t>Jamie Roy</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BIKES &amp;#11088;&amp;#65039;</t>
+          <t>Stages Cycling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>45:10.275</t>
+          <t>46:30.651</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5959135</v>
+        <v>825484</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ben  Spedding [TNP]</t>
+          <t>Jan van Leuverden</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BEAT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>45:54.993</t>
+          <t>46:42.278</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>5604946</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -55669,26 +55649,26 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5981378</v>
+        <v>123241</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>M Kerry (WCC)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>WCC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>44:46.265</t>
+          <t>46:45.263</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -55707,60 +55687,60 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5992789</v>
+        <v>6997588</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mathieu Gosselin</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>42:56.888</t>
+          <t>46:45.606</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6006740</v>
+        <v>1065618</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Keegan McCormick [A-P-V]</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>A-P-V</t>
-        </is>
-      </c>
+          <t>Yuru Kuzmin[VeloKavkaz]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>40:22.127</t>
+          <t>46:48.325</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -55770,23 +55750,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6118343</v>
+        <v>1563175</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Christophe Chris [BIKES-FR]</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>AL C SimpSimpHea</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -55794,89 +55778,93 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>46:24.649</t>
+          <t>46:54.038</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6279252</v>
+        <v>7779078</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Yannik Magnussen</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>40:20.536</t>
+          <t>46:56.468</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6286619</v>
+        <v>25</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>U Will Drop Me</t>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coalition Cycling</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>41:11.215</t>
+          <t>46:57.756</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -55885,18 +55873,14 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6311857</v>
+        <v>3564783</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RollCo</t>
-        </is>
-      </c>
+          <t>P Colo</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -55904,17 +55888,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>45:09.971</t>
+          <t>47:10.819</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -55923,14 +55907,18 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6489023</v>
+        <v>4801108</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Marko J&amp;auml;rvenp&amp;auml;&amp;auml;</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>Jorge Ar&amp;eacute;valo</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Velo&amp;#039;Z</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -55938,17 +55926,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>42:56.346</t>
+          <t>47:30.384</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -55957,16 +55945,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6513233</v>
+        <v>7283905</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>sean carter [WMZ]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -55976,7 +55964,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>50:14.612</t>
+          <t>48:23.912</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -55986,35 +55974,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6536177</v>
+        <v>5086087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Jack Barton</t>
+          <t>Miguel Loureiro</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>41:57.667</t>
+          <t>49:18.384</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -56024,73 +56012,77 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6559107</v>
+        <v>284739</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>S Thrashco</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Mike Alford [EVO]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>46:34.184</t>
+          <t>49:37.995</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6715306</v>
+        <v>4127743</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Jay Rowe</t>
+          <t>Jos&amp;eacute; Ignacio URZUA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>Velo&amp;#039;Z</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>40:26.761</t>
+          <t>50:03.243</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="113">
@@ -56105,128 +56097,132 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6842342</v>
+        <v>1379058</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>51:04.185</t>
+          <t>50:10.835</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>5604950</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6853346</v>
+        <v>832585</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthieu De Smet </t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>38:50.090</t>
+          <t>50:14.370</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6863000</v>
+        <v>6842342</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Markus Schweizer</t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>WEz pb Cycling District</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>38:58.040</t>
+          <t>51:04.185</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6866514</v>
+        <v>5895690</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Dennis Livesay</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>Franco Borrini</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>50+</t>
@@ -56234,35 +56230,35 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>43:56.130</t>
+          <t>51:35.393</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6952720</v>
+        <v>7455653</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Remco Vanhoutte [A-P-V]</t>
+          <t>Justin Draper [Fellowship]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -56272,45 +56268,41 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>40:19.734</t>
+          <t>52:28.846</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>5604947</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6991072</v>
+        <v>7654466</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nicolas Schmitt</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>45:09.662</t>
+          <t>45:09.588</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -56320,27 +56312,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="C119" t="n">
-        <v>6997588</v>
+        <v>2208583</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
-        </is>
-      </c>
+          <t>Ethan Crain</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>50+</t>
@@ -56348,30 +56336,30 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>46:45.606</t>
+          <t>46:31.341</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7053041</v>
+        <v>1475359</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>William Smith (RollCo/TNP)</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -56381,38 +56369,42 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>42:42.775</t>
+          <t>48:21.275</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>7105167</v>
+        <v>5491339</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erik Grindbakken</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>Brian Benner (HERC)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>50+</t>
@@ -56420,93 +56412,93 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>46:27.111</t>
+          <t>50:01.560</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C122" t="n">
-        <v>7283905</v>
+        <v>4107226</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>sean carter [WMZ]</t>
+          <t>Lars Falck [V]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>48:23.912</t>
+          <t>50:02.253</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7364132</v>
+        <v>6513233</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Eddie Adams</t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>43:57.081</t>
+          <t>50:14.612</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -56515,204 +56507,212 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7376425</v>
+        <v>2648548</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>JakOnWheels   Attack</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>Claire Greensides [HERC]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>46:27.196</t>
+          <t>50:14.634</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7410098</v>
+        <v>3294901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Luke van Harskamp</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>42:23.934</t>
+          <t>50:27.559</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="C126" t="n">
-        <v>7455653</v>
+        <v>441381</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
+          <t>Russell Agius2 (Epsom Tri A)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Epsom Tri</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>52:28.846</t>
+          <t>52:02.863</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5604946</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7484167</v>
+        <v>2901486</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Edmund Tang</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Ingrid Klocke</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>42:46.269</t>
+          <t>52:05.019</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C128" t="n">
-        <v>7582753</v>
+        <v>66794</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Dan Thomas</t>
+          <t>Robby Parker</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>FinishStrong</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45:07.711</t>
+          <t>52:19.248</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7589756</v>
+        <v>3228186</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Kasper Steadywheel</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>46:45.815</t>
+          <t>53:00.922</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -56727,64 +56727,64 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7654466</v>
+        <v>2984059</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Nicolas Schmitt</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Bruce Novis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NOVIS</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>45:09.588</t>
+          <t>53:06.743</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C131" t="n">
-        <v>7779078</v>
+        <v>2288977</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>David Irwin</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>H Suzu&amp;#128150;</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>46:56.468</t>
+          <t>54:25.788</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -56794,20 +56794,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7799511</v>
+        <v>421191</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Andy Davy</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -56817,12 +56817,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>48:21.340</t>
+          <t>55:32.221</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -56832,58 +56832,58 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>8262983</v>
+        <v>356837</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tuco  Benedicto (TEZH)</t>
+          <t>Joe Conley</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>45:58.245</t>
+          <t>57:35.394</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>5604946</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>8280250</v>
+        <v>3894706</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>D L</t>
+          <t>Mauro Malatesta</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -56893,35 +56893,35 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>41:55.141</t>
+          <t>58:42.537</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8389020</v>
+        <v>3732567</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tibo Peeters</t>
+          <t>Adam Levin</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -56932,11 +56932,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>40:20.278</t>
+          <t>57:35.811</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
   </sheetData>

--- a/LaBlanca/LaBlanca.xlsx
+++ b/LaBlanca/LaBlanca.xlsx
@@ -18197,73 +18197,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>6853346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+          <t xml:space="preserve">Matthieu De Smet </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>46:57.756</t>
+          <t>38:50.090</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9152</v>
+        <v>6863000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simon Baker</t>
+          <t>Markus Schweizer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>WEz pb Cycling District</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>45:08.032</t>
+          <t>38:58.040</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -18273,25 +18273,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49722</v>
+        <v>877291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Charron </t>
+          <t>Nicolas Dricot</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.W.4.T</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44:42.909</t>
+          <t>39:09.291</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -18311,97 +18311,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66794</v>
+        <v>6952720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Robby Parker</t>
+          <t>Remco Vanhoutte [A-P-V]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FinishStrong</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>52:19.248</t>
+          <t>40:19.734</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70401</v>
+        <v>8389020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Andy S</t>
+          <t>Tibo Peeters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>45:30.492</t>
+          <t>40:20.278</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74284</v>
+        <v>3044689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mark Feeney (COALITION)</t>
+          <t>Yassine Sissi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -18411,11 +18411,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>48:07.217</t>
+          <t>40:20.335</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="8">
@@ -18426,30 +18426,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94741</v>
+        <v>6279252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ben Bradley [ORB]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Orb</t>
-        </is>
-      </c>
+          <t>Yannik Magnussen</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>41:40.380</t>
+          <t>40:20.536</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -18459,25 +18455,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>123241</v>
+        <v>635562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M Kerry (WCC)</t>
+          <t>Charles McCarthy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>Cycling Experts</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -18487,7 +18483,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>46:45.263</t>
+          <t>40:20.734</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -18506,14 +18502,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149551</v>
+        <v>5402095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jack  Matthews</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Quentin Vee [EVO]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -18521,11 +18521,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>41:10.519</t>
+          <t>40:20.947</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="11">
@@ -18536,68 +18536,68 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>162661</v>
+        <v>4730842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cam Candelaria (CRYO-GEN)</t>
+          <t>Harris Waters(ATGNI)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>42:42.731</t>
+          <t>40:21.219</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>168494</v>
+        <v>2133020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TADEUSZ H (OMG)</t>
+          <t>Thomas Grill (TSE)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OMG</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>42:33.757</t>
+          <t>40:21.226</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -18616,64 +18616,64 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>176342</v>
+        <v>5893609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maurice Hessel (MoeDirt)</t>
+          <t>Aled Jones</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EFT p/b Eliel Cycling</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>42:43.264</t>
+          <t>40:21.924</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>193389</v>
+        <v>6006740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B.VERBEIREN (WATT)</t>
+          <t>Keegan McCormick [A-P-V]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>42:38.106</t>
+          <t>40:22.127</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -18688,36 +18688,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>226811</v>
+        <v>2165929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Adam Gascoigne</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Andreas Schitter (KC)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>41:10.210</t>
+          <t>40:23.625</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -18726,64 +18730,64 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>260262</v>
+        <v>6715306</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>Jay Rowe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45:42.621</t>
+          <t>40:26.761</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>284739</v>
+        <v>399059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mike Alford [EVO]</t>
+          <t>Alan   Glendinning</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>49:37.995</t>
+          <t>40:28.235</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -18793,39 +18797,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>356837</v>
+        <v>5687025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Joe Conley</t>
+          <t>Jonas Grunau</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>57:35.394</t>
+          <t>40:37.442</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="19">
@@ -18840,30 +18844,30 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>374410</v>
+        <v>5877680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tom Ross  (TNP)</t>
+          <t>Sem VH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>COERS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>42:57.567</t>
+          <t>40:37.948</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="20">
@@ -18874,20 +18878,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>399059</v>
+        <v>429749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Alan   Glendinning</t>
+          <t xml:space="preserve">Brage Bergeng [V] </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -18897,49 +18901,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>40:28.235</t>
+          <t>41:08.523</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>421191</v>
+        <v>795625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Andy Davy</t>
+          <t>Mike Saunders (OTR)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55:32.221</t>
+          <t>41:08.658</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="22">
@@ -18950,20 +18954,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>429749</v>
+        <v>2765354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brage Bergeng [V] </t>
+          <t>BEHE Peter Gilmore</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -18973,7 +18977,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41:08.523</t>
+          <t>41:08.704</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -18983,73 +18987,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>441381</v>
+        <v>226811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Russell Agius2 (Epsom Tri A)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Epsom Tri</t>
-        </is>
-      </c>
+          <t>Adam Gascoigne</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>52:02.863</t>
+          <t>41:10.210</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>461128</v>
+        <v>4506475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Andrew Walsh</t>
+          <t>Roman Bevz</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>46:30.530</t>
+          <t>41:10.290</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="25">
@@ -19060,40 +19060,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>478958</v>
+        <v>1161167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>David Johnson</t>
+          <t>Henrik Grundberg  [AAC]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>AAC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>45:27.660</t>
+          <t>41:10.326</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5604945</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -19102,36 +19102,32 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>504916</v>
+        <v>149551</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Simone Mado (ITA)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Team Italy</t>
-        </is>
-      </c>
+          <t>Jack  Matthews</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>42:57.390</t>
+          <t>41:10.519</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -19140,16 +19136,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>603773</v>
+        <v>6286619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eugenio Montecinos </t>
+          <t>U Will Drop Me</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>Coalition Cycling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -19159,49 +19155,49 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42:46.392</t>
+          <t>41:11.215</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>605707</v>
+        <v>4980720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jason Peters</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Glassforge</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>42:49.087</t>
+          <t>41:18.345</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="29">
@@ -19212,72 +19208,72 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>616981</v>
+        <v>94741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mike  Cuming (Saris | Nopinz)</t>
+          <t>Ben Bradley [ORB]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SARIS</t>
+          <t>Orb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>42:08.667</t>
+          <t>41:40.380</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>619770</v>
+        <v>8280250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>D L</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41:51.483</t>
+          <t>41:55.141</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="31">
@@ -19288,34 +19284,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>635562</v>
+        <v>6536177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Charles McCarthy</t>
+          <t>Jack Barton</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cycling Experts</t>
+          <t xml:space="preserve">4STAR </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>40:20.734</t>
+          <t>41:57.667</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="32">
@@ -19326,30 +19322,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>637897</v>
+        <v>679077</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>David Whitfield &amp;#127482;&amp;#127480; &amp;#127482;&amp;#127462;</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Den Morrison</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>45:14.082</t>
+          <t>41:59.330</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5604951</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="33">
@@ -19364,26 +19364,26 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>679077</v>
+        <v>616981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
+          <t>Mike  Cuming (Saris | Nopinz)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>SARIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>41:59.330</t>
+          <t>42:08.667</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -19393,45 +19393,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>721114</v>
+        <v>2005596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Craig Potter (WGW)</t>
+          <t>Genaro Nu&amp;ntilde;ez</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WGW</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>46:29.600</t>
+          <t>42:23.474</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -19440,14 +19440,18 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>722722</v>
+        <v>162661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derek Lowe </t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Cam Candelaria (CRYO-GEN)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Team CRYO-GEN</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>50+</t>
@@ -19455,7 +19459,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42:43.993</t>
+          <t>42:42.731</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -19470,30 +19474,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>795625</v>
+        <v>7053041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mike Saunders (OTR)</t>
+          <t>William Smith (RollCo/TNP)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>41:08.658</t>
+          <t>42:42.775</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -19503,77 +19507,77 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>825484</v>
+        <v>176342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jan van Leuverden</t>
+          <t>Maurice Hessel (MoeDirt)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BEAT</t>
+          <t>EFT p/b Eliel Cycling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>46:42.278</t>
+          <t>42:43.264</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>832585</v>
+        <v>4382631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>VICTOR MORALES &amp;#127483;&amp;#127466;</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>PETA-Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>50:14.370</t>
+          <t>42:43.267</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="39">
@@ -19584,78 +19588,78 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>877291</v>
+        <v>7484167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nicolas Dricot</t>
+          <t>Edmund Tang</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>39:09.291</t>
+          <t>42:46.269</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1005102</v>
+        <v>5851455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>taku hata</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>45:34.855</t>
+          <t>42:54.445</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -19664,36 +19668,36 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1038506</v>
+        <v>4487255</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
+          <t>Volker Kr&amp;uuml;ger  (WattFabrik)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>WATTFabrik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>45:31.368</t>
+          <t>42:56.762</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -19702,52 +19706,52 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1065618</v>
+        <v>374410</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Yuru Kuzmin[VeloKavkaz]</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>Tom Ross  (TNP)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BIKELY</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>46:48.325</t>
+          <t>42:57.567</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1106558</v>
+        <v>2213032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thomas Rattini  [SST]</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Scannellatori</t>
-        </is>
-      </c>
+          <t>Ben Howell</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -19755,7 +19759,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>42:57.836</t>
+          <t>42:58.803</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -19765,7 +19769,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19774,26 +19778,30 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1115697</v>
+        <v>4192318</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mark Topham</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>Eli Jones</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>46:17.216</t>
+          <t>43:16.946</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="45">
@@ -19808,56 +19816,48 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1161167</v>
+        <v>2914276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Henrik Grundberg  [AAC]</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AAC</t>
-        </is>
-      </c>
+          <t>Eugene Shuster</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41:10.326</t>
+          <t>45:08.703</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1379058</v>
+        <v>637897</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>David Whitfield &amp;#127482;&amp;#127480; &amp;#127482;&amp;#127462;</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>60+</t>
@@ -19865,45 +19865,49 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>50:10.835</t>
+          <t>45:14.082</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5604945</v>
+        <v>5604951</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1392843</v>
+        <v>478958</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zsolt Kun-Szabo</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>David Johnson</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>45:09.182</t>
+          <t>45:27.660</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="48">
@@ -19914,26 +19918,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1455555</v>
+        <v>5959135</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Uli Diedrichsen</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>Ben  Spedding [TNP]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>45:55.013</t>
+          <t>45:54.993</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -19943,63 +19951,59 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1475359</v>
+        <v>1455555</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Uli Diedrichsen</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>48:21.275</t>
+          <t>45:55.013</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5604947</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1516811</v>
+        <v>3006259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Jamie Roy</t>
+          <t>Lennart Pol</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stages Cycling</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -20009,35 +20013,35 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>46:30.651</t>
+          <t>45:55.515</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5604950</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1563175</v>
+        <v>8262983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Tuco  Benedicto (TEZH)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -20047,11 +20051,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>46:54.038</t>
+          <t>45:58.245</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5604945</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="52">
@@ -20066,102 +20070,94 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1788830</v>
+        <v>5139632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Marlon Tang (EVO/FSR/HERC/MBC)</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Thomas Mutz</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>45:32.056</t>
+          <t>41:06.208</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2005596</v>
+        <v>2690737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Genaro Nu&amp;ntilde;ez</t>
+          <t>Patrick Molinari (INTRCPTR-RT)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>Interceptor RT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>42:23.474</t>
+          <t>41:09.056</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2133020</v>
+        <v>4791080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thomas Grill (TSE)</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>TSE</t>
-        </is>
-      </c>
+          <t>karl moreaux</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>40:21.226</t>
+          <t>41:11.882</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -20171,35 +20167,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2165929</v>
+        <v>619770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Andreas Schitter (KC)</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>40:23.625</t>
+          <t>41:51.483</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -20209,65 +20205,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2208583</v>
+        <v>7410098</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ethan Crain</t>
+          <t>Luke van Harskamp</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>46:31.341</t>
+          <t>42:23.934</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2213032</v>
+        <v>168494</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ben Howell</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>TADEUSZ H (OMG)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OMG</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>42:58.803</t>
+          <t>42:33.757</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -20286,16 +20286,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2236225</v>
+        <v>193389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Andy Ebbage</t>
+          <t>B.VERBEIREN (WATT)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DraftingDinos</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>42:57.334</t>
+          <t>42:38.106</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -20315,41 +20315,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2288977</v>
+        <v>722722</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>H Suzu&amp;#128150;</t>
+          <t xml:space="preserve">Derek Lowe </t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>54:25.788</t>
+          <t>42:43.993</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -20358,36 +20358,36 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2602856</v>
+        <v>603773</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t xml:space="preserve">Eugenio Montecinos </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45:09.122</t>
+          <t>42:46.392</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -20396,22 +20396,26 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2623657</v>
+        <v>605707</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nathan True2168</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Jason Peters</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Glassforge</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>42:47.371</t>
+          <t>42:49.087</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -20421,39 +20425,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2648548</v>
+        <v>6489023</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Marko J&amp;auml;rvenp&amp;auml;&amp;auml;</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>50:14.634</t>
+          <t>42:56.346</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="63">
@@ -20468,16 +20468,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2690737</v>
+        <v>2236225</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Patrick Molinari (INTRCPTR-RT)</t>
+          <t>Andy Ebbage</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Interceptor RT</t>
+          <t>DraftingDinos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -20487,35 +20487,35 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>41:09.056</t>
+          <t>42:57.334</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2765354</v>
+        <v>504916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BEHE Peter Gilmore</t>
+          <t>Simone Mado (ITA)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -20525,11 +20525,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>41:08.704</t>
+          <t>42:57.390</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="65">
@@ -20540,74 +20540,74 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2881429</v>
+        <v>1106558</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Thomas Rattini  [SST]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Scannellatori</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45:30.177</t>
+          <t>42:57.836</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2901486</v>
+        <v>6866514</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ingrid Klocke</t>
+          <t>Dennis Livesay</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>52:05.019</t>
+          <t>43:56.130</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -20616,64 +20616,68 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2914276</v>
+        <v>7364132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Eugene Shuster</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>Eddie Adams</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>45:08.703</t>
+          <t>43:57.081</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2984059</v>
+        <v>5880054</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bruce Novis</t>
+          <t>Kyle Sremaniak (GXY / SRT)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NOVIS</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>53:06.743</t>
+          <t>44:42.363</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="69">
@@ -20688,87 +20692,87 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2988740</v>
+        <v>49722</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tony Cal [TSE]</t>
+          <t xml:space="preserve">Xavier Charron </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>5.W.4.T</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45:34.040</t>
+          <t>44:42.909</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3006259</v>
+        <v>5981378</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lennart Pol</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>45:55.515</t>
+          <t>44:46.265</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>5604946</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3044689</v>
+        <v>6991072</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Yassine Sissi</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -20783,7 +20787,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>40:20.335</t>
+          <t>45:09.662</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -20793,7 +20797,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -20802,32 +20806,36 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3053558</v>
+        <v>6311857</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cristian Montero</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>L ook mum no hands (RollCo)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>44:08.751</t>
+          <t>45:09.971</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -20836,90 +20844,90 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3224040</v>
+        <v>5918191</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PAUL      ZU&amp;Ntilde;IGA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>R&amp;eacute;gis Thomas (Bikes-FR)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>42:52.181</t>
+          <t>45:10.275</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3228186</v>
+        <v>2881429</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Aidan Novis (RHINO)</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>53:00.922</t>
+          <t>45:30.177</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3294901</v>
+        <v>70401</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Stephen Groundwater [HERC)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Andy S</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>50+</t>
@@ -20927,17 +20935,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>50:27.559</t>
+          <t>45:30.492</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5604945</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -20946,22 +20954,26 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3564783</v>
+        <v>1038506</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>P Colo</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Vikings</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>47:10.819</t>
+          <t>45:31.368</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -20971,171 +20983,175 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3712273</v>
+        <v>1788830</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CHRIS D</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>Marlon Tang (EVO/FSR/HERC/MBC)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>51:21.363</t>
+          <t>45:32.056</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>5604951</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3732567</v>
+        <v>2988740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Adam Levin</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>Tony Cal [TSE]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>57:35.811</t>
+          <t>45:34.040</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>5604950</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3894706</v>
+        <v>1005102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mauro Malatesta</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>58:42.537</t>
+          <t>45:34.855</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4107226</v>
+        <v>260262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lars Falck [V]</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>50:02.253</t>
+          <t>45:42.621</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4127743</v>
+        <v>1115697</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Jos&amp;eacute; Ignacio URZUA</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Velo&amp;#039;Z</t>
-        </is>
-      </c>
+          <t>Mark Topham</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -21143,17 +21159,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>50:03.243</t>
+          <t>46:17.216</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -21162,74 +21178,66 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4192318</v>
+        <v>6118343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Eli Jones</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Christophe Chris [BIKES-FR]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>43:16.946</t>
+          <t>46:24.649</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4382631</v>
+        <v>7376425</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VICTOR MORALES &amp;#127483;&amp;#127466;</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>PETA-Z</t>
-        </is>
-      </c>
+          <t>JakOnWheels   Attack</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>42:43.267</t>
+          <t>46:27.196</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5604950</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -21238,36 +21246,32 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4487255</v>
+        <v>6559107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Volker Kr&amp;uuml;ger  (WattFabrik)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>WATTFabrik</t>
-        </is>
-      </c>
+          <t>S Thrashco</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>42:56.762</t>
+          <t>46:34.184</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -21276,11 +21280,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4506475</v>
+        <v>7589756</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Roman Bevz</t>
+          <t>Kasper Steadywheel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -21291,7 +21295,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>41:10.290</t>
+          <t>46:45.815</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -21301,35 +21305,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4730842</v>
+        <v>5804361</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
+          <t>. WILLETTS</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ATGNI</t>
+          <t>BAKPDL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>40:21.219</t>
+          <t>46:53.302</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -21348,14 +21352,18 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4791080</v>
+        <v>74284</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>karl moreaux</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>Mark Feeney (COALITION)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -21363,17 +21371,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>41:11.882</t>
+          <t>48:07.217</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -21382,16 +21390,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4801108</v>
+        <v>7799511</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jorge Ar&amp;eacute;valo</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Velo&amp;#039;Z</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -21401,49 +21409,45 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>47:30.384</t>
+          <t>48:21.340</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4980720</v>
+        <v>2623657</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+          <t>Nathan True2168</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>41:18.345</t>
+          <t>42:47.371</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5604948</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="90">
@@ -21454,40 +21458,36 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5086087</v>
+        <v>3224040</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Miguel Loureiro</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>PAUL      ZU&amp;Ntilde;IGA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>49:18.384</t>
+          <t>42:52.181</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5604945</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -21496,11 +21496,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5139632</v>
+        <v>5992789</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thomas Mutz</t>
+          <t>Mathieu Gosselin</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -21511,37 +21511,33 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>41:06.208</t>
+          <t>42:56.888</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5402095</v>
+        <v>3053558</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Quentin Vee [EVO]</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>Cristian Montero</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -21549,45 +21545,45 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>40:20.947</t>
+          <t>44:08.751</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5491339</v>
+        <v>7582753</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Dan Thomas</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>50:01.560</t>
+          <t>45:07.711</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -21597,7 +21593,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -21606,11 +21602,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5687025</v>
+        <v>9152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Jonas Grunau</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -21620,12 +21616,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>40:37.442</t>
+          <t>45:08.032</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -21635,35 +21631,35 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5804361</v>
+        <v>2602856</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>. WILLETTS</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BAKPDL</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>46:53.302</t>
+          <t>45:09.122</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -21673,153 +21669,141 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5851455</v>
+        <v>1392843</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>taku hata</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Zsolt Kun-Szabo</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>42:54.445</t>
+          <t>45:09.182</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5877680</v>
+        <v>7105167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sem VH</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>COERS</t>
-        </is>
-      </c>
+          <t>Erik Grindbakken</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>40:37.948</t>
+          <t>46:27.111</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5880054</v>
+        <v>721114</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (GXY / SRT)</t>
+          <t>Craig Potter (WGW)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>WGW</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>44:42.363</t>
+          <t>46:29.600</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5893609</v>
+        <v>461128</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Andrew Walsh</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>40:21.924</t>
+          <t>46:30.530</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="100">
@@ -21834,92 +21818,92 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5895690</v>
+        <v>1516811</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Franco Borrini</t>
+          <t>Jamie Roy</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>Stages Cycling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>51:35.393</t>
+          <t>46:30.651</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5918191</v>
+        <v>825484</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R&amp;eacute;gis Thomas (Bikes-FR)</t>
+          <t>Jan van Leuverden</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BIKES &amp;#11088;&amp;#65039;</t>
+          <t>BEAT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>45:10.275</t>
+          <t>46:42.278</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5959135</v>
+        <v>123241</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ben  Spedding [TNP]</t>
+          <t>M Kerry (WCC)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>WCC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -21929,45 +21913,45 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>45:54.993</t>
+          <t>46:45.263</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5604946</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5981378</v>
+        <v>6997588</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t xml:space="preserve">L.Tanis[Ghost] </t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>44:46.265</t>
+          <t>46:45.606</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -21986,138 +21970,146 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5992789</v>
+        <v>1065618</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mathieu Gosselin</t>
+          <t>Yuru Kuzmin[VeloKavkaz]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>42:56.888</t>
+          <t>46:48.325</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6006740</v>
+        <v>1563175</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Keegan McCormick [A-P-V]</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>40:22.127</t>
+          <t>46:54.038</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6118343</v>
+        <v>7779078</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Christophe Chris [BIKES-FR]</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>David Irwin</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>46:24.649</t>
+          <t>46:56.468</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6279252</v>
+        <v>25</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Yannik Magnussen</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t xml:space="preserve">Reinhold Brezovszky [HERC/FS] </t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>40:20.536</t>
+          <t>46:57.756</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -22126,18 +22118,14 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6286619</v>
+        <v>3564783</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>U Will Drop Me</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Coalition Cycling</t>
-        </is>
-      </c>
+          <t>P Colo</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -22145,7 +22133,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>41:11.215</t>
+          <t>47:10.819</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -22155,7 +22143,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -22164,16 +22152,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6311857</v>
+        <v>4801108</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>L ook mum no hands (RollCo)</t>
+          <t>Jorge Ar&amp;eacute;valo</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>Velo&amp;#039;Z</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -22183,51 +22171,55 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>45:09.971</t>
+          <t>47:30.384</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6489023</v>
+        <v>7283905</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Marko J&amp;auml;rvenp&amp;auml;&amp;auml;</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>sean carter [WMZ]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>WMZ</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>42:56.346</t>
+          <t>48:23.912</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -22236,26 +22228,26 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6513233</v>
+        <v>5086087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Miguel Loureiro</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>50:14.612</t>
+          <t>49:18.384</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -22265,61 +22257,65 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6536177</v>
+        <v>284739</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Jack Barton</t>
+          <t>Mike Alford [EVO]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>41:57.667</t>
+          <t>49:37.995</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6559107</v>
+        <v>4127743</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>S Thrashco</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>Jos&amp;eacute; Ignacio URZUA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Velo&amp;#039;Z</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -22327,7 +22323,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>46:34.184</t>
+          <t>50:03.243</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -22337,39 +22333,39 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6715306</v>
+        <v>1379058</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Jay Rowe</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>40:26.761</t>
+          <t>50:10.835</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5604947</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="115">
@@ -22384,16 +22380,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6842342</v>
+        <v>832585</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ed Ferebee (Rhino)</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -22403,83 +22399,83 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>51:04.185</t>
+          <t>50:14.370</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5604950</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6853346</v>
+        <v>6842342</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthieu De Smet </t>
+          <t>Ed Ferebee (Rhino)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>38:50.090</t>
+          <t>51:04.185</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6863000</v>
+        <v>5895690</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Markus Schweizer</t>
+          <t>Franco Borrini</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>WEz pb Cycling District</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>38:58.040</t>
+          <t>51:35.393</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -22489,7 +22485,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -22498,60 +22494,60 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6866514</v>
+        <v>7455653</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Dennis Livesay</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>Justin Draper [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>43:56.130</t>
+          <t>52:28.846</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5604948</v>
+        <v>5604946</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6952720</v>
+        <v>7654466</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Remco Vanhoutte [A-P-V]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>A-P-V</t>
-        </is>
-      </c>
+          <t>Nicolas Schmitt</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>40:19.734</t>
+          <t>45:09.588</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -22561,7 +22557,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -22570,54 +22566,50 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6991072</v>
+        <v>2208583</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Ethan Crain</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>45:09.662</t>
+          <t>46:31.341</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="C121" t="n">
-        <v>6997588</v>
+        <v>1475359</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.Tanis[Ghost] </t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -22627,7 +22619,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>46:45.606</t>
+          <t>48:21.275</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -22637,97 +22629,101 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>7053041</v>
+        <v>5491339</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>William Smith (RollCo/TNP)</t>
+          <t>Brian Benner (HERC)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>42:42.775</t>
+          <t>50:01.560</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C123" t="n">
-        <v>7105167</v>
+        <v>4107226</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erik Grindbakken</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>Lars Falck [V]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Vikings</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>46:27.111</t>
+          <t>50:02.253</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5604948</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C124" t="n">
-        <v>7283905</v>
+        <v>6513233</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>sean carter [WMZ]</t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -22737,7 +22733,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>48:23.912</t>
+          <t>50:14.612</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -22747,25 +22743,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7364132</v>
+        <v>2648548</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Eddie Adams</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -22775,223 +22771,227 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>43:57.081</t>
+          <t>50:14.634</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7376425</v>
+        <v>3294901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>JakOnWheels   Attack</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>Stephen Groundwater [HERC)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>46:27.196</t>
+          <t>50:27.559</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5604948</v>
+        <v>5604945</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7410098</v>
+        <v>3712273</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Luke van Harskamp</t>
+          <t>CHRIS D</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>42:23.934</t>
+          <t>51:21.363</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>5604948</v>
+        <v>5604951</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="C128" t="n">
-        <v>7455653</v>
+        <v>441381</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Justin Draper [Fellowship]</t>
+          <t>Russell Agius2 (Epsom Tri A)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Epsom Tri</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>52:28.846</t>
+          <t>52:02.863</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>5604946</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7484167</v>
+        <v>2901486</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Edmund Tang</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Ingrid Klocke</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>42:46.269</t>
+          <t>52:05.019</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>5604950</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C130" t="n">
-        <v>7582753</v>
+        <v>66794</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Dan Thomas</t>
+          <t>Robby Parker</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>FinishStrong</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>45:07.711</t>
+          <t>52:19.248</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7589756</v>
+        <v>3228186</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Kasper Steadywheel</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>Aidan Novis (RHINO)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>46:45.815</t>
+          <t>53:00.922</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -23006,64 +23006,64 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7654466</v>
+        <v>2984059</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Nicolas Schmitt</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>Bruce Novis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>NOVIS</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>45:09.588</t>
+          <t>53:06.743</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>5604947</v>
+        <v>5604948</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C133" t="n">
-        <v>7779078</v>
+        <v>2288977</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>David Irwin</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>H Suzu&amp;#128150;</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>46:56.468</t>
+          <t>54:25.788</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -23073,20 +23073,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7799511</v>
+        <v>421191</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Andy Davy</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -23096,12 +23096,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>48:21.340</t>
+          <t>55:32.221</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -23111,58 +23111,58 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8262983</v>
+        <v>356837</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tuco  Benedicto (TEZH)</t>
+          <t>Joe Conley</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>45:58.245</t>
+          <t>57:35.394</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5604946</v>
+        <v>5604950</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8280250</v>
+        <v>3894706</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>D L</t>
+          <t>Mauro Malatesta</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -23172,35 +23172,35 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>41:55.141</t>
+          <t>58:42.537</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>5604945</v>
+        <v>5604947</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8389020</v>
+        <v>3732567</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tibo Peeters</t>
+          <t>Adam Levin</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -23211,11 +23211,11 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>40:20.278</t>
+          <t>57:35.811</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5604947</v>
+        <v>5604950</v>
       </c>
     </row>
   </sheetData>
